--- a/03. CMH116 OFCI Log REV2.0.xlsx
+++ b/03. CMH116 OFCI Log REV2.0.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6952" uniqueCount="529">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6984" uniqueCount="541">
   <si>
     <t/>
   </si>
@@ -385,7 +385,7 @@
     <t>LV SWITCHGEAR</t>
   </si>
   <si>
-    <t>Going to PreFab or CraneWW</t>
+    <t>Going to PreFab</t>
   </si>
   <si>
     <t>ROMP 01 LV SWITCHGEAR</t>
@@ -470,9 +470,6 @@
   </si>
   <si>
     <t>MV SWITCHGEAR</t>
-  </si>
-  <si>
-    <t>Going to PreFab</t>
   </si>
   <si>
     <t>MV Switchgear</t>
@@ -737,12 +734,12 @@
     <t>Phase 1-10 have been delivered to Crane World Wide</t>
   </si>
   <si>
+    <t>Pull-In Ticket Requested</t>
+  </si>
+  <si>
     <t>Phase 3 PDC</t>
   </si>
   <si>
-    <t>5.5.25 - "TETRIS" proposed via Amazon Approval 38141325</t>
-  </si>
-  <si>
     <t>Phase 4 PDC</t>
   </si>
   <si>
@@ -1158,6 +1155,45 @@
   </si>
   <si>
     <t>Phase 12 Racking</t>
+  </si>
+  <si>
+    <t>Row 80</t>
+  </si>
+  <si>
+    <t>HSSB delivery to Prefab 12/15</t>
+  </si>
+  <si>
+    <t>Jason Laird</t>
+  </si>
+  <si>
+    <t>12/05/25 7:07 AM</t>
+  </si>
+  <si>
+    <t>Row 92</t>
+  </si>
+  <si>
+    <t>Is there an estimated delivery date for the ATS equipment.</t>
+  </si>
+  <si>
+    <t>12/05/25 6:43 AM</t>
+  </si>
+  <si>
+    <t>Row 97</t>
+  </si>
+  <si>
+    <t>Any updates on when the ATS equipment will ship to Prefab?</t>
+  </si>
+  <si>
+    <t>12/05/25 10:48 AM</t>
+  </si>
+  <si>
+    <t>Sheet</t>
+  </si>
+  <si>
+    <t>@alepar@hilscher-clarke.com</t>
+  </si>
+  <si>
+    <t>12/05/25 10:49 AM</t>
   </si>
   <si>
     <t># of Items Overdue on build</t>
@@ -1613,7 +1649,7 @@
     <numFmt numFmtId="165" formatCode="###0;-###0"/>
     <numFmt numFmtId="166" formatCode="###0.0000000000000;-###0.0000000000000"/>
   </numFmts>
-  <fonts count="57">
+  <fonts count="54">
     <font>
       <sz val="11.0"/>
       <color indexed="8"/>
@@ -1949,24 +1985,6 @@
       <color rgb="000000"/>
       <u val="none"/>
     </font>
-    <font>
-      <name val="Arial"/>
-      <sz val="10.0"/>
-      <color rgb="000000"/>
-      <u val="none"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <sz val="10.0"/>
-      <color rgb="000000"/>
-      <u val="none"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <sz val="10.0"/>
-      <color rgb="000000"/>
-      <u val="none"/>
-    </font>
   </fonts>
   <fills count="14">
     <fill>
@@ -2048,7 +2066,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="114">
+  <cellXfs count="108">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -2252,23 +2270,11 @@
       <alignment horizontal="left" vertical="center" wrapText="false" indent="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
-    <xf numFmtId="164" fontId="52" fillId="5" borderId="0" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true">
-      <alignment horizontal="center" vertical="center" wrapText="true" indent="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
-    <xf numFmtId="164" fontId="53" fillId="0" borderId="0" xfId="0" applyNumberFormat="true" applyFont="true">
-      <alignment horizontal="center" vertical="top" wrapText="false" indent="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
-    <xf numFmtId="164" fontId="54" fillId="5" borderId="0" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true">
-      <alignment horizontal="center" vertical="top" wrapText="false" indent="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
-    <xf numFmtId="164" fontId="55" fillId="11" borderId="0" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true">
+    <xf numFmtId="164" fontId="52" fillId="11" borderId="0" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true">
       <alignment horizontal="center" vertical="top" wrapText="false" indent="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="56" fillId="13" borderId="0" xfId="0" applyFont="true" applyFill="true">
+    <xf numFmtId="0" fontId="53" fillId="13" borderId="0" xfId="0" applyFont="true" applyFill="true">
       <alignment horizontal="center" vertical="top" wrapText="false" indent="0"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
@@ -2501,7 +2507,7 @@
       <c r="R7" s="17"/>
       <c r="S7" s="17"/>
     </row>
-    <row r="8" hidden="false" outlineLevel="1">
+    <row r="8" hidden="true" outlineLevel="1">
       <c r="A8" s="25"/>
       <c r="B8" s="5"/>
       <c r="C8" s="5"/>
@@ -2522,7 +2528,7 @@
       <c r="R8" s="5"/>
       <c r="S8" s="5"/>
     </row>
-    <row r="9" hidden="false" outlineLevel="1">
+    <row r="9" hidden="true" outlineLevel="1">
       <c r="A9" t="s" s="27">
         <v>25</v>
       </c>
@@ -2551,7 +2557,7 @@
       </c>
       <c r="S9" s="29"/>
     </row>
-    <row r="10" hidden="false" outlineLevel="2">
+    <row r="10" hidden="true" outlineLevel="2">
       <c r="A10" t="s" s="37">
         <v>28</v>
       </c>
@@ -2606,7 +2612,7 @@
         <v>45963.0</v>
       </c>
     </row>
-    <row r="11" hidden="false" outlineLevel="2">
+    <row r="11" hidden="true" outlineLevel="2">
       <c r="A11" t="s" s="37">
         <v>28</v>
       </c>
@@ -2661,7 +2667,7 @@
         <v>45963.0</v>
       </c>
     </row>
-    <row r="12" hidden="false" outlineLevel="2">
+    <row r="12" hidden="true" outlineLevel="2">
       <c r="A12" t="s" s="37">
         <v>28</v>
       </c>
@@ -2716,7 +2722,7 @@
         <v>45963.0</v>
       </c>
     </row>
-    <row r="13" hidden="false" outlineLevel="2">
+    <row r="13" hidden="true" outlineLevel="2">
       <c r="A13" t="s" s="37">
         <v>28</v>
       </c>
@@ -2771,7 +2777,7 @@
         <v>45963.0</v>
       </c>
     </row>
-    <row r="14" hidden="false" outlineLevel="2">
+    <row r="14" hidden="true" outlineLevel="2">
       <c r="A14" t="s" s="37">
         <v>28</v>
       </c>
@@ -2822,7 +2828,7 @@
         <v>45963.0</v>
       </c>
     </row>
-    <row r="15" hidden="false" outlineLevel="2">
+    <row r="15" hidden="true" outlineLevel="2">
       <c r="A15" t="s" s="51">
         <v>39</v>
       </c>
@@ -2865,7 +2871,7 @@
       </c>
       <c r="S15" s="5"/>
     </row>
-    <row r="16" hidden="false" outlineLevel="2">
+    <row r="16" hidden="true" outlineLevel="2">
       <c r="A16" t="s" s="37">
         <v>42</v>
       </c>
@@ -2908,7 +2914,7 @@
       </c>
       <c r="S16" s="5"/>
     </row>
-    <row r="17" hidden="false" outlineLevel="1">
+    <row r="17" hidden="true" outlineLevel="1">
       <c r="A17" t="s" s="27">
         <v>43</v>
       </c>
@@ -2937,7 +2943,7 @@
       </c>
       <c r="S17" s="57"/>
     </row>
-    <row r="18" hidden="false" outlineLevel="2">
+    <row r="18" hidden="true" outlineLevel="2">
       <c r="A18" t="s" s="37">
         <v>44</v>
       </c>
@@ -2992,7 +2998,7 @@
         <v>46041.0</v>
       </c>
     </row>
-    <row r="19" hidden="false" outlineLevel="2">
+    <row r="19" hidden="true" outlineLevel="2">
       <c r="A19" t="s" s="37">
         <v>44</v>
       </c>
@@ -3047,7 +3053,7 @@
         <v>46041.0</v>
       </c>
     </row>
-    <row r="20" hidden="false" outlineLevel="2">
+    <row r="20" hidden="true" outlineLevel="2">
       <c r="A20" t="s" s="61">
         <v>48</v>
       </c>
@@ -3088,7 +3094,7 @@
       </c>
       <c r="S20" s="17"/>
     </row>
-    <row r="21" hidden="false" outlineLevel="2">
+    <row r="21" hidden="true" outlineLevel="2">
       <c r="A21" t="s" s="37">
         <v>49</v>
       </c>
@@ -3131,7 +3137,7 @@
       </c>
       <c r="S21" s="5"/>
     </row>
-    <row r="22" hidden="false" outlineLevel="1">
+    <row r="22" hidden="true" outlineLevel="1">
       <c r="A22" t="s" s="27">
         <v>50</v>
       </c>
@@ -3160,7 +3166,7 @@
       </c>
       <c r="S22" s="57"/>
     </row>
-    <row r="23" hidden="false" outlineLevel="2">
+    <row r="23" hidden="true" outlineLevel="2">
       <c r="A23" t="s" s="37">
         <v>51</v>
       </c>
@@ -3213,7 +3219,7 @@
         <v>46062.0</v>
       </c>
     </row>
-    <row r="24" hidden="false" outlineLevel="2">
+    <row r="24" hidden="true" outlineLevel="2">
       <c r="A24" t="s" s="37">
         <v>51</v>
       </c>
@@ -3266,7 +3272,7 @@
         <v>46062.0</v>
       </c>
     </row>
-    <row r="25" hidden="false" outlineLevel="2">
+    <row r="25" hidden="true" outlineLevel="2">
       <c r="A25" t="s" s="61">
         <v>55</v>
       </c>
@@ -3309,7 +3315,7 @@
       </c>
       <c r="S25" s="17"/>
     </row>
-    <row r="26" hidden="false" outlineLevel="2">
+    <row r="26" hidden="true" outlineLevel="2">
       <c r="A26" t="s" s="61">
         <v>57</v>
       </c>
@@ -3350,7 +3356,7 @@
       </c>
       <c r="S26" s="5"/>
     </row>
-    <row r="27" hidden="false" outlineLevel="1">
+    <row r="27" hidden="true" outlineLevel="1">
       <c r="A27" t="s" s="27">
         <v>58</v>
       </c>
@@ -3379,7 +3385,7 @@
       </c>
       <c r="S27" s="57"/>
     </row>
-    <row r="28" hidden="false" outlineLevel="2">
+    <row r="28" hidden="true" outlineLevel="2">
       <c r="A28" t="s" s="61">
         <v>59</v>
       </c>
@@ -3430,7 +3436,7 @@
         <v>46083.0</v>
       </c>
     </row>
-    <row r="29" hidden="false" outlineLevel="2">
+    <row r="29" hidden="true" outlineLevel="2">
       <c r="A29" t="s" s="61">
         <v>59</v>
       </c>
@@ -3481,7 +3487,7 @@
         <v>46083.0</v>
       </c>
     </row>
-    <row r="30" hidden="false" outlineLevel="2">
+    <row r="30" hidden="true" outlineLevel="2">
       <c r="A30" t="s" s="61">
         <v>64</v>
       </c>
@@ -3524,7 +3530,7 @@
       </c>
       <c r="S30" s="17"/>
     </row>
-    <row r="31" hidden="false" outlineLevel="2">
+    <row r="31" hidden="true" outlineLevel="2">
       <c r="A31" t="s" s="61">
         <v>65</v>
       </c>
@@ -3565,7 +3571,7 @@
       </c>
       <c r="S31" s="5"/>
     </row>
-    <row r="32" hidden="false" outlineLevel="1">
+    <row r="32" hidden="true" outlineLevel="1">
       <c r="A32" t="s" s="27">
         <v>66</v>
       </c>
@@ -3594,7 +3600,7 @@
       </c>
       <c r="S32" s="57"/>
     </row>
-    <row r="33" hidden="false" outlineLevel="2">
+    <row r="33" hidden="true" outlineLevel="2">
       <c r="A33" t="s" s="61">
         <v>67</v>
       </c>
@@ -3645,7 +3651,7 @@
         <v>46104.0</v>
       </c>
     </row>
-    <row r="34" hidden="false" outlineLevel="2">
+    <row r="34" hidden="true" outlineLevel="2">
       <c r="A34" t="s" s="61">
         <v>67</v>
       </c>
@@ -3696,7 +3702,7 @@
         <v>46104.0</v>
       </c>
     </row>
-    <row r="35" hidden="false" outlineLevel="2">
+    <row r="35" hidden="true" outlineLevel="2">
       <c r="A35" t="s" s="61">
         <v>71</v>
       </c>
@@ -3737,7 +3743,7 @@
       </c>
       <c r="S35" s="17"/>
     </row>
-    <row r="36" hidden="false" outlineLevel="2">
+    <row r="36" hidden="true" outlineLevel="2">
       <c r="A36" t="s" s="61">
         <v>72</v>
       </c>
@@ -3782,7 +3788,7 @@
       </c>
       <c r="S36" s="5"/>
     </row>
-    <row r="37" hidden="false" outlineLevel="1">
+    <row r="37" hidden="true" outlineLevel="1">
       <c r="A37" t="s" s="27">
         <v>73</v>
       </c>
@@ -3811,7 +3817,7 @@
       </c>
       <c r="S37" s="57"/>
     </row>
-    <row r="38" hidden="false" outlineLevel="2">
+    <row r="38" hidden="true" outlineLevel="2">
       <c r="A38" t="s" s="61">
         <v>74</v>
       </c>
@@ -3862,7 +3868,7 @@
         <v>46125.0</v>
       </c>
     </row>
-    <row r="39" hidden="false" outlineLevel="2">
+    <row r="39" hidden="true" outlineLevel="2">
       <c r="A39" t="s" s="61">
         <v>74</v>
       </c>
@@ -3913,7 +3919,7 @@
         <v>46125.0</v>
       </c>
     </row>
-    <row r="40" hidden="false" outlineLevel="2">
+    <row r="40" hidden="true" outlineLevel="2">
       <c r="A40" t="s" s="61">
         <v>78</v>
       </c>
@@ -3954,7 +3960,7 @@
       </c>
       <c r="S40" s="17"/>
     </row>
-    <row r="41" hidden="false" outlineLevel="2">
+    <row r="41" hidden="true" outlineLevel="2">
       <c r="A41" t="s" s="61">
         <v>79</v>
       </c>
@@ -3999,7 +4005,7 @@
       </c>
       <c r="S41" s="5"/>
     </row>
-    <row r="42" hidden="false" outlineLevel="1">
+    <row r="42" hidden="true" outlineLevel="1">
       <c r="A42" t="s" s="27">
         <v>80</v>
       </c>
@@ -4028,7 +4034,7 @@
       </c>
       <c r="S42" s="57"/>
     </row>
-    <row r="43" hidden="false" outlineLevel="2">
+    <row r="43" hidden="true" outlineLevel="2">
       <c r="A43" t="s" s="61">
         <v>81</v>
       </c>
@@ -4079,7 +4085,7 @@
         <v>46146.0</v>
       </c>
     </row>
-    <row r="44" hidden="false" outlineLevel="2">
+    <row r="44" hidden="true" outlineLevel="2">
       <c r="A44" t="s" s="61">
         <v>81</v>
       </c>
@@ -4130,7 +4136,7 @@
         <v>46146.0</v>
       </c>
     </row>
-    <row r="45" hidden="false" outlineLevel="2">
+    <row r="45" hidden="true" outlineLevel="2">
       <c r="A45" t="s" s="61">
         <v>85</v>
       </c>
@@ -4171,7 +4177,7 @@
       </c>
       <c r="S45" s="17"/>
     </row>
-    <row r="46" hidden="false" outlineLevel="2">
+    <row r="46" hidden="true" outlineLevel="2">
       <c r="A46" t="s" s="61">
         <v>86</v>
       </c>
@@ -4216,7 +4222,7 @@
       </c>
       <c r="S46" s="5"/>
     </row>
-    <row r="47" hidden="false" outlineLevel="1">
+    <row r="47" hidden="true" outlineLevel="1">
       <c r="A47" t="s" s="27">
         <v>87</v>
       </c>
@@ -4245,7 +4251,7 @@
       </c>
       <c r="S47" s="57"/>
     </row>
-    <row r="48" hidden="false" outlineLevel="2">
+    <row r="48" hidden="true" outlineLevel="2">
       <c r="A48" t="s" s="61">
         <v>88</v>
       </c>
@@ -4296,7 +4302,7 @@
         <v>46167.0</v>
       </c>
     </row>
-    <row r="49" hidden="false" outlineLevel="2">
+    <row r="49" hidden="true" outlineLevel="2">
       <c r="A49" t="s" s="61">
         <v>88</v>
       </c>
@@ -4347,7 +4353,7 @@
         <v>46167.0</v>
       </c>
     </row>
-    <row r="50" hidden="false" outlineLevel="2">
+    <row r="50" hidden="true" outlineLevel="2">
       <c r="A50" t="s" s="61">
         <v>92</v>
       </c>
@@ -4388,7 +4394,7 @@
       </c>
       <c r="S50" s="17"/>
     </row>
-    <row r="51" hidden="false" outlineLevel="2">
+    <row r="51" hidden="true" outlineLevel="2">
       <c r="A51" t="s" s="61">
         <v>93</v>
       </c>
@@ -4433,7 +4439,7 @@
       </c>
       <c r="S51" s="5"/>
     </row>
-    <row r="52" hidden="false" outlineLevel="1">
+    <row r="52" hidden="true" outlineLevel="1">
       <c r="A52" t="s" s="27">
         <v>94</v>
       </c>
@@ -4462,7 +4468,7 @@
       </c>
       <c r="S52" s="57"/>
     </row>
-    <row r="53" hidden="false" outlineLevel="2">
+    <row r="53" hidden="true" outlineLevel="2">
       <c r="A53" t="s" s="61">
         <v>95</v>
       </c>
@@ -4513,7 +4519,7 @@
         <v>46188.0</v>
       </c>
     </row>
-    <row r="54" hidden="false" outlineLevel="2">
+    <row r="54" hidden="true" outlineLevel="2">
       <c r="A54" t="s" s="61">
         <v>95</v>
       </c>
@@ -4564,7 +4570,7 @@
         <v>46188.0</v>
       </c>
     </row>
-    <row r="55" hidden="false" outlineLevel="2">
+    <row r="55" hidden="true" outlineLevel="2">
       <c r="A55" t="s" s="61">
         <v>99</v>
       </c>
@@ -4605,7 +4611,7 @@
       </c>
       <c r="S55" s="17"/>
     </row>
-    <row r="56" hidden="false" outlineLevel="2">
+    <row r="56" hidden="true" outlineLevel="2">
       <c r="A56" t="s" s="61">
         <v>100</v>
       </c>
@@ -4650,7 +4656,7 @@
       </c>
       <c r="S56" s="5"/>
     </row>
-    <row r="57" hidden="false" outlineLevel="1">
+    <row r="57" hidden="true" outlineLevel="1">
       <c r="A57" t="s" s="27">
         <v>101</v>
       </c>
@@ -4679,7 +4685,7 @@
       </c>
       <c r="S57" s="57"/>
     </row>
-    <row r="58" hidden="false" outlineLevel="2">
+    <row r="58" hidden="true" outlineLevel="2">
       <c r="A58" t="s" s="61">
         <v>102</v>
       </c>
@@ -4730,7 +4736,7 @@
         <v>46209.0</v>
       </c>
     </row>
-    <row r="59" hidden="false" outlineLevel="2">
+    <row r="59" hidden="true" outlineLevel="2">
       <c r="A59" t="s" s="61">
         <v>102</v>
       </c>
@@ -4781,7 +4787,7 @@
         <v>46209.0</v>
       </c>
     </row>
-    <row r="60" hidden="false" outlineLevel="2">
+    <row r="60" hidden="true" outlineLevel="2">
       <c r="A60" t="s" s="61">
         <v>106</v>
       </c>
@@ -4822,7 +4828,7 @@
       </c>
       <c r="S60" s="17"/>
     </row>
-    <row r="61" hidden="false" outlineLevel="2">
+    <row r="61" hidden="true" outlineLevel="2">
       <c r="A61" t="s" s="61">
         <v>107</v>
       </c>
@@ -4867,7 +4873,7 @@
       </c>
       <c r="S61" s="5"/>
     </row>
-    <row r="62" hidden="false" outlineLevel="1">
+    <row r="62" hidden="true" outlineLevel="1">
       <c r="A62" t="s" s="27">
         <v>108</v>
       </c>
@@ -4896,7 +4902,7 @@
       </c>
       <c r="S62" s="57"/>
     </row>
-    <row r="63" hidden="false" outlineLevel="2">
+    <row r="63" hidden="true" outlineLevel="2">
       <c r="A63" t="s" s="61">
         <v>109</v>
       </c>
@@ -4947,7 +4953,7 @@
         <v>46230.0</v>
       </c>
     </row>
-    <row r="64" hidden="false" outlineLevel="2">
+    <row r="64" hidden="true" outlineLevel="2">
       <c r="A64" t="s" s="61">
         <v>109</v>
       </c>
@@ -4998,7 +5004,7 @@
         <v>46230.0</v>
       </c>
     </row>
-    <row r="65" hidden="false" outlineLevel="2">
+    <row r="65" hidden="true" outlineLevel="2">
       <c r="A65" t="s" s="61">
         <v>113</v>
       </c>
@@ -5039,7 +5045,7 @@
       </c>
       <c r="S65" s="17"/>
     </row>
-    <row r="66" hidden="false" outlineLevel="2">
+    <row r="66" hidden="true" outlineLevel="2">
       <c r="A66" t="s" s="61">
         <v>114</v>
       </c>
@@ -5084,7 +5090,7 @@
       </c>
       <c r="S66" s="5"/>
     </row>
-    <row r="67" hidden="false" outlineLevel="1">
+    <row r="67" hidden="true" outlineLevel="1">
       <c r="A67" t="s" s="27">
         <v>115</v>
       </c>
@@ -5113,7 +5119,7 @@
       </c>
       <c r="S67" s="57"/>
     </row>
-    <row r="68" hidden="false" outlineLevel="2">
+    <row r="68" hidden="true" outlineLevel="2">
       <c r="A68" t="s" s="61">
         <v>116</v>
       </c>
@@ -5164,7 +5170,7 @@
         <v>46251.0</v>
       </c>
     </row>
-    <row r="69" hidden="false" outlineLevel="2">
+    <row r="69" hidden="true" outlineLevel="2">
       <c r="A69" t="s" s="61">
         <v>116</v>
       </c>
@@ -5215,7 +5221,7 @@
         <v>46251.0</v>
       </c>
     </row>
-    <row r="70" hidden="false" outlineLevel="2">
+    <row r="70" hidden="true" outlineLevel="2">
       <c r="A70" t="s" s="61">
         <v>120</v>
       </c>
@@ -5256,7 +5262,7 @@
       </c>
       <c r="S70" s="17"/>
     </row>
-    <row r="71" hidden="false" outlineLevel="2">
+    <row r="71" hidden="true" outlineLevel="2">
       <c r="A71" t="s" s="61">
         <v>121</v>
       </c>
@@ -8761,7 +8767,7 @@
       <c r="L161" s="77"/>
       <c r="M161" s="77"/>
       <c r="N161" t="s" s="77">
-        <v>152</v>
+        <v>123</v>
       </c>
       <c r="O161" s="77"/>
       <c r="P161" s="19"/>
@@ -8769,7 +8775,7 @@
       <c r="R161" s="17"/>
       <c r="S161" s="19"/>
     </row>
-    <row r="162" hidden="false" outlineLevel="1">
+    <row r="162" hidden="true" outlineLevel="1">
       <c r="A162" s="25"/>
       <c r="B162" s="5"/>
       <c r="C162" s="5"/>
@@ -8790,7 +8796,7 @@
       <c r="R162" s="5"/>
       <c r="S162" s="5"/>
     </row>
-    <row r="163" hidden="false" outlineLevel="1">
+    <row r="163" hidden="true" outlineLevel="1">
       <c r="A163" t="s" s="101">
         <v>25</v>
       </c>
@@ -8798,10 +8804,10 @@
         <v>29</v>
       </c>
       <c r="C163" t="s" s="39">
+        <v>152</v>
+      </c>
+      <c r="D163" t="s" s="39">
         <v>153</v>
-      </c>
-      <c r="D163" t="s" s="39">
-        <v>154</v>
       </c>
       <c r="E163" t="s" s="39">
         <v>126</v>
@@ -8829,7 +8835,7 @@
       </c>
       <c r="M163" s="11"/>
       <c r="N163" t="s" s="13">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="O163" s="11"/>
       <c r="P163" s="5"/>
@@ -8841,7 +8847,7 @@
       </c>
       <c r="S163" s="5"/>
     </row>
-    <row r="164" hidden="false" outlineLevel="1">
+    <row r="164" hidden="true" outlineLevel="1">
       <c r="A164" t="s" s="101">
         <v>25</v>
       </c>
@@ -8849,10 +8855,10 @@
         <v>29</v>
       </c>
       <c r="C164" t="s" s="39">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D164" t="s" s="39">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E164" t="s" s="39">
         <v>126</v>
@@ -8880,7 +8886,7 @@
       </c>
       <c r="M164" s="11"/>
       <c r="N164" t="s" s="13">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="O164" s="11"/>
       <c r="P164" s="5"/>
@@ -8915,7 +8921,7 @@
     </row>
     <row r="166" hidden="false">
       <c r="A166" t="s" s="15">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B166" s="19"/>
       <c r="C166" s="19"/>
@@ -8936,7 +8942,7 @@
       <c r="R166" s="17"/>
       <c r="S166" s="19"/>
     </row>
-    <row r="167" hidden="false" outlineLevel="1">
+    <row r="167" hidden="true" outlineLevel="1">
       <c r="A167" s="25"/>
       <c r="B167" s="5"/>
       <c r="C167" s="5"/>
@@ -8957,13 +8963,13 @@
       <c r="R167" s="5"/>
       <c r="S167" s="5"/>
     </row>
-    <row r="168" hidden="false" outlineLevel="1">
+    <row r="168" hidden="true" outlineLevel="1">
       <c r="A168" t="s" s="27">
         <v>25</v>
       </c>
       <c r="B168" s="57"/>
       <c r="C168" t="s" s="29">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D168" s="57"/>
       <c r="E168" t="s" s="29">
@@ -8984,18 +8990,18 @@
       <c r="R168" s="29"/>
       <c r="S168" s="57"/>
     </row>
-    <row r="169" hidden="false" outlineLevel="2">
+    <row r="169" hidden="true" outlineLevel="2">
       <c r="A169" t="s" s="61">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B169" t="s" s="63">
         <v>29</v>
       </c>
       <c r="C169" t="s" s="63">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D169" t="s" s="63">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E169" t="s" s="63">
         <v>126</v>
@@ -9021,7 +9027,7 @@
       <c r="L169" s="75"/>
       <c r="M169" s="11"/>
       <c r="N169" t="s" s="13">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="O169" s="11"/>
       <c r="P169" s="5"/>
@@ -9033,18 +9039,18 @@
       </c>
       <c r="S169" s="5"/>
     </row>
-    <row r="170" hidden="false" outlineLevel="2">
+    <row r="170" hidden="true" outlineLevel="2">
       <c r="A170" t="s" s="37">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B170" t="s" s="39">
         <v>29</v>
       </c>
       <c r="C170" t="s" s="39">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D170" t="s" s="39">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E170" t="s" s="39">
         <v>126</v>
@@ -9072,7 +9078,7 @@
       </c>
       <c r="M170" s="11"/>
       <c r="N170" t="s" s="13">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="O170" s="11"/>
       <c r="P170" s="5"/>
@@ -9084,18 +9090,18 @@
       </c>
       <c r="S170" s="5"/>
     </row>
-    <row r="171" hidden="false" outlineLevel="2">
+    <row r="171" hidden="true" outlineLevel="2">
       <c r="A171" t="s" s="37">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B171" t="s" s="39">
         <v>29</v>
       </c>
       <c r="C171" t="s" s="39">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D171" t="s" s="39">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E171" t="s" s="39">
         <v>126</v>
@@ -9123,7 +9129,7 @@
       </c>
       <c r="M171" s="11"/>
       <c r="N171" t="s" s="13">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="O171" s="11"/>
       <c r="P171" s="5"/>
@@ -9135,18 +9141,18 @@
       </c>
       <c r="S171" s="5"/>
     </row>
-    <row r="172" hidden="false" outlineLevel="2">
+    <row r="172" hidden="true" outlineLevel="2">
       <c r="A172" t="s" s="37">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B172" t="s" s="39">
         <v>29</v>
       </c>
       <c r="C172" t="s" s="39">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D172" t="s" s="39">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E172" t="s" s="39">
         <v>126</v>
@@ -9174,7 +9180,7 @@
       </c>
       <c r="M172" s="11"/>
       <c r="N172" t="s" s="13">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="O172" s="11"/>
       <c r="P172" s="5"/>
@@ -9186,18 +9192,18 @@
       </c>
       <c r="S172" s="5"/>
     </row>
-    <row r="173" hidden="false" outlineLevel="2">
+    <row r="173" hidden="true" outlineLevel="2">
       <c r="A173" t="s" s="51">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B173" t="s" s="5">
         <v>29</v>
       </c>
       <c r="C173" t="s" s="5">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D173" t="s" s="5">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E173" t="s" s="5">
         <v>126</v>
@@ -9215,13 +9221,13 @@
         <v>45949.0</v>
       </c>
       <c r="J173" t="s" s="5">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="K173" s="5"/>
       <c r="L173" s="11"/>
       <c r="M173" s="11"/>
       <c r="N173" t="s" s="13">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="O173" s="11"/>
       <c r="P173" s="5"/>
@@ -9233,13 +9239,13 @@
       </c>
       <c r="S173" s="5"/>
     </row>
-    <row r="174" hidden="false" outlineLevel="1">
+    <row r="174" hidden="true" outlineLevel="1">
       <c r="A174" t="s" s="27">
         <v>43</v>
       </c>
       <c r="B174" s="57"/>
       <c r="C174" t="s" s="29">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D174" s="57"/>
       <c r="E174" t="s" s="29">
@@ -9262,18 +9268,18 @@
       </c>
       <c r="S174" s="57"/>
     </row>
-    <row r="175" hidden="false" outlineLevel="2">
+    <row r="175" hidden="true" outlineLevel="2">
       <c r="A175" t="s" s="37">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B175" t="s" s="39">
         <v>45</v>
       </c>
       <c r="C175" t="s" s="39">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D175" t="s" s="39">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E175" t="s" s="39">
         <v>126</v>
@@ -9301,7 +9307,7 @@
       </c>
       <c r="M175" s="11"/>
       <c r="N175" t="s" s="13">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="O175" s="11"/>
       <c r="P175" s="5"/>
@@ -9313,18 +9319,18 @@
       </c>
       <c r="S175" s="5"/>
     </row>
-    <row r="176" hidden="false" outlineLevel="2">
+    <row r="176" hidden="true" outlineLevel="2">
       <c r="A176" t="s" s="37">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B176" t="s" s="39">
         <v>45</v>
       </c>
       <c r="C176" t="s" s="39">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D176" t="s" s="39">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E176" t="s" s="39">
         <v>126</v>
@@ -9352,7 +9358,7 @@
       </c>
       <c r="M176" s="11"/>
       <c r="N176" t="s" s="13">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="O176" s="11"/>
       <c r="P176" s="5"/>
@@ -9364,13 +9370,13 @@
       </c>
       <c r="S176" s="5"/>
     </row>
-    <row r="177" hidden="false" outlineLevel="1">
+    <row r="177" hidden="true" outlineLevel="1">
       <c r="A177" t="s" s="27">
         <v>50</v>
       </c>
       <c r="B177" s="57"/>
       <c r="C177" t="s" s="29">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D177" s="57"/>
       <c r="E177" t="s" s="29">
@@ -9393,18 +9399,18 @@
       </c>
       <c r="S177" s="57"/>
     </row>
-    <row r="178" hidden="false" outlineLevel="2">
+    <row r="178" hidden="true" outlineLevel="2">
       <c r="A178" t="s" s="37">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B178" t="s" s="39">
         <v>52</v>
       </c>
       <c r="C178" t="s" s="39">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D178" t="s" s="39">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E178" t="s" s="39">
         <v>126</v>
@@ -9432,7 +9438,7 @@
       </c>
       <c r="M178" s="11"/>
       <c r="N178" t="s" s="13">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="O178" s="11"/>
       <c r="P178" s="5"/>
@@ -9444,18 +9450,18 @@
       </c>
       <c r="S178" s="5"/>
     </row>
-    <row r="179" hidden="false" outlineLevel="2">
+    <row r="179" hidden="true" outlineLevel="2">
       <c r="A179" t="s" s="37">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B179" t="s" s="39">
         <v>52</v>
       </c>
       <c r="C179" t="s" s="39">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D179" t="s" s="39">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E179" t="s" s="39">
         <v>126</v>
@@ -9483,7 +9489,7 @@
       </c>
       <c r="M179" s="11"/>
       <c r="N179" t="s" s="13">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="O179" s="11"/>
       <c r="P179" s="5"/>
@@ -9495,13 +9501,13 @@
       </c>
       <c r="S179" s="5"/>
     </row>
-    <row r="180" hidden="false" outlineLevel="1">
+    <row r="180" hidden="true" outlineLevel="1">
       <c r="A180" t="s" s="27">
         <v>58</v>
       </c>
       <c r="B180" s="57"/>
       <c r="C180" t="s" s="29">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D180" s="57"/>
       <c r="E180" t="s" s="29">
@@ -9524,18 +9530,18 @@
       </c>
       <c r="S180" s="57"/>
     </row>
-    <row r="181" hidden="false" outlineLevel="2">
+    <row r="181" hidden="true" outlineLevel="2">
       <c r="A181" t="s" s="37">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B181" t="s" s="39">
         <v>60</v>
       </c>
       <c r="C181" t="s" s="39">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D181" t="s" s="39">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E181" t="s" s="39">
         <v>126</v>
@@ -9563,7 +9569,7 @@
       </c>
       <c r="M181" s="11"/>
       <c r="N181" t="s" s="13">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="O181" s="11"/>
       <c r="P181" s="5"/>
@@ -9575,18 +9581,18 @@
       </c>
       <c r="S181" s="5"/>
     </row>
-    <row r="182" hidden="false" outlineLevel="2">
+    <row r="182" hidden="true" outlineLevel="2">
       <c r="A182" t="s" s="37">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B182" t="s" s="39">
         <v>60</v>
       </c>
       <c r="C182" t="s" s="39">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D182" t="s" s="39">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E182" t="s" s="39">
         <v>126</v>
@@ -9614,7 +9620,7 @@
       </c>
       <c r="M182" s="11"/>
       <c r="N182" t="s" s="13">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="O182" s="11"/>
       <c r="P182" s="5"/>
@@ -9626,13 +9632,13 @@
       </c>
       <c r="S182" s="5"/>
     </row>
-    <row r="183" hidden="false" outlineLevel="1">
+    <row r="183" hidden="true" outlineLevel="1">
       <c r="A183" t="s" s="27">
         <v>66</v>
       </c>
       <c r="B183" s="57"/>
       <c r="C183" t="s" s="29">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D183" s="57"/>
       <c r="E183" t="s" s="29">
@@ -9655,18 +9661,18 @@
       </c>
       <c r="S183" s="57"/>
     </row>
-    <row r="184" hidden="false" outlineLevel="2">
+    <row r="184" hidden="true" outlineLevel="2">
       <c r="A184" t="s" s="37">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B184" t="s" s="39">
         <v>68</v>
       </c>
       <c r="C184" t="s" s="39">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D184" t="s" s="39">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E184" t="s" s="39">
         <v>126</v>
@@ -9694,7 +9700,7 @@
       </c>
       <c r="M184" s="11"/>
       <c r="N184" t="s" s="13">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="O184" s="11"/>
       <c r="P184" s="5"/>
@@ -9706,18 +9712,18 @@
       </c>
       <c r="S184" s="5"/>
     </row>
-    <row r="185" hidden="false" outlineLevel="2">
+    <row r="185" hidden="true" outlineLevel="2">
       <c r="A185" t="s" s="37">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B185" t="s" s="39">
         <v>68</v>
       </c>
       <c r="C185" t="s" s="39">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D185" t="s" s="39">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E185" t="s" s="39">
         <v>126</v>
@@ -9745,7 +9751,7 @@
       </c>
       <c r="M185" s="11"/>
       <c r="N185" t="s" s="13">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="O185" s="11"/>
       <c r="P185" s="5"/>
@@ -9757,13 +9763,13 @@
       </c>
       <c r="S185" s="5"/>
     </row>
-    <row r="186" hidden="false" outlineLevel="1">
+    <row r="186" hidden="true" outlineLevel="1">
       <c r="A186" t="s" s="27">
         <v>73</v>
       </c>
       <c r="B186" s="57"/>
       <c r="C186" t="s" s="29">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D186" s="57"/>
       <c r="E186" t="s" s="29">
@@ -9786,18 +9792,18 @@
       </c>
       <c r="S186" s="57"/>
     </row>
-    <row r="187" hidden="false" outlineLevel="2">
+    <row r="187" hidden="true" outlineLevel="2">
       <c r="A187" t="s" s="37">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B187" t="s" s="39">
         <v>75</v>
       </c>
       <c r="C187" t="s" s="39">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D187" t="s" s="39">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E187" t="s" s="39">
         <v>126</v>
@@ -9825,7 +9831,7 @@
       </c>
       <c r="M187" s="11"/>
       <c r="N187" t="s" s="13">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="O187" s="11"/>
       <c r="P187" s="5"/>
@@ -9837,18 +9843,18 @@
       </c>
       <c r="S187" s="5"/>
     </row>
-    <row r="188" hidden="false" outlineLevel="2">
+    <row r="188" hidden="true" outlineLevel="2">
       <c r="A188" t="s" s="37">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B188" t="s" s="39">
         <v>75</v>
       </c>
       <c r="C188" t="s" s="39">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D188" t="s" s="39">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E188" t="s" s="39">
         <v>126</v>
@@ -9876,7 +9882,7 @@
       </c>
       <c r="M188" s="11"/>
       <c r="N188" t="s" s="13">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="O188" s="11"/>
       <c r="P188" s="5"/>
@@ -9888,13 +9894,13 @@
       </c>
       <c r="S188" s="5"/>
     </row>
-    <row r="189" hidden="false" outlineLevel="1">
+    <row r="189" hidden="true" outlineLevel="1">
       <c r="A189" t="s" s="27">
         <v>80</v>
       </c>
       <c r="B189" s="57"/>
       <c r="C189" t="s" s="29">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D189" s="57"/>
       <c r="E189" t="s" s="29">
@@ -9917,18 +9923,18 @@
       </c>
       <c r="S189" s="57"/>
     </row>
-    <row r="190" hidden="false" outlineLevel="2">
+    <row r="190" hidden="true" outlineLevel="2">
       <c r="A190" t="s" s="61">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B190" t="s" s="63">
         <v>82</v>
       </c>
       <c r="C190" t="s" s="63">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D190" t="s" s="63">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E190" t="s" s="63">
         <v>126</v>
@@ -9954,7 +9960,7 @@
       <c r="L190" s="75"/>
       <c r="M190" s="11"/>
       <c r="N190" t="s" s="13">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="O190" t="s" s="11">
         <v>129</v>
@@ -9968,18 +9974,18 @@
       </c>
       <c r="S190" s="5"/>
     </row>
-    <row r="191" hidden="false" outlineLevel="2">
+    <row r="191" hidden="true" outlineLevel="2">
       <c r="A191" t="s" s="61">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B191" t="s" s="63">
         <v>82</v>
       </c>
       <c r="C191" t="s" s="63">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D191" t="s" s="63">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E191" t="s" s="63">
         <v>126</v>
@@ -10005,7 +10011,7 @@
       <c r="L191" s="75"/>
       <c r="M191" s="11"/>
       <c r="N191" t="s" s="13">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="O191" t="s" s="11">
         <v>129</v>
@@ -10019,18 +10025,18 @@
       </c>
       <c r="S191" s="5"/>
     </row>
-    <row r="192" hidden="false" outlineLevel="2">
+    <row r="192" hidden="true" outlineLevel="2">
       <c r="A192" t="s" s="37">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B192" t="s" s="39">
         <v>82</v>
       </c>
       <c r="C192" t="s" s="39">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D192" t="s" s="39">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E192" t="s" s="39">
         <v>126</v>
@@ -10068,13 +10074,13 @@
       </c>
       <c r="S192" s="5"/>
     </row>
-    <row r="193" hidden="false" outlineLevel="1">
+    <row r="193" hidden="true" outlineLevel="1">
       <c r="A193" t="s" s="27">
         <v>87</v>
       </c>
       <c r="B193" s="57"/>
       <c r="C193" t="s" s="29">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D193" s="57"/>
       <c r="E193" t="s" s="29">
@@ -10097,18 +10103,18 @@
       </c>
       <c r="S193" s="57"/>
     </row>
-    <row r="194" hidden="false" outlineLevel="2">
+    <row r="194" hidden="true" outlineLevel="2">
       <c r="A194" t="s" s="61">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B194" t="s" s="63">
         <v>89</v>
       </c>
       <c r="C194" t="s" s="63">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D194" t="s" s="63">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E194" t="s" s="63">
         <v>126</v>
@@ -10134,7 +10140,7 @@
       <c r="L194" s="75"/>
       <c r="M194" s="11"/>
       <c r="N194" t="s" s="13">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="O194" t="s" s="11">
         <v>129</v>
@@ -10148,18 +10154,18 @@
       </c>
       <c r="S194" s="5"/>
     </row>
-    <row r="195" hidden="false" outlineLevel="2">
+    <row r="195" hidden="true" outlineLevel="2">
       <c r="A195" t="s" s="61">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B195" t="s" s="63">
         <v>89</v>
       </c>
       <c r="C195" t="s" s="63">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D195" t="s" s="63">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E195" t="s" s="63">
         <v>126</v>
@@ -10185,7 +10191,7 @@
       <c r="L195" s="75"/>
       <c r="M195" s="11"/>
       <c r="N195" t="s" s="13">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="O195" t="s" s="11">
         <v>129</v>
@@ -10199,13 +10205,13 @@
       </c>
       <c r="S195" s="5"/>
     </row>
-    <row r="196" hidden="false" outlineLevel="1">
+    <row r="196" hidden="true" outlineLevel="1">
       <c r="A196" t="s" s="27">
         <v>94</v>
       </c>
       <c r="B196" s="57"/>
       <c r="C196" t="s" s="29">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D196" s="57"/>
       <c r="E196" t="s" s="29">
@@ -10228,18 +10234,18 @@
       </c>
       <c r="S196" s="57"/>
     </row>
-    <row r="197" hidden="false" outlineLevel="2">
+    <row r="197" hidden="true" outlineLevel="2">
       <c r="A197" t="s" s="61">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B197" t="s" s="63">
         <v>96</v>
       </c>
       <c r="C197" t="s" s="63">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D197" t="s" s="63">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E197" t="s" s="63">
         <v>126</v>
@@ -10265,7 +10271,7 @@
       <c r="L197" s="75"/>
       <c r="M197" s="11"/>
       <c r="N197" t="s" s="13">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="O197" t="s" s="11">
         <v>129</v>
@@ -10279,18 +10285,18 @@
       </c>
       <c r="S197" s="5"/>
     </row>
-    <row r="198" hidden="false" outlineLevel="2">
+    <row r="198" hidden="true" outlineLevel="2">
       <c r="A198" t="s" s="61">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B198" t="s" s="63">
         <v>96</v>
       </c>
       <c r="C198" t="s" s="63">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D198" t="s" s="63">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E198" t="s" s="63">
         <v>126</v>
@@ -10316,7 +10322,7 @@
       <c r="L198" s="75"/>
       <c r="M198" s="11"/>
       <c r="N198" t="s" s="13">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="O198" t="s" s="11">
         <v>129</v>
@@ -10330,13 +10336,13 @@
       </c>
       <c r="S198" s="5"/>
     </row>
-    <row r="199" hidden="false" outlineLevel="1">
+    <row r="199" hidden="true" outlineLevel="1">
       <c r="A199" t="s" s="27">
         <v>101</v>
       </c>
       <c r="B199" s="57"/>
       <c r="C199" t="s" s="29">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D199" s="57"/>
       <c r="E199" t="s" s="29">
@@ -10359,18 +10365,18 @@
       </c>
       <c r="S199" s="57"/>
     </row>
-    <row r="200" hidden="false" outlineLevel="2">
+    <row r="200" hidden="true" outlineLevel="2">
       <c r="A200" t="s" s="61">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B200" t="s" s="63">
         <v>103</v>
       </c>
       <c r="C200" t="s" s="63">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D200" t="s" s="63">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E200" t="s" s="63">
         <v>126</v>
@@ -10396,7 +10402,7 @@
       <c r="L200" s="75"/>
       <c r="M200" s="11"/>
       <c r="N200" t="s" s="13">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="O200" t="s" s="11">
         <v>129</v>
@@ -10410,18 +10416,18 @@
       </c>
       <c r="S200" s="5"/>
     </row>
-    <row r="201" hidden="false" outlineLevel="2">
+    <row r="201" hidden="true" outlineLevel="2">
       <c r="A201" t="s" s="61">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B201" t="s" s="63">
         <v>103</v>
       </c>
       <c r="C201" t="s" s="63">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D201" t="s" s="63">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E201" t="s" s="63">
         <v>126</v>
@@ -10447,7 +10453,7 @@
       <c r="L201" s="75"/>
       <c r="M201" s="11"/>
       <c r="N201" t="s" s="13">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="O201" t="s" s="11">
         <v>129</v>
@@ -10461,13 +10467,13 @@
       </c>
       <c r="S201" s="5"/>
     </row>
-    <row r="202" hidden="false" outlineLevel="1">
+    <row r="202" hidden="true" outlineLevel="1">
       <c r="A202" t="s" s="27">
         <v>108</v>
       </c>
       <c r="B202" s="57"/>
       <c r="C202" t="s" s="29">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D202" s="57"/>
       <c r="E202" t="s" s="29">
@@ -10490,18 +10496,18 @@
       </c>
       <c r="S202" s="57"/>
     </row>
-    <row r="203" hidden="false" outlineLevel="2">
+    <row r="203" hidden="true" outlineLevel="2">
       <c r="A203" t="s" s="61">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B203" t="s" s="63">
         <v>110</v>
       </c>
       <c r="C203" t="s" s="63">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D203" t="s" s="63">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E203" t="s" s="63">
         <v>126</v>
@@ -10527,7 +10533,7 @@
       <c r="L203" s="75"/>
       <c r="M203" s="11"/>
       <c r="N203" t="s" s="13">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="O203" t="s" s="11">
         <v>129</v>
@@ -10541,18 +10547,18 @@
       </c>
       <c r="S203" s="5"/>
     </row>
-    <row r="204" hidden="false" outlineLevel="2">
+    <row r="204" hidden="true" outlineLevel="2">
       <c r="A204" t="s" s="61">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B204" t="s" s="63">
         <v>110</v>
       </c>
       <c r="C204" t="s" s="63">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D204" t="s" s="63">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E204" t="s" s="63">
         <v>126</v>
@@ -10578,7 +10584,7 @@
       <c r="L204" s="75"/>
       <c r="M204" s="11"/>
       <c r="N204" t="s" s="13">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="O204" t="s" s="11">
         <v>129</v>
@@ -10592,13 +10598,13 @@
       </c>
       <c r="S204" s="5"/>
     </row>
-    <row r="205" hidden="false" outlineLevel="1">
+    <row r="205" hidden="true" outlineLevel="1">
       <c r="A205" t="s" s="27">
         <v>115</v>
       </c>
       <c r="B205" s="57"/>
       <c r="C205" t="s" s="29">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D205" s="57"/>
       <c r="E205" t="s" s="29">
@@ -10621,18 +10627,18 @@
       </c>
       <c r="S205" s="57"/>
     </row>
-    <row r="206" hidden="false" outlineLevel="2">
+    <row r="206" hidden="true" outlineLevel="2">
       <c r="A206" t="s" s="61">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B206" t="s" s="63">
         <v>117</v>
       </c>
       <c r="C206" t="s" s="63">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D206" t="s" s="63">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E206" t="s" s="63">
         <v>126</v>
@@ -10658,7 +10664,7 @@
       <c r="L206" s="75"/>
       <c r="M206" s="11"/>
       <c r="N206" t="s" s="13">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="O206" t="s" s="11">
         <v>129</v>
@@ -10672,18 +10678,18 @@
       </c>
       <c r="S206" s="5"/>
     </row>
-    <row r="207" hidden="false" outlineLevel="2">
+    <row r="207" hidden="true" outlineLevel="2">
       <c r="A207" t="s" s="61">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B207" t="s" s="63">
         <v>117</v>
       </c>
       <c r="C207" t="s" s="63">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D207" t="s" s="63">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E207" t="s" s="63">
         <v>126</v>
@@ -10709,7 +10715,7 @@
       <c r="L207" s="75"/>
       <c r="M207" s="11"/>
       <c r="N207" t="s" s="13">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="O207" t="s" s="11">
         <v>129</v>
@@ -10746,7 +10752,7 @@
     </row>
     <row r="209" hidden="false">
       <c r="A209" t="s" s="15">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B209" s="19"/>
       <c r="C209" s="19"/>
@@ -10790,22 +10796,22 @@
     </row>
     <row r="211" hidden="true" outlineLevel="1">
       <c r="A211" t="s" s="79">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B211" t="s" s="63">
         <v>29</v>
       </c>
       <c r="C211" t="s" s="63">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D211" t="n" s="63">
         <v>2.1</v>
       </c>
       <c r="E211" t="s" s="63">
+        <v>207</v>
+      </c>
+      <c r="F211" t="s" s="63">
         <v>208</v>
-      </c>
-      <c r="F211" t="s" s="63">
-        <v>209</v>
       </c>
       <c r="G211" t="n" s="65">
         <v>45957.0</v>
@@ -10825,7 +10831,7 @@
       <c r="L211" s="75"/>
       <c r="M211" s="11"/>
       <c r="N211" t="s" s="13">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="O211" t="s" s="11">
         <v>129</v>
@@ -10841,22 +10847,22 @@
     </row>
     <row r="212" hidden="true" outlineLevel="1">
       <c r="A212" t="s" s="79">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B212" t="s" s="63">
         <v>45</v>
       </c>
       <c r="C212" t="s" s="63">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D212" t="n" s="63">
         <v>1.1</v>
       </c>
       <c r="E212" t="s" s="63">
+        <v>207</v>
+      </c>
+      <c r="F212" t="s" s="63">
         <v>208</v>
-      </c>
-      <c r="F212" t="s" s="63">
-        <v>209</v>
       </c>
       <c r="G212" t="n" s="65">
         <v>46034.0</v>
@@ -10876,7 +10882,7 @@
       <c r="L212" s="75"/>
       <c r="M212" s="33"/>
       <c r="N212" t="s" s="33">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="O212" t="s" s="33">
         <v>129</v>
@@ -10892,22 +10898,22 @@
     </row>
     <row r="213" hidden="true" outlineLevel="1">
       <c r="A213" t="s" s="79">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B213" t="s" s="63">
         <v>52</v>
       </c>
       <c r="C213" t="s" s="63">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D213" t="n" s="63">
         <v>2.2</v>
       </c>
       <c r="E213" t="s" s="63">
+        <v>207</v>
+      </c>
+      <c r="F213" t="s" s="63">
         <v>208</v>
-      </c>
-      <c r="F213" t="s" s="63">
-        <v>209</v>
       </c>
       <c r="G213" t="n" s="65">
         <v>46055.0</v>
@@ -10927,7 +10933,7 @@
       <c r="L213" s="75"/>
       <c r="M213" s="11"/>
       <c r="N213" t="s" s="13">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="O213" t="s" s="11">
         <v>129</v>
@@ -10943,22 +10949,22 @@
     </row>
     <row r="214" hidden="true" outlineLevel="1">
       <c r="A214" t="s" s="79">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B214" t="s" s="63">
         <v>60</v>
       </c>
       <c r="C214" t="s" s="63">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D214" t="n" s="63">
         <v>1.2</v>
       </c>
       <c r="E214" t="s" s="63">
+        <v>207</v>
+      </c>
+      <c r="F214" t="s" s="63">
         <v>208</v>
-      </c>
-      <c r="F214" t="s" s="63">
-        <v>209</v>
       </c>
       <c r="G214" t="n" s="65">
         <v>46076.0</v>
@@ -10978,7 +10984,7 @@
       <c r="L214" s="75"/>
       <c r="M214" s="33"/>
       <c r="N214" t="s" s="33">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="O214" t="s" s="33">
         <v>129</v>
@@ -10994,22 +11000,22 @@
     </row>
     <row r="215" hidden="true" outlineLevel="1">
       <c r="A215" t="s" s="79">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B215" t="s" s="63">
         <v>68</v>
       </c>
       <c r="C215" t="s" s="63">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D215" t="n" s="63">
         <v>2.3</v>
       </c>
       <c r="E215" t="s" s="63">
+        <v>207</v>
+      </c>
+      <c r="F215" t="s" s="63">
         <v>208</v>
-      </c>
-      <c r="F215" t="s" s="63">
-        <v>209</v>
       </c>
       <c r="G215" t="n" s="65">
         <v>46097.0</v>
@@ -11029,7 +11035,7 @@
       <c r="L215" s="75"/>
       <c r="M215" s="11"/>
       <c r="N215" t="s" s="13">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="O215" t="s" s="11">
         <v>129</v>
@@ -11045,22 +11051,22 @@
     </row>
     <row r="216" hidden="true" outlineLevel="1">
       <c r="A216" t="s" s="79">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B216" t="s" s="63">
         <v>75</v>
       </c>
       <c r="C216" t="s" s="63">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D216" t="n" s="63">
         <v>1.3</v>
       </c>
       <c r="E216" t="s" s="63">
+        <v>207</v>
+      </c>
+      <c r="F216" t="s" s="63">
         <v>208</v>
-      </c>
-      <c r="F216" t="s" s="63">
-        <v>209</v>
       </c>
       <c r="G216" t="n" s="65">
         <v>46118.0</v>
@@ -11080,7 +11086,7 @@
       <c r="L216" s="75"/>
       <c r="M216" s="33"/>
       <c r="N216" t="s" s="33">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="O216" t="s" s="33">
         <v>129</v>
@@ -11096,22 +11102,22 @@
     </row>
     <row r="217" hidden="true" outlineLevel="1">
       <c r="A217" t="s" s="79">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B217" t="s" s="63">
         <v>82</v>
       </c>
       <c r="C217" t="s" s="63">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D217" t="n" s="63">
         <v>2.4</v>
       </c>
       <c r="E217" t="s" s="63">
+        <v>207</v>
+      </c>
+      <c r="F217" t="s" s="63">
         <v>208</v>
-      </c>
-      <c r="F217" t="s" s="63">
-        <v>209</v>
       </c>
       <c r="G217" t="n" s="65">
         <v>46139.0</v>
@@ -11131,7 +11137,7 @@
       <c r="L217" s="75"/>
       <c r="M217" s="11"/>
       <c r="N217" t="s" s="13">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="O217" t="s" s="11">
         <v>129</v>
@@ -11147,22 +11153,22 @@
     </row>
     <row r="218" hidden="true" outlineLevel="1">
       <c r="A218" t="s" s="79">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B218" t="s" s="63">
         <v>89</v>
       </c>
       <c r="C218" t="s" s="63">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D218" t="n" s="63">
         <v>1.4</v>
       </c>
       <c r="E218" t="s" s="63">
+        <v>207</v>
+      </c>
+      <c r="F218" t="s" s="63">
         <v>208</v>
-      </c>
-      <c r="F218" t="s" s="63">
-        <v>209</v>
       </c>
       <c r="G218" t="n" s="65">
         <v>46160.0</v>
@@ -11182,7 +11188,7 @@
       <c r="L218" s="75"/>
       <c r="M218" s="33"/>
       <c r="N218" t="s" s="33">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="O218" t="s" s="33">
         <v>129</v>
@@ -11198,22 +11204,22 @@
     </row>
     <row r="219" hidden="true" outlineLevel="1">
       <c r="A219" t="s" s="79">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B219" t="s" s="63">
         <v>96</v>
       </c>
       <c r="C219" t="s" s="63">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D219" t="n" s="63">
         <v>2.5</v>
       </c>
       <c r="E219" t="s" s="63">
+        <v>207</v>
+      </c>
+      <c r="F219" t="s" s="63">
         <v>208</v>
-      </c>
-      <c r="F219" t="s" s="63">
-        <v>209</v>
       </c>
       <c r="G219" t="n" s="65">
         <v>46181.0</v>
@@ -11233,7 +11239,7 @@
       <c r="L219" s="75"/>
       <c r="M219" s="11"/>
       <c r="N219" t="s" s="13">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="O219" t="s" s="11">
         <v>129</v>
@@ -11249,22 +11255,22 @@
     </row>
     <row r="220" hidden="true" outlineLevel="1">
       <c r="A220" t="s" s="79">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B220" t="s" s="63">
         <v>103</v>
       </c>
       <c r="C220" t="s" s="63">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D220" t="n" s="63">
         <v>1.5</v>
       </c>
       <c r="E220" t="s" s="63">
+        <v>207</v>
+      </c>
+      <c r="F220" t="s" s="63">
         <v>208</v>
-      </c>
-      <c r="F220" t="s" s="63">
-        <v>209</v>
       </c>
       <c r="G220" t="n" s="65">
         <v>46202.0</v>
@@ -11284,7 +11290,7 @@
       <c r="L220" s="75"/>
       <c r="M220" s="33"/>
       <c r="N220" t="s" s="33">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="O220" t="s" s="33">
         <v>129</v>
@@ -11300,22 +11306,22 @@
     </row>
     <row r="221" hidden="true" outlineLevel="1">
       <c r="A221" t="s" s="79">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B221" t="s" s="63">
         <v>110</v>
       </c>
       <c r="C221" t="s" s="63">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D221" t="n" s="63">
         <v>2.6</v>
       </c>
       <c r="E221" t="s" s="63">
+        <v>207</v>
+      </c>
+      <c r="F221" t="s" s="63">
         <v>208</v>
-      </c>
-      <c r="F221" t="s" s="63">
-        <v>209</v>
       </c>
       <c r="G221" t="n" s="65">
         <v>46223.0</v>
@@ -11335,7 +11341,7 @@
       <c r="L221" s="75"/>
       <c r="M221" s="11"/>
       <c r="N221" t="s" s="13">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="O221" t="s" s="11">
         <v>129</v>
@@ -11351,22 +11357,22 @@
     </row>
     <row r="222" hidden="true" outlineLevel="1">
       <c r="A222" t="s" s="79">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B222" t="s" s="63">
         <v>117</v>
       </c>
       <c r="C222" t="s" s="63">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D222" t="n" s="63">
         <v>1.6</v>
       </c>
       <c r="E222" t="s" s="63">
+        <v>207</v>
+      </c>
+      <c r="F222" t="s" s="63">
         <v>208</v>
-      </c>
-      <c r="F222" t="s" s="63">
-        <v>209</v>
       </c>
       <c r="G222" t="n" s="65">
         <v>46244.0</v>
@@ -11386,7 +11392,7 @@
       <c r="L222" s="75"/>
       <c r="M222" s="33"/>
       <c r="N222" t="s" s="33">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="O222" t="s" s="33">
         <v>129</v>
@@ -11423,7 +11429,7 @@
     </row>
     <row r="224" hidden="false">
       <c r="A224" t="s" s="15">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B224" s="19"/>
       <c r="C224" s="19"/>
@@ -11467,22 +11473,22 @@
     </row>
     <row r="226" hidden="false" outlineLevel="1">
       <c r="A226" t="s" s="101">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B226" t="s" s="39">
         <v>29</v>
       </c>
       <c r="C226" t="s" s="39">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D226" t="n" s="39">
         <v>2.1</v>
       </c>
       <c r="E226" t="s" s="39">
+        <v>234</v>
+      </c>
+      <c r="F226" t="s" s="39">
         <v>235</v>
-      </c>
-      <c r="F226" t="s" s="39">
-        <v>236</v>
       </c>
       <c r="G226" t="n" s="41">
         <v>45971.0</v>
@@ -11504,7 +11510,7 @@
       </c>
       <c r="M226" s="11"/>
       <c r="N226" t="s" s="13">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="O226" t="s" s="11">
         <v>33</v>
@@ -11519,46 +11525,46 @@
       <c r="S226" s="5"/>
     </row>
     <row r="227" hidden="false" outlineLevel="1">
-      <c r="A227" t="s" s="27">
-        <v>238</v>
-      </c>
-      <c r="B227" t="s" s="29">
+      <c r="A227" t="s" s="79">
+        <v>237</v>
+      </c>
+      <c r="B227" t="s" s="63">
         <v>45</v>
       </c>
-      <c r="C227" t="s" s="29">
-        <v>233</v>
-      </c>
-      <c r="D227" t="n" s="29">
+      <c r="C227" t="s" s="63">
+        <v>232</v>
+      </c>
+      <c r="D227" t="n" s="63">
         <v>1.1</v>
       </c>
-      <c r="E227" t="s" s="5">
+      <c r="E227" t="s" s="63">
+        <v>234</v>
+      </c>
+      <c r="F227" t="s" s="63">
         <v>235</v>
       </c>
-      <c r="F227" t="s" s="29">
-        <v>236</v>
-      </c>
-      <c r="G227" t="n" s="103">
+      <c r="G227" t="n" s="65">
         <v>46048.0</v>
       </c>
       <c r="H227" t="n" s="35">
-        <v>45946.0</v>
-      </c>
-      <c r="I227" t="n" s="35">
+        <v>46001.0</v>
+      </c>
+      <c r="I227" t="n" s="67">
         <v>45950.0</v>
       </c>
-      <c r="J227" t="n" s="35">
-        <v>46048.0</v>
-      </c>
-      <c r="K227" t="n" s="29">
-        <v>0.0</v>
-      </c>
-      <c r="L227" s="33"/>
+      <c r="J227" t="n" s="67">
+        <v>46001.0</v>
+      </c>
+      <c r="K227" t="n" s="63">
+        <v>47.0</v>
+      </c>
+      <c r="L227" s="75"/>
       <c r="M227" s="33"/>
       <c r="N227" t="s" s="33">
+        <v>238</v>
+      </c>
+      <c r="O227" t="s" s="33">
         <v>239</v>
-      </c>
-      <c r="O227" t="s" s="33">
-        <v>33</v>
       </c>
       <c r="P227" s="29"/>
       <c r="Q227" t="n" s="29">
@@ -11570,46 +11576,46 @@
       <c r="S227" s="29"/>
     </row>
     <row r="228" hidden="false" outlineLevel="1">
-      <c r="A228" t="s" s="25">
+      <c r="A228" t="s" s="79">
         <v>240</v>
       </c>
-      <c r="B228" t="s" s="5">
+      <c r="B228" t="s" s="63">
         <v>52</v>
       </c>
-      <c r="C228" t="s" s="5">
-        <v>233</v>
-      </c>
-      <c r="D228" t="n" s="5">
+      <c r="C228" t="s" s="63">
+        <v>232</v>
+      </c>
+      <c r="D228" t="n" s="63">
         <v>2.2</v>
       </c>
-      <c r="E228" t="s" s="5">
+      <c r="E228" t="s" s="63">
+        <v>234</v>
+      </c>
+      <c r="F228" t="s" s="63">
         <v>235</v>
       </c>
-      <c r="F228" t="s" s="5">
-        <v>236</v>
-      </c>
-      <c r="G228" t="n" s="53">
+      <c r="G228" t="n" s="65">
         <v>46069.0</v>
       </c>
       <c r="H228" t="n" s="43">
+        <v>46006.0</v>
+      </c>
+      <c r="I228" t="n" s="67">
         <v>45967.0</v>
       </c>
-      <c r="I228" t="n" s="43">
-        <v>45967.0</v>
-      </c>
-      <c r="J228" t="n" s="105">
-        <v>46069.0</v>
-      </c>
-      <c r="K228" t="n" s="5">
-        <v>0.0</v>
-      </c>
-      <c r="L228" s="11"/>
+      <c r="J228" t="n" s="103">
+        <v>46006.0</v>
+      </c>
+      <c r="K228" t="n" s="63">
+        <v>63.0</v>
+      </c>
+      <c r="L228" s="75"/>
       <c r="M228" s="11"/>
       <c r="N228" t="s" s="13">
-        <v>241</v>
-      </c>
-      <c r="O228" t="s" s="11">
-        <v>33</v>
+        <v>238</v>
+      </c>
+      <c r="O228" t="s" s="13">
+        <v>239</v>
       </c>
       <c r="P228" s="5"/>
       <c r="Q228" t="n" s="5">
@@ -11621,46 +11627,46 @@
       <c r="S228" s="5"/>
     </row>
     <row r="229" hidden="false" outlineLevel="1">
-      <c r="A229" t="s" s="27">
-        <v>242</v>
-      </c>
-      <c r="B229" t="s" s="29">
+      <c r="A229" t="s" s="79">
+        <v>241</v>
+      </c>
+      <c r="B229" t="s" s="63">
         <v>60</v>
       </c>
-      <c r="C229" t="s" s="29">
-        <v>233</v>
-      </c>
-      <c r="D229" t="n" s="29">
+      <c r="C229" t="s" s="63">
+        <v>232</v>
+      </c>
+      <c r="D229" t="n" s="63">
         <v>1.2</v>
       </c>
-      <c r="E229" t="s" s="5">
+      <c r="E229" t="s" s="63">
+        <v>234</v>
+      </c>
+      <c r="F229" t="s" s="63">
         <v>235</v>
       </c>
-      <c r="F229" t="s" s="29">
-        <v>236</v>
-      </c>
-      <c r="G229" t="n" s="103">
+      <c r="G229" t="n" s="65">
         <v>46090.0</v>
       </c>
       <c r="H229" t="n" s="35">
+        <v>46027.0</v>
+      </c>
+      <c r="I229" t="n" s="67">
         <v>45988.0</v>
       </c>
-      <c r="I229" t="n" s="35">
-        <v>45988.0</v>
-      </c>
-      <c r="J229" t="n" s="107">
-        <v>46090.0</v>
-      </c>
-      <c r="K229" t="n" s="29">
-        <v>0.0</v>
-      </c>
-      <c r="L229" s="33"/>
+      <c r="J229" t="n" s="103">
+        <v>46027.0</v>
+      </c>
+      <c r="K229" t="n" s="63">
+        <v>63.0</v>
+      </c>
+      <c r="L229" s="75"/>
       <c r="M229" s="33"/>
       <c r="N229" t="s" s="33">
+        <v>238</v>
+      </c>
+      <c r="O229" t="s" s="33">
         <v>239</v>
-      </c>
-      <c r="O229" t="s" s="33">
-        <v>33</v>
       </c>
       <c r="P229" s="29"/>
       <c r="Q229" t="n" s="29">
@@ -11672,46 +11678,46 @@
       <c r="S229" s="29"/>
     </row>
     <row r="230" hidden="false" outlineLevel="1">
-      <c r="A230" t="s" s="25">
-        <v>243</v>
-      </c>
-      <c r="B230" t="s" s="5">
+      <c r="A230" t="s" s="79">
+        <v>242</v>
+      </c>
+      <c r="B230" t="s" s="63">
         <v>68</v>
       </c>
-      <c r="C230" t="s" s="5">
-        <v>233</v>
-      </c>
-      <c r="D230" t="n" s="5">
+      <c r="C230" t="s" s="63">
+        <v>232</v>
+      </c>
+      <c r="D230" t="n" s="63">
         <v>2.3</v>
       </c>
-      <c r="E230" t="s" s="5">
+      <c r="E230" t="s" s="63">
+        <v>234</v>
+      </c>
+      <c r="F230" t="s" s="63">
         <v>235</v>
       </c>
-      <c r="F230" t="s" s="5">
-        <v>236</v>
-      </c>
-      <c r="G230" t="n" s="53">
+      <c r="G230" t="n" s="65">
         <v>46111.0</v>
       </c>
       <c r="H230" t="n" s="43">
+        <v>46048.0</v>
+      </c>
+      <c r="I230" t="n" s="67">
         <v>46009.0</v>
       </c>
-      <c r="I230" t="n" s="43">
-        <v>46009.0</v>
-      </c>
-      <c r="J230" t="n" s="105">
-        <v>46111.0</v>
-      </c>
-      <c r="K230" t="n" s="5">
-        <v>0.0</v>
-      </c>
-      <c r="L230" s="11"/>
+      <c r="J230" t="n" s="103">
+        <v>46048.0</v>
+      </c>
+      <c r="K230" t="n" s="63">
+        <v>63.0</v>
+      </c>
+      <c r="L230" s="75"/>
       <c r="M230" s="11"/>
       <c r="N230" t="s" s="13">
-        <v>241</v>
-      </c>
-      <c r="O230" t="s" s="11">
-        <v>33</v>
+        <v>238</v>
+      </c>
+      <c r="O230" t="s" s="13">
+        <v>239</v>
       </c>
       <c r="P230" s="5"/>
       <c r="Q230" t="n" s="5">
@@ -11724,45 +11730,45 @@
     </row>
     <row r="231" hidden="false" outlineLevel="1">
       <c r="A231" t="s" s="79">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B231" t="s" s="63">
         <v>75</v>
       </c>
       <c r="C231" t="s" s="63">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D231" t="n" s="63">
         <v>1.3</v>
       </c>
       <c r="E231" t="s" s="63">
+        <v>234</v>
+      </c>
+      <c r="F231" t="s" s="63">
         <v>235</v>
-      </c>
-      <c r="F231" t="s" s="63">
-        <v>236</v>
       </c>
       <c r="G231" t="n" s="65">
         <v>46132.0</v>
       </c>
       <c r="H231" t="n" s="35">
-        <v>46013.0</v>
+        <v>46069.0</v>
       </c>
       <c r="I231" t="n" s="67">
         <v>46013.0</v>
       </c>
-      <c r="J231" t="n" s="109">
-        <v>46013.0</v>
+      <c r="J231" t="n" s="103">
+        <v>46069.0</v>
       </c>
       <c r="K231" t="n" s="63">
-        <v>119.0</v>
+        <v>63.0</v>
       </c>
       <c r="L231" s="75"/>
       <c r="M231" s="33"/>
       <c r="N231" t="s" s="33">
+        <v>238</v>
+      </c>
+      <c r="O231" t="s" s="33">
         <v>239</v>
-      </c>
-      <c r="O231" t="s" s="33">
-        <v>33</v>
       </c>
       <c r="P231" s="29"/>
       <c r="Q231" t="n" s="29">
@@ -11774,46 +11780,46 @@
       <c r="S231" s="29"/>
     </row>
     <row r="232" hidden="false" outlineLevel="1">
-      <c r="A232" t="s" s="25">
-        <v>245</v>
-      </c>
-      <c r="B232" t="s" s="5">
+      <c r="A232" t="s" s="79">
+        <v>244</v>
+      </c>
+      <c r="B232" t="s" s="63">
         <v>82</v>
       </c>
-      <c r="C232" t="s" s="5">
-        <v>233</v>
-      </c>
-      <c r="D232" t="n" s="5">
+      <c r="C232" t="s" s="63">
+        <v>232</v>
+      </c>
+      <c r="D232" t="n" s="63">
         <v>2.4</v>
       </c>
-      <c r="E232" t="s" s="5">
+      <c r="E232" t="s" s="63">
+        <v>234</v>
+      </c>
+      <c r="F232" t="s" s="63">
         <v>235</v>
       </c>
-      <c r="F232" t="s" s="5">
-        <v>236</v>
-      </c>
-      <c r="G232" t="n" s="53">
+      <c r="G232" t="n" s="65">
         <v>46153.0</v>
       </c>
       <c r="H232" t="n" s="43">
+        <v>46090.0</v>
+      </c>
+      <c r="I232" t="n" s="67">
         <v>46065.0</v>
       </c>
-      <c r="I232" t="n" s="43">
-        <v>46065.0</v>
-      </c>
-      <c r="J232" t="n" s="105">
-        <v>46153.0</v>
-      </c>
-      <c r="K232" t="n" s="5">
-        <v>0.0</v>
-      </c>
-      <c r="L232" s="11"/>
+      <c r="J232" t="n" s="103">
+        <v>46090.0</v>
+      </c>
+      <c r="K232" t="n" s="63">
+        <v>63.0</v>
+      </c>
+      <c r="L232" s="75"/>
       <c r="M232" s="11"/>
       <c r="N232" t="s" s="13">
-        <v>241</v>
-      </c>
-      <c r="O232" t="s" s="11">
-        <v>33</v>
+        <v>238</v>
+      </c>
+      <c r="O232" t="s" s="13">
+        <v>239</v>
       </c>
       <c r="P232" s="5"/>
       <c r="Q232" t="n" s="5">
@@ -11825,46 +11831,46 @@
       <c r="S232" s="5"/>
     </row>
     <row r="233" hidden="false" outlineLevel="1">
-      <c r="A233" t="s" s="27">
-        <v>246</v>
-      </c>
-      <c r="B233" t="s" s="29">
+      <c r="A233" t="s" s="79">
+        <v>245</v>
+      </c>
+      <c r="B233" t="s" s="63">
         <v>89</v>
       </c>
-      <c r="C233" t="s" s="29">
-        <v>233</v>
-      </c>
-      <c r="D233" t="n" s="29">
+      <c r="C233" t="s" s="63">
+        <v>232</v>
+      </c>
+      <c r="D233" t="n" s="63">
         <v>1.4</v>
       </c>
-      <c r="E233" t="s" s="5">
+      <c r="E233" t="s" s="63">
+        <v>234</v>
+      </c>
+      <c r="F233" t="s" s="63">
         <v>235</v>
       </c>
-      <c r="F233" t="s" s="29">
-        <v>236</v>
-      </c>
-      <c r="G233" t="n" s="103">
+      <c r="G233" t="n" s="65">
         <v>46174.0</v>
       </c>
       <c r="H233" t="n" s="35">
+        <v>46111.0</v>
+      </c>
+      <c r="I233" t="n" s="67">
         <v>46086.0</v>
       </c>
-      <c r="I233" t="n" s="35">
-        <v>46086.0</v>
-      </c>
-      <c r="J233" t="n" s="107">
-        <v>46174.0</v>
-      </c>
-      <c r="K233" t="n" s="29">
-        <v>0.0</v>
-      </c>
-      <c r="L233" s="33"/>
+      <c r="J233" t="n" s="103">
+        <v>46111.0</v>
+      </c>
+      <c r="K233" t="n" s="63">
+        <v>63.0</v>
+      </c>
+      <c r="L233" s="75"/>
       <c r="M233" s="33"/>
       <c r="N233" t="s" s="33">
+        <v>238</v>
+      </c>
+      <c r="O233" t="s" s="33">
         <v>239</v>
-      </c>
-      <c r="O233" t="s" s="33">
-        <v>33</v>
       </c>
       <c r="P233" s="29"/>
       <c r="Q233" t="n" s="29">
@@ -11877,45 +11883,45 @@
     </row>
     <row r="234" hidden="false" outlineLevel="1">
       <c r="A234" t="s" s="79">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B234" t="s" s="63">
         <v>96</v>
       </c>
       <c r="C234" t="s" s="63">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D234" t="n" s="63">
         <v>2.5</v>
       </c>
       <c r="E234" t="s" s="63">
+        <v>234</v>
+      </c>
+      <c r="F234" t="s" s="63">
         <v>235</v>
-      </c>
-      <c r="F234" t="s" s="63">
-        <v>236</v>
       </c>
       <c r="G234" t="n" s="65">
         <v>46195.0</v>
       </c>
       <c r="H234" t="n" s="43">
-        <v>46107.0</v>
+        <v>46132.0</v>
       </c>
       <c r="I234" t="n" s="67">
         <v>46107.0</v>
       </c>
-      <c r="J234" t="n" s="109">
-        <v>46174.0</v>
+      <c r="J234" t="n" s="103">
+        <v>46132.0</v>
       </c>
       <c r="K234" t="n" s="63">
-        <v>21.0</v>
+        <v>63.0</v>
       </c>
       <c r="L234" s="75"/>
       <c r="M234" s="11"/>
       <c r="N234" t="s" s="13">
-        <v>241</v>
-      </c>
-      <c r="O234" t="s" s="11">
-        <v>33</v>
+        <v>238</v>
+      </c>
+      <c r="O234" t="s" s="13">
+        <v>239</v>
       </c>
       <c r="P234" s="5"/>
       <c r="Q234" t="n" s="5">
@@ -11927,46 +11933,46 @@
       <c r="S234" s="5"/>
     </row>
     <row r="235" hidden="false" outlineLevel="1">
-      <c r="A235" t="s" s="27">
-        <v>248</v>
-      </c>
-      <c r="B235" t="s" s="29">
+      <c r="A235" t="s" s="79">
+        <v>247</v>
+      </c>
+      <c r="B235" t="s" s="63">
         <v>103</v>
       </c>
-      <c r="C235" t="s" s="29">
-        <v>233</v>
-      </c>
-      <c r="D235" t="n" s="29">
+      <c r="C235" t="s" s="63">
+        <v>232</v>
+      </c>
+      <c r="D235" t="n" s="63">
         <v>1.5</v>
       </c>
-      <c r="E235" t="s" s="5">
+      <c r="E235" t="s" s="63">
+        <v>234</v>
+      </c>
+      <c r="F235" t="s" s="63">
         <v>235</v>
       </c>
-      <c r="F235" t="s" s="29">
-        <v>236</v>
-      </c>
-      <c r="G235" t="n" s="103">
+      <c r="G235" t="n" s="65">
         <v>46216.0</v>
       </c>
       <c r="H235" t="n" s="35">
+        <v>46153.0</v>
+      </c>
+      <c r="I235" t="n" s="67">
         <v>46127.0</v>
       </c>
-      <c r="I235" t="n" s="35">
-        <v>46127.0</v>
-      </c>
-      <c r="J235" t="n" s="107">
-        <v>46216.0</v>
-      </c>
-      <c r="K235" t="n" s="29">
-        <v>0.0</v>
-      </c>
-      <c r="L235" s="33"/>
+      <c r="J235" t="n" s="103">
+        <v>46153.0</v>
+      </c>
+      <c r="K235" t="n" s="63">
+        <v>63.0</v>
+      </c>
+      <c r="L235" s="75"/>
       <c r="M235" s="33"/>
       <c r="N235" t="s" s="33">
+        <v>238</v>
+      </c>
+      <c r="O235" t="s" s="33">
         <v>239</v>
-      </c>
-      <c r="O235" t="s" s="33">
-        <v>33</v>
       </c>
       <c r="P235" s="29"/>
       <c r="Q235" t="n" s="29">
@@ -11978,46 +11984,46 @@
       <c r="S235" s="29"/>
     </row>
     <row r="236" hidden="false" outlineLevel="1">
-      <c r="A236" t="s" s="25">
-        <v>249</v>
-      </c>
-      <c r="B236" t="s" s="5">
+      <c r="A236" t="s" s="79">
+        <v>248</v>
+      </c>
+      <c r="B236" t="s" s="63">
         <v>110</v>
       </c>
-      <c r="C236" t="s" s="5">
-        <v>233</v>
-      </c>
-      <c r="D236" t="n" s="5">
+      <c r="C236" t="s" s="63">
+        <v>232</v>
+      </c>
+      <c r="D236" t="n" s="63">
         <v>2.6</v>
       </c>
-      <c r="E236" t="s" s="5">
+      <c r="E236" t="s" s="63">
+        <v>234</v>
+      </c>
+      <c r="F236" t="s" s="63">
         <v>235</v>
       </c>
-      <c r="F236" t="s" s="5">
-        <v>236</v>
-      </c>
-      <c r="G236" t="n" s="53">
+      <c r="G236" t="n" s="65">
         <v>46237.0</v>
       </c>
       <c r="H236" t="n" s="43">
+        <v>46174.0</v>
+      </c>
+      <c r="I236" t="n" s="67">
         <v>46148.0</v>
       </c>
-      <c r="I236" t="n" s="43">
-        <v>46148.0</v>
-      </c>
-      <c r="J236" t="n" s="105">
-        <v>46237.0</v>
-      </c>
-      <c r="K236" t="n" s="5">
-        <v>0.0</v>
-      </c>
-      <c r="L236" s="11"/>
+      <c r="J236" t="n" s="103">
+        <v>46174.0</v>
+      </c>
+      <c r="K236" t="n" s="63">
+        <v>63.0</v>
+      </c>
+      <c r="L236" s="75"/>
       <c r="M236" s="11"/>
       <c r="N236" t="s" s="13">
-        <v>241</v>
-      </c>
-      <c r="O236" t="s" s="11">
-        <v>33</v>
+        <v>238</v>
+      </c>
+      <c r="O236" t="s" s="13">
+        <v>239</v>
       </c>
       <c r="P236" s="5"/>
       <c r="Q236" t="n" s="5">
@@ -12029,46 +12035,46 @@
       <c r="S236" s="5"/>
     </row>
     <row r="237" hidden="false" outlineLevel="1">
-      <c r="A237" t="s" s="27">
-        <v>250</v>
-      </c>
-      <c r="B237" t="s" s="29">
+      <c r="A237" t="s" s="79">
+        <v>249</v>
+      </c>
+      <c r="B237" t="s" s="63">
         <v>117</v>
       </c>
-      <c r="C237" t="s" s="29">
-        <v>233</v>
-      </c>
-      <c r="D237" t="n" s="29">
+      <c r="C237" t="s" s="63">
+        <v>232</v>
+      </c>
+      <c r="D237" t="n" s="63">
         <v>1.6</v>
       </c>
-      <c r="E237" t="s" s="5">
+      <c r="E237" t="s" s="63">
+        <v>234</v>
+      </c>
+      <c r="F237" t="s" s="63">
         <v>235</v>
       </c>
-      <c r="F237" t="s" s="29">
-        <v>236</v>
-      </c>
-      <c r="G237" t="n" s="103">
+      <c r="G237" t="n" s="65">
         <v>46258.0</v>
       </c>
       <c r="H237" t="n" s="35">
+        <v>46195.0</v>
+      </c>
+      <c r="I237" t="n" s="67">
         <v>46169.0</v>
       </c>
-      <c r="I237" t="n" s="35">
-        <v>46169.0</v>
-      </c>
-      <c r="J237" t="n" s="107">
-        <v>46258.0</v>
-      </c>
-      <c r="K237" t="n" s="29">
-        <v>0.0</v>
-      </c>
-      <c r="L237" s="33"/>
+      <c r="J237" t="n" s="103">
+        <v>46195.0</v>
+      </c>
+      <c r="K237" t="n" s="63">
+        <v>63.0</v>
+      </c>
+      <c r="L237" s="75"/>
       <c r="M237" s="33"/>
       <c r="N237" t="s" s="33">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="O237" t="s" s="33">
-        <v>33</v>
+        <v>239</v>
       </c>
       <c r="P237" s="29"/>
       <c r="Q237" t="n" s="29">
@@ -12102,7 +12108,7 @@
     </row>
     <row r="239" hidden="false">
       <c r="A239" t="s" s="15">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B239" s="19"/>
       <c r="C239" s="19"/>
@@ -12146,22 +12152,22 @@
     </row>
     <row r="241" hidden="true" outlineLevel="1">
       <c r="A241" t="s" s="101">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B241" t="s" s="39">
         <v>29</v>
       </c>
       <c r="C241" t="s" s="39">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D241" t="s" s="39">
         <v>40</v>
       </c>
       <c r="E241" t="s" s="39">
+        <v>253</v>
+      </c>
+      <c r="F241" t="s" s="39">
         <v>254</v>
-      </c>
-      <c r="F241" t="s" s="39">
-        <v>255</v>
       </c>
       <c r="G241" t="n" s="41">
         <v>45964.0</v>
@@ -12183,7 +12189,7 @@
       </c>
       <c r="M241" s="11"/>
       <c r="N241" t="s" s="13">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="O241" t="s" s="13">
         <v>33</v>
@@ -12199,22 +12205,22 @@
     </row>
     <row r="242" hidden="true" outlineLevel="1">
       <c r="A242" t="s" s="101">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B242" t="s" s="39">
         <v>45</v>
       </c>
       <c r="C242" t="s" s="39">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D242" t="s" s="39">
         <v>40</v>
       </c>
       <c r="E242" t="s" s="39">
+        <v>253</v>
+      </c>
+      <c r="F242" t="s" s="39">
         <v>254</v>
-      </c>
-      <c r="F242" t="s" s="39">
-        <v>255</v>
       </c>
       <c r="G242" t="n" s="41">
         <v>46041.0</v>
@@ -12236,7 +12242,7 @@
       </c>
       <c r="M242" s="11"/>
       <c r="N242" t="s" s="13">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="O242" t="s" s="13">
         <v>33</v>
@@ -12252,22 +12258,22 @@
     </row>
     <row r="243" hidden="true" outlineLevel="1">
       <c r="A243" t="s" s="101">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B243" t="s" s="39">
         <v>52</v>
       </c>
       <c r="C243" t="s" s="39">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D243" t="s" s="39">
         <v>40</v>
       </c>
       <c r="E243" t="s" s="39">
+        <v>253</v>
+      </c>
+      <c r="F243" t="s" s="39">
         <v>254</v>
-      </c>
-      <c r="F243" t="s" s="39">
-        <v>255</v>
       </c>
       <c r="G243" t="n" s="41">
         <v>46062.0</v>
@@ -12289,7 +12295,7 @@
       </c>
       <c r="M243" s="11"/>
       <c r="N243" t="s" s="11">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="O243" t="s" s="11">
         <v>33</v>
@@ -12305,22 +12311,22 @@
     </row>
     <row r="244" hidden="true" outlineLevel="1">
       <c r="A244" t="s" s="101">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B244" t="s" s="39">
         <v>60</v>
       </c>
       <c r="C244" t="s" s="39">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D244" t="s" s="39">
         <v>40</v>
       </c>
       <c r="E244" t="s" s="39">
+        <v>253</v>
+      </c>
+      <c r="F244" t="s" s="39">
         <v>254</v>
-      </c>
-      <c r="F244" t="s" s="39">
-        <v>255</v>
       </c>
       <c r="G244" t="n" s="41">
         <v>46083.0</v>
@@ -12342,7 +12348,7 @@
       </c>
       <c r="M244" s="33"/>
       <c r="N244" t="s" s="33">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="O244" t="s" s="33">
         <v>33</v>
@@ -12358,22 +12364,22 @@
     </row>
     <row r="245" hidden="true" outlineLevel="1">
       <c r="A245" t="s" s="101">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B245" t="s" s="39">
         <v>68</v>
       </c>
       <c r="C245" t="s" s="39">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D245" t="s" s="39">
         <v>40</v>
       </c>
       <c r="E245" t="s" s="39">
+        <v>253</v>
+      </c>
+      <c r="F245" t="s" s="39">
         <v>254</v>
-      </c>
-      <c r="F245" t="s" s="39">
-        <v>255</v>
       </c>
       <c r="G245" t="n" s="41">
         <v>46104.0</v>
@@ -12395,7 +12401,7 @@
       </c>
       <c r="M245" s="11"/>
       <c r="N245" t="s" s="11">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="O245" t="s" s="11">
         <v>33</v>
@@ -12411,22 +12417,22 @@
     </row>
     <row r="246" hidden="true" outlineLevel="1">
       <c r="A246" t="s" s="101">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B246" t="s" s="39">
         <v>75</v>
       </c>
       <c r="C246" t="s" s="39">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D246" t="s" s="39">
         <v>40</v>
       </c>
       <c r="E246" t="s" s="39">
+        <v>253</v>
+      </c>
+      <c r="F246" t="s" s="39">
         <v>254</v>
-      </c>
-      <c r="F246" t="s" s="39">
-        <v>255</v>
       </c>
       <c r="G246" t="n" s="41">
         <v>46125.0</v>
@@ -12448,7 +12454,7 @@
       </c>
       <c r="M246" s="33"/>
       <c r="N246" t="s" s="33">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="O246" t="s" s="33">
         <v>33</v>
@@ -12464,22 +12470,22 @@
     </row>
     <row r="247" hidden="true" outlineLevel="1">
       <c r="A247" t="s" s="101">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B247" t="s" s="39">
         <v>82</v>
       </c>
       <c r="C247" t="s" s="39">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D247" t="s" s="39">
         <v>40</v>
       </c>
       <c r="E247" t="s" s="39">
+        <v>253</v>
+      </c>
+      <c r="F247" t="s" s="39">
         <v>254</v>
-      </c>
-      <c r="F247" t="s" s="39">
-        <v>255</v>
       </c>
       <c r="G247" t="n" s="41">
         <v>46146.0</v>
@@ -12501,7 +12507,7 @@
       </c>
       <c r="M247" s="11"/>
       <c r="N247" t="s" s="11">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="O247" t="s" s="11">
         <v>33</v>
@@ -12517,22 +12523,22 @@
     </row>
     <row r="248" hidden="true" outlineLevel="1">
       <c r="A248" t="s" s="101">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B248" t="s" s="39">
         <v>89</v>
       </c>
       <c r="C248" t="s" s="39">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D248" t="s" s="39">
         <v>40</v>
       </c>
       <c r="E248" t="s" s="39">
+        <v>253</v>
+      </c>
+      <c r="F248" t="s" s="39">
         <v>254</v>
-      </c>
-      <c r="F248" t="s" s="39">
-        <v>255</v>
       </c>
       <c r="G248" t="n" s="41">
         <v>46167.0</v>
@@ -12554,7 +12560,7 @@
       </c>
       <c r="M248" s="33"/>
       <c r="N248" t="s" s="33">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="O248" t="s" s="33">
         <v>33</v>
@@ -12570,22 +12576,22 @@
     </row>
     <row r="249" hidden="true" outlineLevel="1">
       <c r="A249" t="s" s="101">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B249" t="s" s="39">
         <v>96</v>
       </c>
       <c r="C249" t="s" s="39">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D249" t="s" s="39">
         <v>40</v>
       </c>
       <c r="E249" t="s" s="39">
+        <v>253</v>
+      </c>
+      <c r="F249" t="s" s="39">
         <v>254</v>
-      </c>
-      <c r="F249" t="s" s="39">
-        <v>255</v>
       </c>
       <c r="G249" t="n" s="41">
         <v>46188.0</v>
@@ -12607,7 +12613,7 @@
       </c>
       <c r="M249" s="11"/>
       <c r="N249" t="s" s="11">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="O249" t="s" s="11">
         <v>33</v>
@@ -12623,22 +12629,22 @@
     </row>
     <row r="250" hidden="true" outlineLevel="1">
       <c r="A250" t="s" s="101">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B250" t="s" s="39">
         <v>103</v>
       </c>
       <c r="C250" t="s" s="39">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D250" t="s" s="39">
         <v>40</v>
       </c>
       <c r="E250" t="s" s="39">
+        <v>253</v>
+      </c>
+      <c r="F250" t="s" s="39">
         <v>254</v>
-      </c>
-      <c r="F250" t="s" s="39">
-        <v>255</v>
       </c>
       <c r="G250" t="n" s="41">
         <v>46209.0</v>
@@ -12660,7 +12666,7 @@
       </c>
       <c r="M250" s="33"/>
       <c r="N250" t="s" s="33">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="O250" t="s" s="33">
         <v>33</v>
@@ -12676,22 +12682,22 @@
     </row>
     <row r="251" hidden="true" outlineLevel="1">
       <c r="A251" t="s" s="101">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B251" t="s" s="39">
         <v>110</v>
       </c>
       <c r="C251" t="s" s="39">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D251" t="s" s="39">
         <v>40</v>
       </c>
       <c r="E251" t="s" s="39">
+        <v>253</v>
+      </c>
+      <c r="F251" t="s" s="39">
         <v>254</v>
-      </c>
-      <c r="F251" t="s" s="39">
-        <v>255</v>
       </c>
       <c r="G251" t="n" s="41">
         <v>46230.0</v>
@@ -12713,7 +12719,7 @@
       </c>
       <c r="M251" s="11"/>
       <c r="N251" t="s" s="11">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="O251" t="s" s="11">
         <v>33</v>
@@ -12729,22 +12735,22 @@
     </row>
     <row r="252" hidden="true" outlineLevel="1">
       <c r="A252" t="s" s="101">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B252" t="s" s="39">
         <v>117</v>
       </c>
       <c r="C252" t="s" s="39">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D252" t="s" s="39">
         <v>40</v>
       </c>
       <c r="E252" t="s" s="39">
+        <v>253</v>
+      </c>
+      <c r="F252" t="s" s="39">
         <v>254</v>
-      </c>
-      <c r="F252" t="s" s="39">
-        <v>255</v>
       </c>
       <c r="G252" t="n" s="41">
         <v>46251.0</v>
@@ -12766,7 +12772,7 @@
       </c>
       <c r="M252" s="33"/>
       <c r="N252" t="s" s="33">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="O252" t="s" s="33">
         <v>33</v>
@@ -12803,7 +12809,7 @@
     </row>
     <row r="254" hidden="false">
       <c r="A254" t="s" s="15">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B254" s="19"/>
       <c r="C254" s="19"/>
@@ -12814,7 +12820,7 @@
       <c r="H254" s="17"/>
       <c r="I254" s="19"/>
       <c r="J254" t="s" s="19">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="K254" s="17"/>
       <c r="L254" s="77"/>
@@ -12826,7 +12832,7 @@
       <c r="R254" s="17"/>
       <c r="S254" s="19"/>
     </row>
-    <row r="255" hidden="false" outlineLevel="1">
+    <row r="255" hidden="true" outlineLevel="1">
       <c r="A255" s="25"/>
       <c r="B255" s="5"/>
       <c r="C255" s="5"/>
@@ -12847,24 +12853,24 @@
       <c r="R255" s="5"/>
       <c r="S255" s="5"/>
     </row>
-    <row r="256" hidden="false" outlineLevel="1">
+    <row r="256" hidden="true" outlineLevel="1">
       <c r="A256" t="s" s="101">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B256" t="s" s="39">
         <v>29</v>
       </c>
       <c r="C256" t="s" s="39">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D256" t="n" s="39">
         <v>2.1</v>
       </c>
       <c r="E256" t="s" s="39">
+        <v>273</v>
+      </c>
+      <c r="F256" t="s" s="39">
         <v>274</v>
-      </c>
-      <c r="F256" t="s" s="39">
-        <v>275</v>
       </c>
       <c r="G256" t="n" s="41">
         <v>45964.0</v>
@@ -12898,24 +12904,24 @@
       </c>
       <c r="S256" s="5"/>
     </row>
-    <row r="257" hidden="false" outlineLevel="1">
+    <row r="257" hidden="true" outlineLevel="1">
       <c r="A257" t="s" s="101">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B257" t="s" s="39">
         <v>45</v>
       </c>
       <c r="C257" t="s" s="39">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D257" t="n" s="39">
         <v>1.1</v>
       </c>
       <c r="E257" t="s" s="39">
+        <v>273</v>
+      </c>
+      <c r="F257" t="s" s="39">
         <v>274</v>
-      </c>
-      <c r="F257" t="s" s="39">
-        <v>275</v>
       </c>
       <c r="G257" t="n" s="41">
         <v>46041.0</v>
@@ -12949,24 +12955,24 @@
       </c>
       <c r="S257" s="29"/>
     </row>
-    <row r="258" hidden="false" outlineLevel="1">
+    <row r="258" hidden="true" outlineLevel="1">
       <c r="A258" t="s" s="101">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B258" t="s" s="39">
         <v>52</v>
       </c>
       <c r="C258" t="s" s="39">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D258" t="n" s="39">
         <v>2.2</v>
       </c>
       <c r="E258" t="s" s="39">
+        <v>273</v>
+      </c>
+      <c r="F258" t="s" s="39">
         <v>274</v>
-      </c>
-      <c r="F258" t="s" s="39">
-        <v>275</v>
       </c>
       <c r="G258" t="n" s="41">
         <v>46062.0</v>
@@ -13000,24 +13006,24 @@
       </c>
       <c r="S258" s="5"/>
     </row>
-    <row r="259" hidden="false" outlineLevel="1">
+    <row r="259" hidden="true" outlineLevel="1">
       <c r="A259" t="s" s="101">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B259" t="s" s="39">
         <v>60</v>
       </c>
       <c r="C259" t="s" s="39">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D259" t="n" s="39">
         <v>1.2</v>
       </c>
       <c r="E259" t="s" s="39">
+        <v>273</v>
+      </c>
+      <c r="F259" t="s" s="39">
         <v>274</v>
-      </c>
-      <c r="F259" t="s" s="39">
-        <v>275</v>
       </c>
       <c r="G259" t="n" s="41">
         <v>46083.0</v>
@@ -13039,7 +13045,7 @@
       </c>
       <c r="M259" s="33"/>
       <c r="N259" t="s" s="33">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="O259" t="s" s="33">
         <v>33</v>
@@ -13053,24 +13059,24 @@
       </c>
       <c r="S259" s="29"/>
     </row>
-    <row r="260" hidden="false" outlineLevel="1">
+    <row r="260" hidden="true" outlineLevel="1">
       <c r="A260" t="s" s="101">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B260" t="s" s="39">
         <v>68</v>
       </c>
       <c r="C260" t="s" s="39">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D260" t="n" s="39">
         <v>2.3</v>
       </c>
       <c r="E260" t="s" s="39">
+        <v>273</v>
+      </c>
+      <c r="F260" t="s" s="39">
         <v>274</v>
-      </c>
-      <c r="F260" t="s" s="39">
-        <v>275</v>
       </c>
       <c r="G260" t="n" s="41">
         <v>46104.0</v>
@@ -13092,7 +13098,7 @@
       </c>
       <c r="M260" s="11"/>
       <c r="N260" t="s" s="13">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="O260" t="s" s="11">
         <v>33</v>
@@ -13106,24 +13112,24 @@
       </c>
       <c r="S260" s="5"/>
     </row>
-    <row r="261" hidden="false" outlineLevel="1">
+    <row r="261" hidden="true" outlineLevel="1">
       <c r="A261" t="s" s="101">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B261" t="s" s="39">
         <v>75</v>
       </c>
       <c r="C261" t="s" s="39">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D261" t="n" s="39">
         <v>1.3</v>
       </c>
       <c r="E261" t="s" s="39">
+        <v>273</v>
+      </c>
+      <c r="F261" t="s" s="39">
         <v>274</v>
-      </c>
-      <c r="F261" t="s" s="39">
-        <v>275</v>
       </c>
       <c r="G261" t="n" s="41">
         <v>46125.0</v>
@@ -13145,7 +13151,7 @@
       </c>
       <c r="M261" s="33"/>
       <c r="N261" t="s" s="13">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="O261" t="s" s="33">
         <v>33</v>
@@ -13159,24 +13165,24 @@
       </c>
       <c r="S261" s="29"/>
     </row>
-    <row r="262" hidden="false" outlineLevel="1">
+    <row r="262" hidden="true" outlineLevel="1">
       <c r="A262" t="s" s="101">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B262" t="s" s="39">
         <v>82</v>
       </c>
       <c r="C262" t="s" s="39">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D262" t="n" s="39">
         <v>2.4</v>
       </c>
       <c r="E262" t="s" s="39">
+        <v>273</v>
+      </c>
+      <c r="F262" t="s" s="39">
         <v>274</v>
-      </c>
-      <c r="F262" t="s" s="39">
-        <v>275</v>
       </c>
       <c r="G262" t="n" s="41">
         <v>46146.0</v>
@@ -13210,24 +13216,24 @@
       </c>
       <c r="S262" s="5"/>
     </row>
-    <row r="263" hidden="false" outlineLevel="1">
+    <row r="263" hidden="true" outlineLevel="1">
       <c r="A263" t="s" s="79">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B263" t="s" s="63">
         <v>89</v>
       </c>
       <c r="C263" t="s" s="63">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D263" t="n" s="63">
         <v>1.4</v>
       </c>
       <c r="E263" t="s" s="63">
+        <v>273</v>
+      </c>
+      <c r="F263" t="s" s="63">
         <v>274</v>
-      </c>
-      <c r="F263" t="s" s="63">
-        <v>275</v>
       </c>
       <c r="G263" t="n" s="65">
         <v>46167.0</v>
@@ -13259,24 +13265,24 @@
       </c>
       <c r="S263" s="29"/>
     </row>
-    <row r="264" hidden="false" outlineLevel="1">
+    <row r="264" hidden="true" outlineLevel="1">
       <c r="A264" t="s" s="79">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B264" t="s" s="63">
         <v>96</v>
       </c>
       <c r="C264" t="s" s="63">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D264" t="n" s="63">
         <v>2.5</v>
       </c>
       <c r="E264" t="s" s="63">
+        <v>273</v>
+      </c>
+      <c r="F264" t="s" s="63">
         <v>274</v>
-      </c>
-      <c r="F264" t="s" s="63">
-        <v>275</v>
       </c>
       <c r="G264" t="n" s="65">
         <v>46188.0</v>
@@ -13296,7 +13302,7 @@
       <c r="L264" s="75"/>
       <c r="M264" s="11"/>
       <c r="N264" t="s" s="13">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="O264" t="s" s="11">
         <v>33</v>
@@ -13310,24 +13316,24 @@
       </c>
       <c r="S264" s="5"/>
     </row>
-    <row r="265" hidden="false" outlineLevel="1">
+    <row r="265" hidden="true" outlineLevel="1">
       <c r="A265" t="s" s="79">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B265" t="s" s="63">
         <v>103</v>
       </c>
       <c r="C265" t="s" s="63">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D265" t="n" s="63">
         <v>1.5</v>
       </c>
       <c r="E265" t="s" s="63">
+        <v>273</v>
+      </c>
+      <c r="F265" t="s" s="63">
         <v>274</v>
-      </c>
-      <c r="F265" t="s" s="63">
-        <v>275</v>
       </c>
       <c r="G265" t="n" s="65">
         <v>46209.0</v>
@@ -13347,7 +13353,7 @@
       <c r="L265" s="75"/>
       <c r="M265" s="33"/>
       <c r="N265" t="s" s="33">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="O265" t="s" s="33">
         <v>33</v>
@@ -13361,24 +13367,24 @@
       </c>
       <c r="S265" s="29"/>
     </row>
-    <row r="266" hidden="false" outlineLevel="1">
+    <row r="266" hidden="true" outlineLevel="1">
       <c r="A266" t="s" s="79">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B266" t="s" s="63">
         <v>110</v>
       </c>
       <c r="C266" t="s" s="63">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D266" t="n" s="63">
         <v>2.6</v>
       </c>
       <c r="E266" t="s" s="63">
+        <v>273</v>
+      </c>
+      <c r="F266" t="s" s="63">
         <v>274</v>
-      </c>
-      <c r="F266" t="s" s="63">
-        <v>275</v>
       </c>
       <c r="G266" t="n" s="65">
         <v>46230.0</v>
@@ -13398,7 +13404,7 @@
       <c r="L266" s="75"/>
       <c r="M266" s="11"/>
       <c r="N266" t="s" s="13">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="O266" t="s" s="11">
         <v>33</v>
@@ -13412,24 +13418,24 @@
       </c>
       <c r="S266" s="5"/>
     </row>
-    <row r="267" hidden="false" outlineLevel="1">
+    <row r="267" hidden="true" outlineLevel="1">
       <c r="A267" t="s" s="79">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B267" t="s" s="63">
         <v>117</v>
       </c>
       <c r="C267" t="s" s="63">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D267" t="n" s="63">
         <v>1.6</v>
       </c>
       <c r="E267" t="s" s="63">
+        <v>273</v>
+      </c>
+      <c r="F267" t="s" s="63">
         <v>274</v>
-      </c>
-      <c r="F267" t="s" s="63">
-        <v>275</v>
       </c>
       <c r="G267" t="n" s="65">
         <v>46251.0</v>
@@ -13449,7 +13455,7 @@
       <c r="L267" s="75"/>
       <c r="M267" s="33"/>
       <c r="N267" t="s" s="33">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="O267" t="s" s="33">
         <v>33</v>
@@ -13486,7 +13492,7 @@
     </row>
     <row r="269" hidden="false">
       <c r="A269" t="s" s="15">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B269" s="19"/>
       <c r="C269" s="19"/>
@@ -13501,7 +13507,7 @@
       <c r="L269" s="77"/>
       <c r="M269" s="77"/>
       <c r="N269" t="s" s="77">
-        <v>152</v>
+        <v>123</v>
       </c>
       <c r="O269" s="77"/>
       <c r="P269" s="19"/>
@@ -13509,7 +13515,7 @@
       <c r="R269" s="17"/>
       <c r="S269" s="19"/>
     </row>
-    <row r="270" hidden="false" outlineLevel="1">
+    <row r="270" hidden="true" outlineLevel="1">
       <c r="A270" s="25"/>
       <c r="B270" s="5"/>
       <c r="C270" s="5"/>
@@ -13530,24 +13536,24 @@
       <c r="R270" s="5"/>
       <c r="S270" s="5"/>
     </row>
-    <row r="271" hidden="false" outlineLevel="1">
+    <row r="271" hidden="true" outlineLevel="1">
       <c r="A271" t="s" s="101">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B271" t="s" s="39">
         <v>29</v>
       </c>
       <c r="C271" t="s" s="39">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D271" t="n" s="39">
         <v>2.1</v>
       </c>
       <c r="E271" t="s" s="39">
+        <v>295</v>
+      </c>
+      <c r="F271" t="s" s="39">
         <v>296</v>
-      </c>
-      <c r="F271" t="s" s="39">
-        <v>297</v>
       </c>
       <c r="G271" t="n" s="41">
         <v>45964.0</v>
@@ -13581,24 +13587,24 @@
       </c>
       <c r="S271" s="5"/>
     </row>
-    <row r="272" hidden="false" outlineLevel="1">
+    <row r="272" hidden="true" outlineLevel="1">
       <c r="A272" t="s" s="101">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B272" t="s" s="39">
         <v>45</v>
       </c>
       <c r="C272" t="s" s="39">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D272" t="n" s="39">
         <v>1.1</v>
       </c>
       <c r="E272" t="s" s="39">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F272" t="s" s="39">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="G272" t="n" s="41">
         <v>46041.0</v>
@@ -13632,24 +13638,24 @@
       </c>
       <c r="S272" s="29"/>
     </row>
-    <row r="273" hidden="false" outlineLevel="1">
+    <row r="273" hidden="true" outlineLevel="1">
       <c r="A273" t="s" s="101">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B273" t="s" s="39">
         <v>52</v>
       </c>
       <c r="C273" t="s" s="39">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D273" t="n" s="39">
         <v>2.2</v>
       </c>
       <c r="E273" t="s" s="39">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F273" t="s" s="39">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="G273" t="n" s="41">
         <v>46062.0</v>
@@ -13683,24 +13689,24 @@
       </c>
       <c r="S273" s="5"/>
     </row>
-    <row r="274" hidden="false" outlineLevel="1">
+    <row r="274" hidden="true" outlineLevel="1">
       <c r="A274" t="s" s="101">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B274" t="s" s="39">
         <v>60</v>
       </c>
       <c r="C274" t="s" s="39">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D274" t="n" s="39">
         <v>1.2</v>
       </c>
       <c r="E274" t="s" s="39">
+        <v>295</v>
+      </c>
+      <c r="F274" t="s" s="39">
         <v>296</v>
-      </c>
-      <c r="F274" t="s" s="39">
-        <v>297</v>
       </c>
       <c r="G274" t="n" s="41">
         <v>46083.0</v>
@@ -13722,7 +13728,7 @@
       </c>
       <c r="M274" s="33"/>
       <c r="N274" t="s" s="33">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="O274" t="s" s="33">
         <v>33</v>
@@ -13736,24 +13742,24 @@
       </c>
       <c r="S274" s="29"/>
     </row>
-    <row r="275" hidden="false" outlineLevel="1">
+    <row r="275" hidden="true" outlineLevel="1">
       <c r="A275" t="s" s="101">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B275" t="s" s="39">
         <v>68</v>
       </c>
       <c r="C275" t="s" s="39">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D275" t="n" s="39">
         <v>2.3</v>
       </c>
       <c r="E275" t="s" s="39">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F275" t="s" s="39">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="G275" t="n" s="41">
         <v>46104.0</v>
@@ -13787,24 +13793,24 @@
       </c>
       <c r="S275" s="5"/>
     </row>
-    <row r="276" hidden="false" outlineLevel="1">
+    <row r="276" hidden="true" outlineLevel="1">
       <c r="A276" t="s" s="79">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B276" t="s" s="63">
         <v>75</v>
       </c>
       <c r="C276" t="s" s="63">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D276" t="n" s="63">
         <v>1.3</v>
       </c>
       <c r="E276" t="s" s="63">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F276" t="s" s="63">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="G276" t="n" s="65">
         <v>46125.0</v>
@@ -13836,24 +13842,24 @@
       </c>
       <c r="S276" s="29"/>
     </row>
-    <row r="277" hidden="false" outlineLevel="1">
+    <row r="277" hidden="true" outlineLevel="1">
       <c r="A277" t="s" s="79">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B277" t="s" s="63">
         <v>82</v>
       </c>
       <c r="C277" t="s" s="63">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D277" t="n" s="63">
         <v>2.4</v>
       </c>
       <c r="E277" t="s" s="63">
+        <v>295</v>
+      </c>
+      <c r="F277" t="s" s="63">
         <v>296</v>
-      </c>
-      <c r="F277" t="s" s="63">
-        <v>297</v>
       </c>
       <c r="G277" t="n" s="65">
         <v>46146.0</v>
@@ -13885,24 +13891,24 @@
       </c>
       <c r="S277" s="5"/>
     </row>
-    <row r="278" hidden="false" outlineLevel="1">
+    <row r="278" hidden="true" outlineLevel="1">
       <c r="A278" t="s" s="79">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B278" t="s" s="63">
         <v>89</v>
       </c>
       <c r="C278" t="s" s="63">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D278" t="n" s="63">
         <v>1.4</v>
       </c>
       <c r="E278" t="s" s="63">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F278" t="s" s="63">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="G278" t="n" s="65">
         <v>46167.0</v>
@@ -13934,24 +13940,24 @@
       </c>
       <c r="S278" s="29"/>
     </row>
-    <row r="279" hidden="false" outlineLevel="1">
+    <row r="279" hidden="true" outlineLevel="1">
       <c r="A279" t="s" s="79">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B279" t="s" s="63">
         <v>96</v>
       </c>
       <c r="C279" t="s" s="63">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D279" t="n" s="63">
         <v>2.5</v>
       </c>
       <c r="E279" t="s" s="63">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F279" t="s" s="63">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="G279" t="n" s="65">
         <v>46188.0</v>
@@ -13983,24 +13989,24 @@
       </c>
       <c r="S279" s="5"/>
     </row>
-    <row r="280" hidden="false" outlineLevel="1">
+    <row r="280" hidden="true" outlineLevel="1">
       <c r="A280" t="s" s="79">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B280" t="s" s="63">
         <v>103</v>
       </c>
       <c r="C280" t="s" s="63">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D280" t="n" s="63">
         <v>1.5</v>
       </c>
       <c r="E280" t="s" s="63">
+        <v>295</v>
+      </c>
+      <c r="F280" t="s" s="63">
         <v>296</v>
-      </c>
-      <c r="F280" t="s" s="63">
-        <v>297</v>
       </c>
       <c r="G280" t="n" s="65">
         <v>46209.0</v>
@@ -14032,24 +14038,24 @@
       </c>
       <c r="S280" s="29"/>
     </row>
-    <row r="281" hidden="false" outlineLevel="1">
+    <row r="281" hidden="true" outlineLevel="1">
       <c r="A281" t="s" s="79">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B281" t="s" s="63">
         <v>110</v>
       </c>
       <c r="C281" t="s" s="63">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D281" t="n" s="63">
         <v>2.6</v>
       </c>
       <c r="E281" t="s" s="63">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F281" t="s" s="63">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="G281" t="n" s="65">
         <v>46230.0</v>
@@ -14081,24 +14087,24 @@
       </c>
       <c r="S281" s="5"/>
     </row>
-    <row r="282" hidden="false" outlineLevel="1">
+    <row r="282" hidden="true" outlineLevel="1">
       <c r="A282" t="s" s="79">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B282" t="s" s="63">
         <v>117</v>
       </c>
       <c r="C282" t="s" s="63">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D282" t="n" s="63">
         <v>1.6</v>
       </c>
       <c r="E282" t="s" s="63">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F282" t="s" s="63">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="G282" t="n" s="65">
         <v>46251.0</v>
@@ -14153,7 +14159,7 @@
     </row>
     <row r="284" hidden="false">
       <c r="A284" t="s" s="15">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B284" s="19"/>
       <c r="C284" s="19"/>
@@ -14168,7 +14174,7 @@
       <c r="L284" s="77"/>
       <c r="M284" s="77"/>
       <c r="N284" t="s" s="77">
-        <v>152</v>
+        <v>123</v>
       </c>
       <c r="O284" s="77"/>
       <c r="P284" s="19"/>
@@ -14176,7 +14182,7 @@
       <c r="R284" s="17"/>
       <c r="S284" s="19"/>
     </row>
-    <row r="285" hidden="false" outlineLevel="1">
+    <row r="285" hidden="true" outlineLevel="1">
       <c r="A285" s="25"/>
       <c r="B285" s="5"/>
       <c r="C285" s="5"/>
@@ -14197,24 +14203,24 @@
       <c r="R285" s="5"/>
       <c r="S285" s="5"/>
     </row>
-    <row r="286" hidden="false" outlineLevel="1">
+    <row r="286" hidden="true" outlineLevel="1">
       <c r="A286" t="s" s="101">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B286" t="s" s="39">
         <v>29</v>
       </c>
       <c r="C286" t="s" s="39">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D286" t="n" s="39">
         <v>2.1</v>
       </c>
       <c r="E286" t="s" s="39">
+        <v>313</v>
+      </c>
+      <c r="F286" t="s" s="39">
         <v>314</v>
-      </c>
-      <c r="F286" t="s" s="39">
-        <v>315</v>
       </c>
       <c r="G286" t="n" s="41">
         <v>45964.0</v>
@@ -14248,24 +14254,24 @@
       </c>
       <c r="S286" s="5"/>
     </row>
-    <row r="287" hidden="false" outlineLevel="1">
+    <row r="287" hidden="true" outlineLevel="1">
       <c r="A287" t="s" s="101">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B287" t="s" s="39">
         <v>45</v>
       </c>
       <c r="C287" t="s" s="39">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D287" t="n" s="39">
         <v>1.1</v>
       </c>
       <c r="E287" t="s" s="39">
+        <v>313</v>
+      </c>
+      <c r="F287" t="s" s="39">
         <v>314</v>
-      </c>
-      <c r="F287" t="s" s="39">
-        <v>315</v>
       </c>
       <c r="G287" t="n" s="41">
         <v>46041.0</v>
@@ -14299,24 +14305,24 @@
       </c>
       <c r="S287" s="29"/>
     </row>
-    <row r="288" hidden="false" outlineLevel="1">
+    <row r="288" hidden="true" outlineLevel="1">
       <c r="A288" t="s" s="101">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B288" t="s" s="39">
         <v>52</v>
       </c>
       <c r="C288" t="s" s="39">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D288" t="n" s="39">
         <v>2.2</v>
       </c>
       <c r="E288" t="s" s="39">
+        <v>313</v>
+      </c>
+      <c r="F288" t="s" s="39">
         <v>314</v>
-      </c>
-      <c r="F288" t="s" s="39">
-        <v>315</v>
       </c>
       <c r="G288" t="n" s="41">
         <v>46062.0</v>
@@ -14350,24 +14356,24 @@
       </c>
       <c r="S288" s="5"/>
     </row>
-    <row r="289" hidden="false" outlineLevel="1">
+    <row r="289" hidden="true" outlineLevel="1">
       <c r="A289" t="s" s="101">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B289" t="s" s="39">
         <v>60</v>
       </c>
       <c r="C289" t="s" s="39">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D289" t="n" s="39">
         <v>1.2</v>
       </c>
       <c r="E289" t="s" s="39">
+        <v>313</v>
+      </c>
+      <c r="F289" t="s" s="39">
         <v>314</v>
-      </c>
-      <c r="F289" t="s" s="39">
-        <v>315</v>
       </c>
       <c r="G289" t="n" s="41">
         <v>46083.0</v>
@@ -14401,24 +14407,24 @@
       </c>
       <c r="S289" s="29"/>
     </row>
-    <row r="290" hidden="false" outlineLevel="1">
+    <row r="290" hidden="true" outlineLevel="1">
       <c r="A290" t="s" s="101">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B290" t="s" s="39">
         <v>68</v>
       </c>
       <c r="C290" t="s" s="39">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D290" t="n" s="39">
         <v>2.3</v>
       </c>
       <c r="E290" t="s" s="39">
+        <v>313</v>
+      </c>
+      <c r="F290" t="s" s="39">
         <v>314</v>
-      </c>
-      <c r="F290" t="s" s="39">
-        <v>315</v>
       </c>
       <c r="G290" t="n" s="41">
         <v>46104.0</v>
@@ -14452,24 +14458,24 @@
       </c>
       <c r="S290" s="5"/>
     </row>
-    <row r="291" hidden="false" outlineLevel="1">
+    <row r="291" hidden="true" outlineLevel="1">
       <c r="A291" t="s" s="79">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B291" t="s" s="63">
         <v>75</v>
       </c>
       <c r="C291" t="s" s="63">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D291" t="n" s="63">
         <v>1.3</v>
       </c>
       <c r="E291" t="s" s="63">
+        <v>313</v>
+      </c>
+      <c r="F291" t="s" s="63">
         <v>314</v>
-      </c>
-      <c r="F291" t="s" s="63">
-        <v>315</v>
       </c>
       <c r="G291" t="n" s="65">
         <v>46125.0</v>
@@ -14501,24 +14507,24 @@
       </c>
       <c r="S291" s="29"/>
     </row>
-    <row r="292" hidden="false" outlineLevel="1">
+    <row r="292" hidden="true" outlineLevel="1">
       <c r="A292" t="s" s="79">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B292" t="s" s="63">
         <v>82</v>
       </c>
       <c r="C292" t="s" s="63">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D292" t="n" s="63">
         <v>2.4</v>
       </c>
       <c r="E292" t="s" s="63">
+        <v>313</v>
+      </c>
+      <c r="F292" t="s" s="63">
         <v>314</v>
-      </c>
-      <c r="F292" t="s" s="63">
-        <v>315</v>
       </c>
       <c r="G292" t="n" s="65">
         <v>46146.0</v>
@@ -14550,24 +14556,24 @@
       </c>
       <c r="S292" s="5"/>
     </row>
-    <row r="293" hidden="false" outlineLevel="1">
+    <row r="293" hidden="true" outlineLevel="1">
       <c r="A293" t="s" s="79">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B293" t="s" s="63">
         <v>89</v>
       </c>
       <c r="C293" t="s" s="63">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D293" t="n" s="63">
         <v>1.4</v>
       </c>
       <c r="E293" t="s" s="63">
+        <v>313</v>
+      </c>
+      <c r="F293" t="s" s="63">
         <v>314</v>
-      </c>
-      <c r="F293" t="s" s="63">
-        <v>315</v>
       </c>
       <c r="G293" t="n" s="65">
         <v>46167.0</v>
@@ -14599,24 +14605,24 @@
       </c>
       <c r="S293" s="29"/>
     </row>
-    <row r="294" hidden="false" outlineLevel="1">
+    <row r="294" hidden="true" outlineLevel="1">
       <c r="A294" t="s" s="79">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B294" t="s" s="63">
         <v>96</v>
       </c>
       <c r="C294" t="s" s="63">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D294" t="n" s="63">
         <v>2.5</v>
       </c>
       <c r="E294" t="s" s="63">
+        <v>313</v>
+      </c>
+      <c r="F294" t="s" s="63">
         <v>314</v>
-      </c>
-      <c r="F294" t="s" s="63">
-        <v>315</v>
       </c>
       <c r="G294" t="n" s="65">
         <v>46188.0</v>
@@ -14648,24 +14654,24 @@
       </c>
       <c r="S294" s="5"/>
     </row>
-    <row r="295" hidden="false" outlineLevel="1">
+    <row r="295" hidden="true" outlineLevel="1">
       <c r="A295" t="s" s="79">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B295" t="s" s="63">
         <v>103</v>
       </c>
       <c r="C295" t="s" s="63">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D295" t="n" s="63">
         <v>1.5</v>
       </c>
       <c r="E295" t="s" s="63">
+        <v>313</v>
+      </c>
+      <c r="F295" t="s" s="63">
         <v>314</v>
-      </c>
-      <c r="F295" t="s" s="63">
-        <v>315</v>
       </c>
       <c r="G295" t="n" s="65">
         <v>46209.0</v>
@@ -14697,24 +14703,24 @@
       </c>
       <c r="S295" s="29"/>
     </row>
-    <row r="296" hidden="false" outlineLevel="1">
+    <row r="296" hidden="true" outlineLevel="1">
       <c r="A296" t="s" s="79">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B296" t="s" s="63">
         <v>110</v>
       </c>
       <c r="C296" t="s" s="63">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D296" t="n" s="63">
         <v>2.6</v>
       </c>
       <c r="E296" t="s" s="63">
+        <v>313</v>
+      </c>
+      <c r="F296" t="s" s="63">
         <v>314</v>
-      </c>
-      <c r="F296" t="s" s="63">
-        <v>315</v>
       </c>
       <c r="G296" t="n" s="65">
         <v>46230.0</v>
@@ -14746,24 +14752,24 @@
       </c>
       <c r="S296" s="5"/>
     </row>
-    <row r="297" hidden="false" outlineLevel="1">
+    <row r="297" hidden="true" outlineLevel="1">
       <c r="A297" t="s" s="79">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B297" t="s" s="63">
         <v>117</v>
       </c>
       <c r="C297" t="s" s="63">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D297" t="n" s="63">
         <v>1.6</v>
       </c>
       <c r="E297" t="s" s="63">
+        <v>313</v>
+      </c>
+      <c r="F297" t="s" s="63">
         <v>314</v>
-      </c>
-      <c r="F297" t="s" s="63">
-        <v>315</v>
       </c>
       <c r="G297" t="n" s="65">
         <v>46251.0</v>
@@ -14818,7 +14824,7 @@
     </row>
     <row r="299" hidden="false">
       <c r="A299" t="s" s="15">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B299" s="19"/>
       <c r="C299" s="19"/>
@@ -14833,7 +14839,7 @@
       <c r="L299" s="77"/>
       <c r="M299" s="77"/>
       <c r="N299" t="s" s="77">
-        <v>152</v>
+        <v>123</v>
       </c>
       <c r="O299" s="77"/>
       <c r="P299" s="19"/>
@@ -14841,7 +14847,7 @@
       <c r="R299" s="17"/>
       <c r="S299" s="19"/>
     </row>
-    <row r="300" hidden="false" outlineLevel="1">
+    <row r="300" hidden="true" outlineLevel="1">
       <c r="A300" s="25"/>
       <c r="B300" s="5"/>
       <c r="C300" s="5"/>
@@ -14862,24 +14868,24 @@
       <c r="R300" s="5"/>
       <c r="S300" s="5"/>
     </row>
-    <row r="301" hidden="false" outlineLevel="1">
+    <row r="301" hidden="true" outlineLevel="1">
       <c r="A301" t="s" s="101">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B301" t="s" s="39">
         <v>29</v>
       </c>
       <c r="C301" t="s" s="39">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D301" t="n" s="39">
         <v>2.1</v>
       </c>
       <c r="E301" t="s" s="39">
+        <v>329</v>
+      </c>
+      <c r="F301" t="s" s="39">
         <v>330</v>
-      </c>
-      <c r="F301" t="s" s="39">
-        <v>331</v>
       </c>
       <c r="G301" t="n" s="41">
         <v>45971.0</v>
@@ -14913,24 +14919,24 @@
       </c>
       <c r="S301" s="5"/>
     </row>
-    <row r="302" hidden="false" outlineLevel="1">
+    <row r="302" hidden="true" outlineLevel="1">
       <c r="A302" t="s" s="101">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B302" t="s" s="39">
         <v>45</v>
       </c>
       <c r="C302" t="s" s="39">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D302" t="n" s="39">
         <v>1.1</v>
       </c>
       <c r="E302" t="s" s="39">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="F302" t="s" s="39">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="G302" t="n" s="41">
         <v>46048.0</v>
@@ -14964,24 +14970,24 @@
       </c>
       <c r="S302" s="29"/>
     </row>
-    <row r="303" hidden="false" outlineLevel="1">
+    <row r="303" hidden="true" outlineLevel="1">
       <c r="A303" t="s" s="101">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B303" t="s" s="39">
         <v>52</v>
       </c>
       <c r="C303" t="s" s="39">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D303" t="n" s="39">
         <v>2.2</v>
       </c>
       <c r="E303" t="s" s="39">
+        <v>329</v>
+      </c>
+      <c r="F303" t="s" s="39">
         <v>330</v>
-      </c>
-      <c r="F303" t="s" s="39">
-        <v>331</v>
       </c>
       <c r="G303" t="n" s="41">
         <v>46069.0</v>
@@ -15015,24 +15021,24 @@
       </c>
       <c r="S303" s="5"/>
     </row>
-    <row r="304" hidden="false" outlineLevel="1">
+    <row r="304" hidden="true" outlineLevel="1">
       <c r="A304" t="s" s="79">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B304" t="s" s="63">
         <v>60</v>
       </c>
       <c r="C304" t="s" s="63">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D304" t="n" s="63">
         <v>1.2</v>
       </c>
       <c r="E304" t="s" s="63">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="F304" t="s" s="63">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="G304" t="n" s="65">
         <v>46090.0</v>
@@ -15052,7 +15058,7 @@
       <c r="L304" s="75"/>
       <c r="M304" s="33"/>
       <c r="N304" t="s" s="33">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="O304" t="s" s="33">
         <v>33</v>
@@ -15066,24 +15072,24 @@
       </c>
       <c r="S304" s="29"/>
     </row>
-    <row r="305" hidden="false" outlineLevel="1">
+    <row r="305" hidden="true" outlineLevel="1">
       <c r="A305" t="s" s="79">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B305" t="s" s="63">
         <v>68</v>
       </c>
       <c r="C305" t="s" s="63">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D305" t="n" s="63">
         <v>2.3</v>
       </c>
       <c r="E305" t="s" s="63">
+        <v>329</v>
+      </c>
+      <c r="F305" t="s" s="63">
         <v>330</v>
-      </c>
-      <c r="F305" t="s" s="63">
-        <v>331</v>
       </c>
       <c r="G305" t="n" s="65">
         <v>46111.0</v>
@@ -15115,24 +15121,24 @@
       </c>
       <c r="S305" s="5"/>
     </row>
-    <row r="306" hidden="false" outlineLevel="1">
+    <row r="306" hidden="true" outlineLevel="1">
       <c r="A306" t="s" s="79">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B306" t="s" s="63">
         <v>75</v>
       </c>
       <c r="C306" t="s" s="63">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D306" t="n" s="63">
         <v>1.3</v>
       </c>
       <c r="E306" t="s" s="63">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="F306" t="s" s="63">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="G306" t="n" s="65">
         <v>46132.0</v>
@@ -15152,10 +15158,10 @@
       <c r="L306" s="75"/>
       <c r="M306" s="33"/>
       <c r="N306" t="s" s="33">
+        <v>338</v>
+      </c>
+      <c r="O306" t="s" s="105">
         <v>339</v>
-      </c>
-      <c r="O306" t="s" s="111">
-        <v>340</v>
       </c>
       <c r="P306" s="29"/>
       <c r="Q306" t="n" s="29">
@@ -15166,24 +15172,24 @@
       </c>
       <c r="S306" s="29"/>
     </row>
-    <row r="307" hidden="false" outlineLevel="1">
+    <row r="307" hidden="true" outlineLevel="1">
       <c r="A307" t="s" s="79">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B307" t="s" s="63">
         <v>82</v>
       </c>
       <c r="C307" t="s" s="63">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D307" t="n" s="63">
         <v>2.4</v>
       </c>
       <c r="E307" t="s" s="63">
+        <v>329</v>
+      </c>
+      <c r="F307" t="s" s="63">
         <v>330</v>
-      </c>
-      <c r="F307" t="s" s="63">
-        <v>331</v>
       </c>
       <c r="G307" t="n" s="65">
         <v>46153.0</v>
@@ -15215,24 +15221,24 @@
       </c>
       <c r="S307" s="5"/>
     </row>
-    <row r="308" hidden="false" outlineLevel="1">
+    <row r="308" hidden="true" outlineLevel="1">
       <c r="A308" t="s" s="79">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B308" t="s" s="63">
         <v>89</v>
       </c>
       <c r="C308" t="s" s="63">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D308" t="n" s="63">
         <v>1.4</v>
       </c>
       <c r="E308" t="s" s="63">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="F308" t="s" s="63">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="G308" t="n" s="65">
         <v>46174.0</v>
@@ -15264,24 +15270,24 @@
       </c>
       <c r="S308" s="29"/>
     </row>
-    <row r="309" hidden="false" outlineLevel="1">
+    <row r="309" hidden="true" outlineLevel="1">
       <c r="A309" t="s" s="79">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B309" t="s" s="63">
         <v>96</v>
       </c>
       <c r="C309" t="s" s="63">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D309" t="n" s="63">
         <v>2.5</v>
       </c>
       <c r="E309" t="s" s="63">
+        <v>329</v>
+      </c>
+      <c r="F309" t="s" s="63">
         <v>330</v>
-      </c>
-      <c r="F309" t="s" s="63">
-        <v>331</v>
       </c>
       <c r="G309" t="n" s="65">
         <v>46195.0</v>
@@ -15313,24 +15319,24 @@
       </c>
       <c r="S309" s="5"/>
     </row>
-    <row r="310" hidden="false" outlineLevel="1">
+    <row r="310" hidden="true" outlineLevel="1">
       <c r="A310" t="s" s="79">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B310" t="s" s="63">
         <v>103</v>
       </c>
       <c r="C310" t="s" s="63">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D310" t="n" s="63">
         <v>1.5</v>
       </c>
       <c r="E310" t="s" s="63">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="F310" t="s" s="63">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="G310" t="n" s="65">
         <v>46216.0</v>
@@ -15362,24 +15368,24 @@
       </c>
       <c r="S310" s="29"/>
     </row>
-    <row r="311" hidden="false" outlineLevel="1">
+    <row r="311" hidden="true" outlineLevel="1">
       <c r="A311" t="s" s="79">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B311" t="s" s="63">
         <v>110</v>
       </c>
       <c r="C311" t="s" s="63">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D311" t="n" s="63">
         <v>2.6</v>
       </c>
       <c r="E311" t="s" s="63">
+        <v>329</v>
+      </c>
+      <c r="F311" t="s" s="63">
         <v>330</v>
-      </c>
-      <c r="F311" t="s" s="63">
-        <v>331</v>
       </c>
       <c r="G311" t="n" s="65">
         <v>46237.0</v>
@@ -15411,24 +15417,24 @@
       </c>
       <c r="S311" s="5"/>
     </row>
-    <row r="312" hidden="false" outlineLevel="1">
+    <row r="312" hidden="true" outlineLevel="1">
       <c r="A312" t="s" s="79">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B312" t="s" s="63">
         <v>117</v>
       </c>
       <c r="C312" t="s" s="63">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D312" t="n" s="63">
         <v>1.6</v>
       </c>
       <c r="E312" t="s" s="63">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="F312" t="s" s="63">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="G312" t="n" s="65">
         <v>46258.0</v>
@@ -15483,7 +15489,7 @@
     </row>
     <row r="314" hidden="false">
       <c r="A314" t="s" s="15">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B314" s="19"/>
       <c r="C314" s="19"/>
@@ -15498,7 +15504,7 @@
       <c r="L314" s="77"/>
       <c r="M314" s="77"/>
       <c r="N314" t="s" s="77">
-        <v>152</v>
+        <v>123</v>
       </c>
       <c r="O314" s="77"/>
       <c r="P314" s="19"/>
@@ -15506,7 +15512,7 @@
       <c r="R314" s="17"/>
       <c r="S314" s="19"/>
     </row>
-    <row r="315" hidden="false" outlineLevel="1">
+    <row r="315" hidden="true" outlineLevel="1">
       <c r="A315" s="25"/>
       <c r="B315" s="5"/>
       <c r="C315" s="5"/>
@@ -15527,24 +15533,24 @@
       <c r="R315" s="5"/>
       <c r="S315" s="5"/>
     </row>
-    <row r="316" hidden="false" outlineLevel="1">
+    <row r="316" hidden="true" outlineLevel="1">
       <c r="A316" t="s" s="101">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B316" t="s" s="39">
         <v>29</v>
       </c>
       <c r="C316" t="s" s="39">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D316" t="n" s="39">
         <v>2.1</v>
       </c>
       <c r="E316" t="s" s="39">
+        <v>348</v>
+      </c>
+      <c r="F316" t="s" s="39">
         <v>349</v>
-      </c>
-      <c r="F316" t="s" s="39">
-        <v>350</v>
       </c>
       <c r="G316" t="n" s="41">
         <v>45964.0</v>
@@ -15578,24 +15584,24 @@
       </c>
       <c r="S316" s="5"/>
     </row>
-    <row r="317" hidden="false" outlineLevel="1">
+    <row r="317" hidden="true" outlineLevel="1">
       <c r="A317" t="s" s="101">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B317" t="s" s="39">
         <v>45</v>
       </c>
       <c r="C317" t="s" s="39">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D317" t="n" s="39">
         <v>1.1</v>
       </c>
       <c r="E317" t="s" s="39">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="F317" t="s" s="39">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="G317" t="n" s="41">
         <v>46041.0</v>
@@ -15617,7 +15623,7 @@
       </c>
       <c r="M317" s="33"/>
       <c r="N317" t="s" s="33">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="O317" t="s" s="33">
         <v>63</v>
@@ -15631,24 +15637,24 @@
       </c>
       <c r="S317" s="29"/>
     </row>
-    <row r="318" hidden="false" outlineLevel="1">
+    <row r="318" hidden="true" outlineLevel="1">
       <c r="A318" t="s" s="101">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B318" t="s" s="39">
         <v>52</v>
       </c>
       <c r="C318" t="s" s="39">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D318" t="n" s="39">
         <v>2.2</v>
       </c>
       <c r="E318" t="s" s="39">
+        <v>348</v>
+      </c>
+      <c r="F318" t="s" s="39">
         <v>349</v>
-      </c>
-      <c r="F318" t="s" s="39">
-        <v>350</v>
       </c>
       <c r="G318" t="n" s="41">
         <v>46062.0</v>
@@ -15682,24 +15688,24 @@
       </c>
       <c r="S318" s="5"/>
     </row>
-    <row r="319" hidden="false" outlineLevel="1">
+    <row r="319" hidden="true" outlineLevel="1">
       <c r="A319" t="s" s="101">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B319" t="s" s="39">
         <v>60</v>
       </c>
       <c r="C319" t="s" s="39">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D319" t="n" s="39">
         <v>1.2</v>
       </c>
       <c r="E319" t="s" s="39">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="F319" t="s" s="39">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="G319" t="n" s="41">
         <v>46083.0</v>
@@ -15733,24 +15739,24 @@
       </c>
       <c r="S319" s="29"/>
     </row>
-    <row r="320" hidden="false" outlineLevel="1">
+    <row r="320" hidden="true" outlineLevel="1">
       <c r="A320" t="s" s="79">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B320" t="s" s="63">
         <v>68</v>
       </c>
       <c r="C320" t="s" s="63">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D320" t="n" s="63">
         <v>2.3</v>
       </c>
       <c r="E320" t="s" s="63">
+        <v>348</v>
+      </c>
+      <c r="F320" t="s" s="63">
         <v>349</v>
-      </c>
-      <c r="F320" t="s" s="63">
-        <v>350</v>
       </c>
       <c r="G320" t="n" s="65">
         <v>46104.0</v>
@@ -15782,24 +15788,24 @@
       </c>
       <c r="S320" s="5"/>
     </row>
-    <row r="321" hidden="false" outlineLevel="1">
+    <row r="321" hidden="true" outlineLevel="1">
       <c r="A321" t="s" s="79">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B321" t="s" s="63">
         <v>75</v>
       </c>
       <c r="C321" t="s" s="63">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D321" t="n" s="63">
         <v>1.3</v>
       </c>
       <c r="E321" t="s" s="63">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="F321" t="s" s="63">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="G321" t="n" s="65">
         <v>46125.0</v>
@@ -15831,24 +15837,24 @@
       </c>
       <c r="S321" s="29"/>
     </row>
-    <row r="322" hidden="false" outlineLevel="1">
+    <row r="322" hidden="true" outlineLevel="1">
       <c r="A322" t="s" s="79">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B322" t="s" s="63">
         <v>82</v>
       </c>
       <c r="C322" t="s" s="63">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D322" t="n" s="63">
         <v>2.4</v>
       </c>
       <c r="E322" t="s" s="63">
+        <v>348</v>
+      </c>
+      <c r="F322" t="s" s="63">
         <v>349</v>
-      </c>
-      <c r="F322" t="s" s="63">
-        <v>350</v>
       </c>
       <c r="G322" t="n" s="65">
         <v>46146.0</v>
@@ -15880,24 +15886,24 @@
       </c>
       <c r="S322" s="5"/>
     </row>
-    <row r="323" hidden="false" outlineLevel="1">
+    <row r="323" hidden="true" outlineLevel="1">
       <c r="A323" t="s" s="79">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B323" t="s" s="63">
         <v>89</v>
       </c>
       <c r="C323" t="s" s="63">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D323" t="n" s="63">
         <v>1.4</v>
       </c>
       <c r="E323" t="s" s="63">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="F323" t="s" s="63">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="G323" t="n" s="65">
         <v>46167.0</v>
@@ -15929,24 +15935,24 @@
       </c>
       <c r="S323" s="29"/>
     </row>
-    <row r="324" hidden="false" outlineLevel="1">
+    <row r="324" hidden="true" outlineLevel="1">
       <c r="A324" t="s" s="79">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B324" t="s" s="63">
         <v>96</v>
       </c>
       <c r="C324" t="s" s="63">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D324" t="n" s="63">
         <v>2.5</v>
       </c>
       <c r="E324" t="s" s="63">
+        <v>348</v>
+      </c>
+      <c r="F324" t="s" s="63">
         <v>349</v>
-      </c>
-      <c r="F324" t="s" s="63">
-        <v>350</v>
       </c>
       <c r="G324" t="n" s="65">
         <v>46188.0</v>
@@ -15978,24 +15984,24 @@
       </c>
       <c r="S324" s="5"/>
     </row>
-    <row r="325" hidden="false" outlineLevel="1">
+    <row r="325" hidden="true" outlineLevel="1">
       <c r="A325" t="s" s="79">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B325" t="s" s="63">
         <v>103</v>
       </c>
       <c r="C325" t="s" s="63">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D325" t="n" s="63">
         <v>1.5</v>
       </c>
       <c r="E325" t="s" s="63">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="F325" t="s" s="63">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="G325" t="n" s="65">
         <v>46209.0</v>
@@ -16027,24 +16033,24 @@
       </c>
       <c r="S325" s="29"/>
     </row>
-    <row r="326" hidden="false" outlineLevel="1">
+    <row r="326" hidden="true" outlineLevel="1">
       <c r="A326" t="s" s="79">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B326" t="s" s="63">
         <v>110</v>
       </c>
       <c r="C326" t="s" s="63">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D326" t="n" s="63">
         <v>2.6</v>
       </c>
       <c r="E326" t="s" s="63">
+        <v>348</v>
+      </c>
+      <c r="F326" t="s" s="63">
         <v>349</v>
-      </c>
-      <c r="F326" t="s" s="63">
-        <v>350</v>
       </c>
       <c r="G326" t="n" s="65">
         <v>46230.0</v>
@@ -16076,24 +16082,24 @@
       </c>
       <c r="S326" s="5"/>
     </row>
-    <row r="327" hidden="false" outlineLevel="1">
+    <row r="327" hidden="true" outlineLevel="1">
       <c r="A327" t="s" s="79">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B327" t="s" s="63">
         <v>117</v>
       </c>
       <c r="C327" t="s" s="63">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D327" t="n" s="63">
         <v>1.6</v>
       </c>
       <c r="E327" t="s" s="63">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="F327" t="s" s="63">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="G327" t="n" s="65">
         <v>46251.0</v>
@@ -16148,7 +16154,7 @@
     </row>
     <row r="329" hidden="false">
       <c r="A329" t="s" s="15">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B329" s="19"/>
       <c r="C329" s="19"/>
@@ -16192,22 +16198,22 @@
     </row>
     <row r="331" hidden="true" outlineLevel="1">
       <c r="A331" t="s" s="101">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B331" t="s" s="39">
         <v>29</v>
       </c>
       <c r="C331" t="s" s="39">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="D331" t="n" s="39">
         <v>2.1</v>
       </c>
       <c r="E331" t="s" s="39">
+        <v>366</v>
+      </c>
+      <c r="F331" t="s" s="39">
         <v>367</v>
-      </c>
-      <c r="F331" t="s" s="39">
-        <v>368</v>
       </c>
       <c r="G331" t="n" s="41">
         <v>45957.0</v>
@@ -16229,7 +16235,7 @@
       </c>
       <c r="M331" s="11"/>
       <c r="N331" t="s" s="11">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="O331" t="s" s="33">
         <v>33</v>
@@ -16247,22 +16253,22 @@
     </row>
     <row r="332" hidden="true" outlineLevel="1">
       <c r="A332" t="s" s="101">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B332" t="s" s="39">
         <v>45</v>
       </c>
       <c r="C332" t="s" s="39">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="D332" t="n" s="39">
         <v>1.1</v>
       </c>
       <c r="E332" t="s" s="39">
+        <v>366</v>
+      </c>
+      <c r="F332" t="s" s="39">
         <v>367</v>
-      </c>
-      <c r="F332" t="s" s="39">
-        <v>368</v>
       </c>
       <c r="G332" t="n" s="41">
         <v>46034.0</v>
@@ -16284,7 +16290,7 @@
       </c>
       <c r="M332" s="33"/>
       <c r="N332" t="s" s="33">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="O332" t="s" s="33">
         <v>33</v>
@@ -16302,22 +16308,22 @@
     </row>
     <row r="333" hidden="true" outlineLevel="1">
       <c r="A333" t="s" s="101">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B333" t="s" s="39">
         <v>52</v>
       </c>
       <c r="C333" t="s" s="39">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="D333" t="n" s="39">
         <v>2.2</v>
       </c>
       <c r="E333" t="s" s="39">
+        <v>366</v>
+      </c>
+      <c r="F333" t="s" s="39">
         <v>367</v>
-      </c>
-      <c r="F333" t="s" s="39">
-        <v>368</v>
       </c>
       <c r="G333" t="n" s="41">
         <v>46055.0</v>
@@ -16339,7 +16345,7 @@
       </c>
       <c r="M333" s="11"/>
       <c r="N333" t="s" s="11">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="O333" t="s" s="33">
         <v>33</v>
@@ -16357,22 +16363,22 @@
     </row>
     <row r="334" hidden="true" outlineLevel="1">
       <c r="A334" t="s" s="101">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B334" t="s" s="39">
         <v>60</v>
       </c>
       <c r="C334" t="s" s="39">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="D334" t="n" s="39">
         <v>1.2</v>
       </c>
       <c r="E334" t="s" s="39">
+        <v>366</v>
+      </c>
+      <c r="F334" t="s" s="39">
         <v>367</v>
-      </c>
-      <c r="F334" t="s" s="39">
-        <v>368</v>
       </c>
       <c r="G334" t="n" s="41">
         <v>46076.0</v>
@@ -16394,7 +16400,7 @@
       </c>
       <c r="M334" s="33"/>
       <c r="N334" t="s" s="33">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="O334" t="s" s="33">
         <v>33</v>
@@ -16412,22 +16418,22 @@
     </row>
     <row r="335" hidden="true" outlineLevel="1">
       <c r="A335" t="s" s="101">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B335" t="s" s="39">
         <v>68</v>
       </c>
       <c r="C335" t="s" s="39">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="D335" t="n" s="39">
         <v>2.3</v>
       </c>
       <c r="E335" t="s" s="39">
+        <v>366</v>
+      </c>
+      <c r="F335" t="s" s="39">
         <v>367</v>
-      </c>
-      <c r="F335" t="s" s="39">
-        <v>368</v>
       </c>
       <c r="G335" t="n" s="41">
         <v>46097.0</v>
@@ -16449,7 +16455,7 @@
       </c>
       <c r="M335" s="11"/>
       <c r="N335" t="s" s="11">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="O335" t="s" s="33">
         <v>33</v>
@@ -16467,22 +16473,22 @@
     </row>
     <row r="336" hidden="true" outlineLevel="1">
       <c r="A336" t="s" s="79">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B336" t="s" s="63">
         <v>75</v>
       </c>
       <c r="C336" t="s" s="63">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="D336" t="n" s="63">
         <v>1.3</v>
       </c>
       <c r="E336" t="s" s="63">
+        <v>366</v>
+      </c>
+      <c r="F336" t="s" s="63">
         <v>367</v>
-      </c>
-      <c r="F336" t="s" s="63">
-        <v>368</v>
       </c>
       <c r="G336" t="n" s="65">
         <v>46118.0</v>
@@ -16502,7 +16508,7 @@
       <c r="L336" s="75"/>
       <c r="M336" s="33"/>
       <c r="N336" t="s" s="33">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="O336" t="s" s="33">
         <v>33</v>
@@ -16520,22 +16526,22 @@
     </row>
     <row r="337" hidden="true" outlineLevel="1">
       <c r="A337" t="s" s="79">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B337" t="s" s="63">
         <v>82</v>
       </c>
       <c r="C337" t="s" s="63">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="D337" t="n" s="63">
         <v>2.4</v>
       </c>
       <c r="E337" t="s" s="63">
+        <v>366</v>
+      </c>
+      <c r="F337" t="s" s="63">
         <v>367</v>
-      </c>
-      <c r="F337" t="s" s="63">
-        <v>368</v>
       </c>
       <c r="G337" t="n" s="65">
         <v>46139.0</v>
@@ -16555,7 +16561,7 @@
       <c r="L337" s="75"/>
       <c r="M337" s="11"/>
       <c r="N337" t="s" s="11">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="O337" t="s" s="33">
         <v>33</v>
@@ -16573,22 +16579,22 @@
     </row>
     <row r="338" hidden="true" outlineLevel="1">
       <c r="A338" t="s" s="79">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B338" t="s" s="63">
         <v>89</v>
       </c>
       <c r="C338" t="s" s="63">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="D338" t="n" s="63">
         <v>1.4</v>
       </c>
       <c r="E338" t="s" s="63">
+        <v>366</v>
+      </c>
+      <c r="F338" t="s" s="63">
         <v>367</v>
-      </c>
-      <c r="F338" t="s" s="63">
-        <v>368</v>
       </c>
       <c r="G338" t="n" s="65">
         <v>46160.0</v>
@@ -16608,7 +16614,7 @@
       <c r="L338" s="75"/>
       <c r="M338" s="33"/>
       <c r="N338" t="s" s="33">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="O338" t="s" s="33">
         <v>33</v>
@@ -16626,22 +16632,22 @@
     </row>
     <row r="339" hidden="true" outlineLevel="1">
       <c r="A339" t="s" s="79">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B339" t="s" s="63">
         <v>96</v>
       </c>
       <c r="C339" t="s" s="63">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="D339" t="n" s="63">
         <v>2.5</v>
       </c>
       <c r="E339" t="s" s="63">
+        <v>366</v>
+      </c>
+      <c r="F339" t="s" s="63">
         <v>367</v>
-      </c>
-      <c r="F339" t="s" s="63">
-        <v>368</v>
       </c>
       <c r="G339" t="n" s="65">
         <v>46181.0</v>
@@ -16661,7 +16667,7 @@
       <c r="L339" s="75"/>
       <c r="M339" s="11"/>
       <c r="N339" t="s" s="11">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="O339" t="s" s="33">
         <v>33</v>
@@ -16679,22 +16685,22 @@
     </row>
     <row r="340" hidden="true" outlineLevel="1">
       <c r="A340" t="s" s="79">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B340" t="s" s="63">
         <v>103</v>
       </c>
       <c r="C340" t="s" s="63">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="D340" t="n" s="63">
         <v>1.5</v>
       </c>
       <c r="E340" t="s" s="63">
+        <v>366</v>
+      </c>
+      <c r="F340" t="s" s="63">
         <v>367</v>
-      </c>
-      <c r="F340" t="s" s="63">
-        <v>368</v>
       </c>
       <c r="G340" t="n" s="65">
         <v>46202.0</v>
@@ -16714,7 +16720,7 @@
       <c r="L340" s="75"/>
       <c r="M340" s="33"/>
       <c r="N340" t="s" s="33">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="O340" t="s" s="33">
         <v>33</v>
@@ -16732,22 +16738,22 @@
     </row>
     <row r="341" hidden="true" outlineLevel="1">
       <c r="A341" t="s" s="79">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B341" t="s" s="63">
         <v>110</v>
       </c>
       <c r="C341" t="s" s="63">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="D341" t="n" s="63">
         <v>2.6</v>
       </c>
       <c r="E341" t="s" s="63">
+        <v>366</v>
+      </c>
+      <c r="F341" t="s" s="63">
         <v>367</v>
-      </c>
-      <c r="F341" t="s" s="63">
-        <v>368</v>
       </c>
       <c r="G341" t="n" s="65">
         <v>46223.0</v>
@@ -16767,7 +16773,7 @@
       <c r="L341" s="75"/>
       <c r="M341" s="11"/>
       <c r="N341" t="s" s="11">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="O341" t="s" s="33">
         <v>33</v>
@@ -16785,22 +16791,22 @@
     </row>
     <row r="342" hidden="true" outlineLevel="1">
       <c r="A342" t="s" s="79">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B342" t="s" s="63">
         <v>117</v>
       </c>
       <c r="C342" t="s" s="63">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="D342" t="n" s="63">
         <v>1.6</v>
       </c>
       <c r="E342" t="s" s="63">
+        <v>366</v>
+      </c>
+      <c r="F342" t="s" s="63">
         <v>367</v>
-      </c>
-      <c r="F342" t="s" s="63">
-        <v>368</v>
       </c>
       <c r="G342" t="n" s="65">
         <v>46244.0</v>
@@ -16820,7 +16826,7 @@
       <c r="L342" s="75"/>
       <c r="M342" s="33"/>
       <c r="N342" t="s" s="33">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="O342" t="s" s="33">
         <v>33</v>
@@ -16843,7 +16849,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="10.0" customWidth="true"/>
@@ -16851,7 +16857,68 @@
     <col min="3" max="3" width="30.0" customWidth="true"/>
     <col min="4" max="4" width="20.0" customWidth="true"/>
   </cols>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>380</v>
+      </c>
+      <c r="B1" t="s">
+        <v>381</v>
+      </c>
+      <c r="C1" t="s">
+        <v>382</v>
+      </c>
+      <c r="D1" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>384</v>
+      </c>
+      <c r="B4" t="s">
+        <v>385</v>
+      </c>
+      <c r="C4" t="s">
+        <v>382</v>
+      </c>
+      <c r="D4" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="5"/>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>387</v>
+      </c>
+      <c r="B7" t="s">
+        <v>388</v>
+      </c>
+      <c r="C7" t="s">
+        <v>382</v>
+      </c>
+      <c r="D7" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="8"/>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>390</v>
+      </c>
+      <c r="B10" t="s">
+        <v>391</v>
+      </c>
+      <c r="C10" t="s">
+        <v>382</v>
+      </c>
+      <c r="D10" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="11"/>
+  </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
@@ -16867,1185 +16934,1185 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>381</v>
-      </c>
-      <c r="B1" t="n" s="112">
+        <v>393</v>
+      </c>
+      <c r="B1" t="n" s="106">
         <v>7.0</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>382</v>
-      </c>
-      <c r="B2" t="n" s="112">
+        <v>394</v>
+      </c>
+      <c r="B2" t="n" s="106">
         <v>0.0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>383</v>
-      </c>
-      <c r="B3" t="n" s="113">
+        <v>395</v>
+      </c>
+      <c r="B3" t="n" s="107">
         <v>93.4509803921569</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>384</v>
-      </c>
-      <c r="B4" t="n" s="112">
+        <v>396</v>
+      </c>
+      <c r="B4" t="n" s="106">
         <v>-21.0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>385</v>
-      </c>
-      <c r="B5" t="n" s="112">
+        <v>397</v>
+      </c>
+      <c r="B5" t="n" s="106">
         <v>54.0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>386</v>
-      </c>
-      <c r="B6" t="n" s="112">
+        <v>398</v>
+      </c>
+      <c r="B6" t="n" s="106">
         <v>69.0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>387</v>
-      </c>
-      <c r="B7" t="n" s="112">
+        <v>399</v>
+      </c>
+      <c r="B7" t="n" s="106">
         <v>90.0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>388</v>
-      </c>
-      <c r="B8" t="n" s="112">
+        <v>400</v>
+      </c>
+      <c r="B8" t="n" s="106">
         <v>101.0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>389</v>
-      </c>
-      <c r="B9" t="n" s="112">
+        <v>401</v>
+      </c>
+      <c r="B9" t="n" s="106">
         <v>116.0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>390</v>
-      </c>
-      <c r="B10" t="n" s="112">
+        <v>402</v>
+      </c>
+      <c r="B10" t="n" s="106">
         <v>109.0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>391</v>
-      </c>
-      <c r="B11" t="n" s="112">
+        <v>403</v>
+      </c>
+      <c r="B11" t="n" s="106">
         <v>109.0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>392</v>
-      </c>
-      <c r="B12" t="n" s="112">
+        <v>404</v>
+      </c>
+      <c r="B12" t="n" s="106">
         <v>109.0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>393</v>
-      </c>
-      <c r="B13" t="n" s="112">
+        <v>405</v>
+      </c>
+      <c r="B13" t="n" s="106">
         <v>109.0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>394</v>
-      </c>
-      <c r="B14" t="n" s="112">
+        <v>406</v>
+      </c>
+      <c r="B14" t="n" s="106">
         <v>116.0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>395</v>
-      </c>
-      <c r="B15" t="n" s="112">
+        <v>407</v>
+      </c>
+      <c r="B15" t="n" s="106">
         <v>130.0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>396</v>
-      </c>
-      <c r="B16" t="n" s="112">
+        <v>408</v>
+      </c>
+      <c r="B16" t="n" s="106">
         <v>49.0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>397</v>
-      </c>
-      <c r="B17" t="n" s="112">
+        <v>409</v>
+      </c>
+      <c r="B17" t="n" s="106">
         <v>84.0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>398</v>
-      </c>
-      <c r="B18" t="n" s="112">
+        <v>410</v>
+      </c>
+      <c r="B18" t="n" s="106">
         <v>105.0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>399</v>
-      </c>
-      <c r="B19" t="n" s="112">
+        <v>411</v>
+      </c>
+      <c r="B19" t="n" s="106">
         <v>57.0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>400</v>
-      </c>
-      <c r="B20" t="n" s="112">
+        <v>412</v>
+      </c>
+      <c r="B20" t="n" s="106">
         <v>57.0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>401</v>
-      </c>
-      <c r="B21" t="n" s="112">
+        <v>413</v>
+      </c>
+      <c r="B21" t="n" s="106">
         <v>64.0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>402</v>
-      </c>
-      <c r="B22" t="n" s="112">
+        <v>414</v>
+      </c>
+      <c r="B22" t="n" s="106">
         <v>71.0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>403</v>
-      </c>
-      <c r="B23" t="n" s="112">
+        <v>415</v>
+      </c>
+      <c r="B23" t="n" s="106">
         <v>78.0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>404</v>
-      </c>
-      <c r="B24" t="n" s="112">
+        <v>416</v>
+      </c>
+      <c r="B24" t="n" s="106">
         <v>85.0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>405</v>
-      </c>
-      <c r="B25" t="n" s="112">
+        <v>417</v>
+      </c>
+      <c r="B25" t="n" s="106">
         <v>92.0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>406</v>
-      </c>
-      <c r="B26" t="n" s="112">
+        <v>418</v>
+      </c>
+      <c r="B26" t="n" s="106">
         <v>99.0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>407</v>
-      </c>
-      <c r="B27" t="n" s="112">
+        <v>419</v>
+      </c>
+      <c r="B27" t="n" s="106">
         <v>106.0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>408</v>
-      </c>
-      <c r="B28" t="n" s="112">
+        <v>420</v>
+      </c>
+      <c r="B28" t="n" s="106">
         <v>171.0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>409</v>
-      </c>
-      <c r="B29" t="n" s="112">
+        <v>421</v>
+      </c>
+      <c r="B29" t="n" s="106">
         <v>15.0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>410</v>
-      </c>
-      <c r="B30" t="n" s="112">
+        <v>422</v>
+      </c>
+      <c r="B30" t="n" s="106">
         <v>151.0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>411</v>
-      </c>
-      <c r="B31" t="n" s="112">
+        <v>423</v>
+      </c>
+      <c r="B31" t="n" s="106">
         <v>172.0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>412</v>
-      </c>
-      <c r="B32" t="n" s="112">
+        <v>424</v>
+      </c>
+      <c r="B32" t="n" s="106">
         <v>192.0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>413</v>
-      </c>
-      <c r="B33" t="n" s="112">
+        <v>425</v>
+      </c>
+      <c r="B33" t="n" s="106">
         <v>213.0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>414</v>
-      </c>
-      <c r="B34" t="n" s="112">
+        <v>426</v>
+      </c>
+      <c r="B34" t="n" s="106">
         <v>0.0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>415</v>
-      </c>
-      <c r="B35" t="n" s="112">
+        <v>427</v>
+      </c>
+      <c r="B35" t="n" s="106">
         <v>0.0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>416</v>
-      </c>
-      <c r="B36" t="n" s="112">
+        <v>428</v>
+      </c>
+      <c r="B36" t="n" s="106">
         <v>0.0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>417</v>
-      </c>
-      <c r="B37" t="n" s="112">
+        <v>429</v>
+      </c>
+      <c r="B37" t="n" s="106">
         <v>0.0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>418</v>
-      </c>
-      <c r="B38" t="n" s="112">
+        <v>430</v>
+      </c>
+      <c r="B38" t="n" s="106">
         <v>152.0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>419</v>
-      </c>
-      <c r="B39" t="n" s="112">
+        <v>431</v>
+      </c>
+      <c r="B39" t="n" s="106">
         <v>173.0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>420</v>
-      </c>
-      <c r="B40" t="n" s="112">
+        <v>432</v>
+      </c>
+      <c r="B40" t="n" s="106">
         <v>194.0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>421</v>
-      </c>
-      <c r="B41" t="n" s="112">
+        <v>433</v>
+      </c>
+      <c r="B41" t="n" s="106">
         <v>26.0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>422</v>
-      </c>
-      <c r="B42" t="n" s="112">
+        <v>434</v>
+      </c>
+      <c r="B42" t="n" s="106">
         <v>7.0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>423</v>
-      </c>
-      <c r="B43" t="n" s="112">
+        <v>435</v>
+      </c>
+      <c r="B43" t="n" s="106">
         <v>7.0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>424</v>
-      </c>
-      <c r="B44" t="n" s="112">
+        <v>436</v>
+      </c>
+      <c r="B44" t="n" s="106">
         <v>7.0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>425</v>
-      </c>
-      <c r="B45" t="n" s="112">
+        <v>437</v>
+      </c>
+      <c r="B45" t="n" s="106">
         <v>7.0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>426</v>
-      </c>
-      <c r="B46" t="n" s="112">
+        <v>438</v>
+      </c>
+      <c r="B46" t="n" s="106">
         <v>7.0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>427</v>
-      </c>
-      <c r="B47" t="n" s="112">
+        <v>439</v>
+      </c>
+      <c r="B47" t="n" s="106">
         <v>7.0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>428</v>
-      </c>
-      <c r="B48" t="n" s="112">
+        <v>440</v>
+      </c>
+      <c r="B48" t="n" s="106">
         <v>7.0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>429</v>
-      </c>
-      <c r="B49" t="n" s="112">
+        <v>441</v>
+      </c>
+      <c r="B49" t="n" s="106">
         <v>7.0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>430</v>
-      </c>
-      <c r="B50" t="n" s="112">
+        <v>442</v>
+      </c>
+      <c r="B50" t="n" s="106">
         <v>7.0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>431</v>
-      </c>
-      <c r="B51" t="n" s="112">
+        <v>443</v>
+      </c>
+      <c r="B51" t="n" s="106">
         <v>7.0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>432</v>
-      </c>
-      <c r="B52" t="n" s="112">
+        <v>444</v>
+      </c>
+      <c r="B52" t="n" s="106">
         <v>7.0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>433</v>
-      </c>
-      <c r="B53" t="n" s="112">
+        <v>445</v>
+      </c>
+      <c r="B53" t="n" s="106">
         <v>0.0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>434</v>
-      </c>
-      <c r="B54" t="n" s="112">
+        <v>446</v>
+      </c>
+      <c r="B54" t="n" s="106">
         <v>0.0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>435</v>
-      </c>
-      <c r="B55" t="n" s="112">
+        <v>447</v>
+      </c>
+      <c r="B55" t="n" s="106">
         <v>0.0</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>436</v>
-      </c>
-      <c r="B56" t="n" s="112">
+        <v>448</v>
+      </c>
+      <c r="B56" t="n" s="106">
         <v>0.0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>437</v>
-      </c>
-      <c r="B57" t="n" s="112">
+        <v>449</v>
+      </c>
+      <c r="B57" t="n" s="106">
         <v>0.0</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>438</v>
-      </c>
-      <c r="B58" t="n" s="112">
+        <v>450</v>
+      </c>
+      <c r="B58" t="n" s="106">
         <v>0.0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>439</v>
-      </c>
-      <c r="B59" t="n" s="112">
+        <v>451</v>
+      </c>
+      <c r="B59" t="n" s="106">
         <v>0.0</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>440</v>
-      </c>
-      <c r="B60" t="n" s="112">
+        <v>452</v>
+      </c>
+      <c r="B60" t="n" s="106">
         <v>0.0</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>441</v>
-      </c>
-      <c r="B61" t="n" s="112">
+        <v>453</v>
+      </c>
+      <c r="B61" t="n" s="106">
         <v>0.0</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>442</v>
-      </c>
-      <c r="B62" t="n" s="112">
+        <v>454</v>
+      </c>
+      <c r="B62" t="n" s="106">
         <v>0.0</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>443</v>
-      </c>
-      <c r="B63" t="n" s="112">
+        <v>455</v>
+      </c>
+      <c r="B63" t="n" s="106">
         <v>0.0</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>444</v>
-      </c>
-      <c r="B64" t="n" s="112">
+        <v>456</v>
+      </c>
+      <c r="B64" t="n" s="106">
         <v>0.0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>445</v>
-      </c>
-      <c r="B65" t="n" s="112">
+        <v>457</v>
+      </c>
+      <c r="B65" t="n" s="106">
         <v>128.0</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>446</v>
-      </c>
-      <c r="B66" t="n" s="112">
+        <v>458</v>
+      </c>
+      <c r="B66" t="n" s="106">
         <v>205.0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>447</v>
-      </c>
-      <c r="B67" t="n" s="112">
+        <v>459</v>
+      </c>
+      <c r="B67" t="n" s="106">
         <v>205.0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>448</v>
-      </c>
-      <c r="B68" t="n" s="112">
+        <v>460</v>
+      </c>
+      <c r="B68" t="n" s="106">
         <v>226.0</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>449</v>
-      </c>
-      <c r="B69" t="n" s="112">
+        <v>461</v>
+      </c>
+      <c r="B69" t="n" s="106">
         <v>239.0</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>450</v>
-      </c>
-      <c r="B70" t="n" s="112">
+        <v>462</v>
+      </c>
+      <c r="B70" t="n" s="106">
         <v>260.0</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>451</v>
-      </c>
-      <c r="B71" t="n" s="112">
+        <v>463</v>
+      </c>
+      <c r="B71" t="n" s="106">
         <v>238.0</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>452</v>
-      </c>
-      <c r="B72" t="n" s="112">
+        <v>464</v>
+      </c>
+      <c r="B72" t="n" s="106">
         <v>259.0</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>453</v>
-      </c>
-      <c r="B73" t="n" s="112">
+        <v>465</v>
+      </c>
+      <c r="B73" t="n" s="106">
         <v>268.0</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>454</v>
-      </c>
-      <c r="B74" t="n" s="112">
+        <v>466</v>
+      </c>
+      <c r="B74" t="n" s="106">
         <v>289.0</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>455</v>
-      </c>
-      <c r="B75" t="n" s="112">
+        <v>467</v>
+      </c>
+      <c r="B75" t="n" s="106">
         <v>296.0</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>456</v>
-      </c>
-      <c r="B76" t="n" s="112">
+        <v>468</v>
+      </c>
+      <c r="B76" t="n" s="106">
         <v>317.0</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>457</v>
-      </c>
-      <c r="B77" t="n" s="112">
+        <v>469</v>
+      </c>
+      <c r="B77" t="n" s="106">
         <v>82.0</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>458</v>
-      </c>
-      <c r="B78" t="n" s="112">
+        <v>470</v>
+      </c>
+      <c r="B78" t="n" s="106">
         <v>131.0</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>459</v>
-      </c>
-      <c r="B79" t="n" s="112">
+        <v>471</v>
+      </c>
+      <c r="B79" t="n" s="106">
         <v>131.0</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>460</v>
-      </c>
-      <c r="B80" t="n" s="112">
+        <v>472</v>
+      </c>
+      <c r="B80" t="n" s="106">
         <v>123.0</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>461</v>
-      </c>
-      <c r="B81" t="n" s="112">
+        <v>473</v>
+      </c>
+      <c r="B81" t="n" s="106">
         <v>126.0</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>462</v>
-      </c>
-      <c r="B82" t="n" s="112">
+        <v>474</v>
+      </c>
+      <c r="B82" t="n" s="106">
         <v>145.0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>463</v>
-      </c>
-      <c r="B83" t="n" s="112">
+        <v>475</v>
+      </c>
+      <c r="B83" t="n" s="106">
         <v>152.0</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>464</v>
-      </c>
-      <c r="B84" t="n" s="112">
+        <v>476</v>
+      </c>
+      <c r="B84" t="n" s="106">
         <v>164.0</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>465</v>
-      </c>
-      <c r="B85" t="n" s="112">
+        <v>477</v>
+      </c>
+      <c r="B85" t="n" s="106">
         <v>179.0</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>466</v>
-      </c>
-      <c r="B86" t="n" s="112">
+        <v>478</v>
+      </c>
+      <c r="B86" t="n" s="106">
         <v>172.0</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>467</v>
-      </c>
-      <c r="B87" t="n" s="112">
+        <v>479</v>
+      </c>
+      <c r="B87" t="n" s="106">
         <v>181.0</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>468</v>
-      </c>
-      <c r="B88" t="n" s="112">
+        <v>480</v>
+      </c>
+      <c r="B88" t="n" s="106">
         <v>194.0</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>469</v>
-      </c>
-      <c r="B89" t="n" s="112">
+        <v>481</v>
+      </c>
+      <c r="B89" t="n" s="106">
         <v>97.0</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>470</v>
-      </c>
-      <c r="B90" t="n" s="112">
+        <v>482</v>
+      </c>
+      <c r="B90" t="n" s="106">
         <v>153.0</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>471</v>
-      </c>
-      <c r="B91" t="n" s="112">
+        <v>483</v>
+      </c>
+      <c r="B91" t="n" s="106">
         <v>139.0</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>472</v>
-      </c>
-      <c r="B92" t="n" s="112">
+        <v>484</v>
+      </c>
+      <c r="B92" t="n" s="106">
         <v>136.0</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>473</v>
-      </c>
-      <c r="B93" t="n" s="112">
+        <v>485</v>
+      </c>
+      <c r="B93" t="n" s="106">
         <v>125.0</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>474</v>
-      </c>
-      <c r="B94" t="n" s="112">
+        <v>486</v>
+      </c>
+      <c r="B94" t="n" s="106">
         <v>118.0</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>475</v>
-      </c>
-      <c r="B95" t="n" s="112">
+        <v>487</v>
+      </c>
+      <c r="B95" t="n" s="106">
         <v>104.0</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>476</v>
-      </c>
-      <c r="B96" t="n" s="112">
+        <v>488</v>
+      </c>
+      <c r="B96" t="n" s="106">
         <v>90.0</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>477</v>
-      </c>
-      <c r="B97" t="n" s="112">
+        <v>489</v>
+      </c>
+      <c r="B97" t="n" s="106">
         <v>83.0</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>478</v>
-      </c>
-      <c r="B98" t="n" s="112">
+        <v>490</v>
+      </c>
+      <c r="B98" t="n" s="106">
         <v>76.0</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>479</v>
-      </c>
-      <c r="B99" t="n" s="112">
+        <v>491</v>
+      </c>
+      <c r="B99" t="n" s="106">
         <v>69.0</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>480</v>
-      </c>
-      <c r="B100" t="n" s="112">
+        <v>492</v>
+      </c>
+      <c r="B100" t="n" s="106">
         <v>55.0</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s">
-        <v>481</v>
-      </c>
-      <c r="B101" t="n" s="112">
+        <v>493</v>
+      </c>
+      <c r="B101" t="n" s="106">
         <v>97.0</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s">
-        <v>482</v>
-      </c>
-      <c r="B102" t="n" s="112">
+        <v>494</v>
+      </c>
+      <c r="B102" t="n" s="106">
         <v>153.0</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>483</v>
-      </c>
-      <c r="B103" t="n" s="112">
+        <v>495</v>
+      </c>
+      <c r="B103" t="n" s="106">
         <v>137.0</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>484</v>
-      </c>
-      <c r="B104" t="n" s="112">
+        <v>496</v>
+      </c>
+      <c r="B104" t="n" s="106">
         <v>136.0</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="s">
-        <v>485</v>
-      </c>
-      <c r="B105" t="n" s="112">
+        <v>497</v>
+      </c>
+      <c r="B105" t="n" s="106">
         <v>125.0</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="s">
-        <v>486</v>
-      </c>
-      <c r="B106" t="n" s="112">
+        <v>498</v>
+      </c>
+      <c r="B106" t="n" s="106">
         <v>118.0</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="s">
-        <v>487</v>
-      </c>
-      <c r="B107" t="n" s="112">
+        <v>499</v>
+      </c>
+      <c r="B107" t="n" s="106">
         <v>104.0</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s">
-        <v>488</v>
-      </c>
-      <c r="B108" t="n" s="112">
+        <v>500</v>
+      </c>
+      <c r="B108" t="n" s="106">
         <v>90.0</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s">
-        <v>489</v>
-      </c>
-      <c r="B109" t="n" s="112">
+        <v>501</v>
+      </c>
+      <c r="B109" t="n" s="106">
         <v>83.0</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="s">
-        <v>490</v>
-      </c>
-      <c r="B110" t="n" s="112">
+        <v>502</v>
+      </c>
+      <c r="B110" t="n" s="106">
         <v>76.0</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>491</v>
-      </c>
-      <c r="B111" t="n" s="112">
+        <v>503</v>
+      </c>
+      <c r="B111" t="n" s="106">
         <v>69.0</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="s">
-        <v>492</v>
-      </c>
-      <c r="B112" t="n" s="112">
+        <v>504</v>
+      </c>
+      <c r="B112" t="n" s="106">
         <v>55.0</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="s">
-        <v>493</v>
-      </c>
-      <c r="B113" t="n" s="112">
+        <v>505</v>
+      </c>
+      <c r="B113" t="n" s="106">
         <v>53.0</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="s">
-        <v>494</v>
-      </c>
-      <c r="B114" t="n" s="112">
+        <v>506</v>
+      </c>
+      <c r="B114" t="n" s="106">
         <v>102.0</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s">
-        <v>495</v>
-      </c>
-      <c r="B115" t="n" s="112">
+        <v>507</v>
+      </c>
+      <c r="B115" t="n" s="106">
         <v>102.0</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>496</v>
-      </c>
-      <c r="B116" t="n" s="112">
+        <v>508</v>
+      </c>
+      <c r="B116" t="n" s="106">
         <v>102.0</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>497</v>
-      </c>
-      <c r="B117" t="n" s="112">
+        <v>509</v>
+      </c>
+      <c r="B117" t="n" s="106">
         <v>102.0</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="s">
-        <v>498</v>
-      </c>
-      <c r="B118" t="n" s="112">
+        <v>510</v>
+      </c>
+      <c r="B118" t="n" s="106">
         <v>102.0</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="s">
-        <v>499</v>
-      </c>
-      <c r="B119" t="n" s="112">
+        <v>511</v>
+      </c>
+      <c r="B119" t="n" s="106">
         <v>88.0</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="s">
-        <v>500</v>
-      </c>
-      <c r="B120" t="n" s="112">
+        <v>512</v>
+      </c>
+      <c r="B120" t="n" s="106">
         <v>88.0</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="s">
-        <v>501</v>
-      </c>
-      <c r="B121" t="n" s="112">
+        <v>513</v>
+      </c>
+      <c r="B121" t="n" s="106">
         <v>88.0</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="s">
-        <v>502</v>
-      </c>
-      <c r="B122" t="n" s="112">
+        <v>514</v>
+      </c>
+      <c r="B122" t="n" s="106">
         <v>89.0</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="s">
-        <v>503</v>
-      </c>
-      <c r="B123" t="n" s="112">
+        <v>515</v>
+      </c>
+      <c r="B123" t="n" s="106">
         <v>89.0</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="s">
-        <v>504</v>
-      </c>
-      <c r="B124" t="n" s="112">
+        <v>516</v>
+      </c>
+      <c r="B124" t="n" s="106">
         <v>89.0</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="s">
-        <v>505</v>
-      </c>
-      <c r="B125" t="n" s="112">
+        <v>517</v>
+      </c>
+      <c r="B125" t="n" s="106">
         <v>67.0</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="s">
-        <v>506</v>
-      </c>
-      <c r="B126" t="n" s="112">
+        <v>518</v>
+      </c>
+      <c r="B126" t="n" s="106">
         <v>115.0</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="s">
-        <v>507</v>
-      </c>
-      <c r="B127" t="n" s="112">
+        <v>519</v>
+      </c>
+      <c r="B127" t="n" s="106">
         <v>109.0</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="s">
-        <v>508</v>
-      </c>
-      <c r="B128" t="n" s="112">
+        <v>520</v>
+      </c>
+      <c r="B128" t="n" s="106">
         <v>97.0</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="s">
-        <v>509</v>
-      </c>
-      <c r="B129" t="n" s="112">
+        <v>521</v>
+      </c>
+      <c r="B129" t="n" s="106">
         <v>95.0</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="s">
-        <v>510</v>
-      </c>
-      <c r="B130" t="n" s="112">
+        <v>522</v>
+      </c>
+      <c r="B130" t="n" s="106">
         <v>88.0</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="s">
-        <v>511</v>
-      </c>
-      <c r="B131" t="n" s="112">
+        <v>523</v>
+      </c>
+      <c r="B131" t="n" s="106">
         <v>74.0</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="s">
-        <v>512</v>
-      </c>
-      <c r="B132" t="n" s="112">
+        <v>524</v>
+      </c>
+      <c r="B132" t="n" s="106">
         <v>60.0</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="s">
-        <v>513</v>
-      </c>
-      <c r="B133" t="n" s="112">
+        <v>525</v>
+      </c>
+      <c r="B133" t="n" s="106">
         <v>53.0</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="s">
-        <v>514</v>
-      </c>
-      <c r="B134" t="n" s="112">
+        <v>526</v>
+      </c>
+      <c r="B134" t="n" s="106">
         <v>46.0</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="s">
-        <v>515</v>
-      </c>
-      <c r="B135" t="n" s="112">
+        <v>527</v>
+      </c>
+      <c r="B135" t="n" s="106">
         <v>39.0</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="s">
-        <v>516</v>
-      </c>
-      <c r="B136" t="n" s="112">
+        <v>528</v>
+      </c>
+      <c r="B136" t="n" s="106">
         <v>25.0</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="s">
-        <v>517</v>
-      </c>
-      <c r="B137" t="n" s="112">
+        <v>529</v>
+      </c>
+      <c r="B137" t="n" s="106">
         <v>74.0</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="s">
-        <v>518</v>
-      </c>
-      <c r="B138" t="n" s="112">
+        <v>530</v>
+      </c>
+      <c r="B138" t="n" s="106">
         <v>123.0</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="s">
-        <v>519</v>
-      </c>
-      <c r="B139" t="n" s="112">
+        <v>531</v>
+      </c>
+      <c r="B139" t="n" s="106">
         <v>123.0</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="s">
-        <v>520</v>
-      </c>
-      <c r="B140" t="n" s="112">
+        <v>532</v>
+      </c>
+      <c r="B140" t="n" s="106">
         <v>123.0</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="s">
-        <v>521</v>
-      </c>
-      <c r="B141" t="n" s="112">
+        <v>533</v>
+      </c>
+      <c r="B141" t="n" s="106">
         <v>123.0</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="s">
-        <v>522</v>
-      </c>
-      <c r="B142" t="n" s="112">
+        <v>534</v>
+      </c>
+      <c r="B142" t="n" s="106">
         <v>123.0</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="s">
-        <v>523</v>
-      </c>
-      <c r="B143" t="n" s="112">
+        <v>535</v>
+      </c>
+      <c r="B143" t="n" s="106">
         <v>109.0</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="s">
-        <v>524</v>
-      </c>
-      <c r="B144" t="n" s="112">
+        <v>536</v>
+      </c>
+      <c r="B144" t="n" s="106">
         <v>109.0</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="s">
-        <v>525</v>
-      </c>
-      <c r="B145" t="n" s="112">
+        <v>537</v>
+      </c>
+      <c r="B145" t="n" s="106">
         <v>109.0</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="s">
-        <v>526</v>
-      </c>
-      <c r="B146" t="n" s="112">
+        <v>538</v>
+      </c>
+      <c r="B146" t="n" s="106">
         <v>110.0</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="s">
-        <v>527</v>
-      </c>
-      <c r="B147" t="n" s="112">
+        <v>539</v>
+      </c>
+      <c r="B147" t="n" s="106">
         <v>110.0</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="s">
-        <v>528</v>
-      </c>
-      <c r="B148" t="n" s="112">
+        <v>540</v>
+      </c>
+      <c r="B148" t="n" s="106">
         <v>110.0</v>
       </c>
     </row>

--- a/03. CMH116 OFCI Log REV2.0.xlsx
+++ b/03. CMH116 OFCI Log REV2.0.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6971" uniqueCount="537">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6968" uniqueCount="537">
   <si>
     <t/>
   </si>
@@ -2495,7 +2495,7 @@
       <c r="R7" s="17"/>
       <c r="S7" s="17"/>
     </row>
-    <row r="8" hidden="false" outlineLevel="1">
+    <row r="8" hidden="true" outlineLevel="1">
       <c r="A8" s="25"/>
       <c r="B8" s="5"/>
       <c r="C8" s="5"/>
@@ -2516,7 +2516,7 @@
       <c r="R8" s="5"/>
       <c r="S8" s="5"/>
     </row>
-    <row r="9" hidden="false" outlineLevel="1">
+    <row r="9" hidden="true" outlineLevel="1">
       <c r="A9" t="s" s="27">
         <v>25</v>
       </c>
@@ -2545,7 +2545,7 @@
       </c>
       <c r="S9" s="29"/>
     </row>
-    <row r="10" hidden="false" outlineLevel="2">
+    <row r="10" hidden="true" outlineLevel="2">
       <c r="A10" t="s" s="37">
         <v>28</v>
       </c>
@@ -2600,7 +2600,7 @@
         <v>45963.0</v>
       </c>
     </row>
-    <row r="11" hidden="false" outlineLevel="2">
+    <row r="11" hidden="true" outlineLevel="2">
       <c r="A11" t="s" s="37">
         <v>28</v>
       </c>
@@ -2655,7 +2655,7 @@
         <v>45963.0</v>
       </c>
     </row>
-    <row r="12" hidden="false" outlineLevel="2">
+    <row r="12" hidden="true" outlineLevel="2">
       <c r="A12" t="s" s="37">
         <v>28</v>
       </c>
@@ -2710,7 +2710,7 @@
         <v>45963.0</v>
       </c>
     </row>
-    <row r="13" hidden="false" outlineLevel="2">
+    <row r="13" hidden="true" outlineLevel="2">
       <c r="A13" t="s" s="37">
         <v>28</v>
       </c>
@@ -2765,7 +2765,7 @@
         <v>45963.0</v>
       </c>
     </row>
-    <row r="14" hidden="false" outlineLevel="2">
+    <row r="14" hidden="true" outlineLevel="2">
       <c r="A14" t="s" s="37">
         <v>28</v>
       </c>
@@ -2816,7 +2816,7 @@
         <v>45963.0</v>
       </c>
     </row>
-    <row r="15" hidden="false" outlineLevel="2">
+    <row r="15" hidden="true" outlineLevel="2">
       <c r="A15" t="s" s="37">
         <v>39</v>
       </c>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="S15" s="5"/>
     </row>
-    <row r="16" hidden="false" outlineLevel="2">
+    <row r="16" hidden="true" outlineLevel="2">
       <c r="A16" t="s" s="37">
         <v>42</v>
       </c>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="S16" s="5"/>
     </row>
-    <row r="17" hidden="false" outlineLevel="1">
+    <row r="17" hidden="true" outlineLevel="1">
       <c r="A17" t="s" s="27">
         <v>43</v>
       </c>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="S21" s="5"/>
     </row>
-    <row r="22" hidden="false" outlineLevel="1">
+    <row r="22" hidden="true" outlineLevel="1">
       <c r="A22" t="s" s="27">
         <v>50</v>
       </c>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="S26" s="5"/>
     </row>
-    <row r="27" hidden="false" outlineLevel="1">
+    <row r="27" hidden="true" outlineLevel="1">
       <c r="A27" t="s" s="27">
         <v>58</v>
       </c>
@@ -3575,7 +3575,7 @@
       </c>
       <c r="S31" s="5"/>
     </row>
-    <row r="32" hidden="false" outlineLevel="1">
+    <row r="32" hidden="true" outlineLevel="1">
       <c r="A32" t="s" s="27">
         <v>66</v>
       </c>
@@ -3604,7 +3604,7 @@
       </c>
       <c r="S32" s="53"/>
     </row>
-    <row r="33" hidden="false" outlineLevel="2">
+    <row r="33" hidden="true" outlineLevel="2">
       <c r="A33" t="s" s="63">
         <v>67</v>
       </c>
@@ -3655,7 +3655,7 @@
         <v>46104.0</v>
       </c>
     </row>
-    <row r="34" hidden="false" outlineLevel="2">
+    <row r="34" hidden="true" outlineLevel="2">
       <c r="A34" t="s" s="63">
         <v>67</v>
       </c>
@@ -3706,7 +3706,7 @@
         <v>46104.0</v>
       </c>
     </row>
-    <row r="35" hidden="false" outlineLevel="2">
+    <row r="35" hidden="true" outlineLevel="2">
       <c r="A35" t="s" s="63">
         <v>71</v>
       </c>
@@ -3747,7 +3747,7 @@
       </c>
       <c r="S35" s="17"/>
     </row>
-    <row r="36" hidden="false" outlineLevel="2">
+    <row r="36" hidden="true" outlineLevel="2">
       <c r="A36" t="s" s="63">
         <v>72</v>
       </c>
@@ -3792,7 +3792,7 @@
       </c>
       <c r="S36" s="5"/>
     </row>
-    <row r="37" hidden="false" outlineLevel="1">
+    <row r="37" hidden="true" outlineLevel="1">
       <c r="A37" t="s" s="27">
         <v>73</v>
       </c>
@@ -3821,7 +3821,7 @@
       </c>
       <c r="S37" s="53"/>
     </row>
-    <row r="38" hidden="false" outlineLevel="2">
+    <row r="38" hidden="true" outlineLevel="2">
       <c r="A38" t="s" s="63">
         <v>74</v>
       </c>
@@ -3872,7 +3872,7 @@
         <v>46125.0</v>
       </c>
     </row>
-    <row r="39" hidden="false" outlineLevel="2">
+    <row r="39" hidden="true" outlineLevel="2">
       <c r="A39" t="s" s="63">
         <v>74</v>
       </c>
@@ -3923,7 +3923,7 @@
         <v>46125.0</v>
       </c>
     </row>
-    <row r="40" hidden="false" outlineLevel="2">
+    <row r="40" hidden="true" outlineLevel="2">
       <c r="A40" t="s" s="63">
         <v>78</v>
       </c>
@@ -3964,7 +3964,7 @@
       </c>
       <c r="S40" s="17"/>
     </row>
-    <row r="41" hidden="false" outlineLevel="2">
+    <row r="41" hidden="true" outlineLevel="2">
       <c r="A41" t="s" s="63">
         <v>79</v>
       </c>
@@ -4009,7 +4009,7 @@
       </c>
       <c r="S41" s="5"/>
     </row>
-    <row r="42" hidden="false" outlineLevel="1">
+    <row r="42" hidden="true" outlineLevel="1">
       <c r="A42" t="s" s="27">
         <v>80</v>
       </c>
@@ -4038,7 +4038,7 @@
       </c>
       <c r="S42" s="53"/>
     </row>
-    <row r="43" hidden="false" outlineLevel="2">
+    <row r="43" hidden="true" outlineLevel="2">
       <c r="A43" t="s" s="63">
         <v>81</v>
       </c>
@@ -4089,7 +4089,7 @@
         <v>46146.0</v>
       </c>
     </row>
-    <row r="44" hidden="false" outlineLevel="2">
+    <row r="44" hidden="true" outlineLevel="2">
       <c r="A44" t="s" s="63">
         <v>81</v>
       </c>
@@ -4140,7 +4140,7 @@
         <v>46146.0</v>
       </c>
     </row>
-    <row r="45" hidden="false" outlineLevel="2">
+    <row r="45" hidden="true" outlineLevel="2">
       <c r="A45" t="s" s="63">
         <v>85</v>
       </c>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="S45" s="17"/>
     </row>
-    <row r="46" hidden="false" outlineLevel="2">
+    <row r="46" hidden="true" outlineLevel="2">
       <c r="A46" t="s" s="63">
         <v>86</v>
       </c>
@@ -4226,7 +4226,7 @@
       </c>
       <c r="S46" s="5"/>
     </row>
-    <row r="47" hidden="false" outlineLevel="1">
+    <row r="47" hidden="true" outlineLevel="1">
       <c r="A47" t="s" s="27">
         <v>87</v>
       </c>
@@ -4255,7 +4255,7 @@
       </c>
       <c r="S47" s="53"/>
     </row>
-    <row r="48" hidden="false" outlineLevel="2">
+    <row r="48" hidden="true" outlineLevel="2">
       <c r="A48" t="s" s="63">
         <v>88</v>
       </c>
@@ -4306,7 +4306,7 @@
         <v>46167.0</v>
       </c>
     </row>
-    <row r="49" hidden="false" outlineLevel="2">
+    <row r="49" hidden="true" outlineLevel="2">
       <c r="A49" t="s" s="63">
         <v>88</v>
       </c>
@@ -4357,7 +4357,7 @@
         <v>46167.0</v>
       </c>
     </row>
-    <row r="50" hidden="false" outlineLevel="2">
+    <row r="50" hidden="true" outlineLevel="2">
       <c r="A50" t="s" s="63">
         <v>92</v>
       </c>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="S50" s="17"/>
     </row>
-    <row r="51" hidden="false" outlineLevel="2">
+    <row r="51" hidden="true" outlineLevel="2">
       <c r="A51" t="s" s="63">
         <v>93</v>
       </c>
@@ -4443,7 +4443,7 @@
       </c>
       <c r="S51" s="5"/>
     </row>
-    <row r="52" hidden="false" outlineLevel="1">
+    <row r="52" hidden="true" outlineLevel="1">
       <c r="A52" t="s" s="27">
         <v>94</v>
       </c>
@@ -4472,7 +4472,7 @@
       </c>
       <c r="S52" s="53"/>
     </row>
-    <row r="53" hidden="false" outlineLevel="2">
+    <row r="53" hidden="true" outlineLevel="2">
       <c r="A53" t="s" s="63">
         <v>95</v>
       </c>
@@ -4523,7 +4523,7 @@
         <v>46188.0</v>
       </c>
     </row>
-    <row r="54" hidden="false" outlineLevel="2">
+    <row r="54" hidden="true" outlineLevel="2">
       <c r="A54" t="s" s="63">
         <v>95</v>
       </c>
@@ -4574,7 +4574,7 @@
         <v>46188.0</v>
       </c>
     </row>
-    <row r="55" hidden="false" outlineLevel="2">
+    <row r="55" hidden="true" outlineLevel="2">
       <c r="A55" t="s" s="63">
         <v>99</v>
       </c>
@@ -4615,7 +4615,7 @@
       </c>
       <c r="S55" s="17"/>
     </row>
-    <row r="56" hidden="false" outlineLevel="2">
+    <row r="56" hidden="true" outlineLevel="2">
       <c r="A56" t="s" s="63">
         <v>100</v>
       </c>
@@ -4660,7 +4660,7 @@
       </c>
       <c r="S56" s="5"/>
     </row>
-    <row r="57" hidden="false" outlineLevel="1">
+    <row r="57" hidden="true" outlineLevel="1">
       <c r="A57" t="s" s="27">
         <v>101</v>
       </c>
@@ -4689,7 +4689,7 @@
       </c>
       <c r="S57" s="53"/>
     </row>
-    <row r="58" hidden="false" outlineLevel="2">
+    <row r="58" hidden="true" outlineLevel="2">
       <c r="A58" t="s" s="63">
         <v>102</v>
       </c>
@@ -4740,7 +4740,7 @@
         <v>46209.0</v>
       </c>
     </row>
-    <row r="59" hidden="false" outlineLevel="2">
+    <row r="59" hidden="true" outlineLevel="2">
       <c r="A59" t="s" s="63">
         <v>102</v>
       </c>
@@ -4791,7 +4791,7 @@
         <v>46209.0</v>
       </c>
     </row>
-    <row r="60" hidden="false" outlineLevel="2">
+    <row r="60" hidden="true" outlineLevel="2">
       <c r="A60" t="s" s="63">
         <v>106</v>
       </c>
@@ -4832,7 +4832,7 @@
       </c>
       <c r="S60" s="17"/>
     </row>
-    <row r="61" hidden="false" outlineLevel="2">
+    <row r="61" hidden="true" outlineLevel="2">
       <c r="A61" t="s" s="63">
         <v>107</v>
       </c>
@@ -4877,7 +4877,7 @@
       </c>
       <c r="S61" s="5"/>
     </row>
-    <row r="62" hidden="false" outlineLevel="1">
+    <row r="62" hidden="true" outlineLevel="1">
       <c r="A62" t="s" s="27">
         <v>108</v>
       </c>
@@ -4906,7 +4906,7 @@
       </c>
       <c r="S62" s="53"/>
     </row>
-    <row r="63" hidden="false" outlineLevel="2">
+    <row r="63" hidden="true" outlineLevel="2">
       <c r="A63" t="s" s="63">
         <v>109</v>
       </c>
@@ -4957,7 +4957,7 @@
         <v>46230.0</v>
       </c>
     </row>
-    <row r="64" hidden="false" outlineLevel="2">
+    <row r="64" hidden="true" outlineLevel="2">
       <c r="A64" t="s" s="63">
         <v>109</v>
       </c>
@@ -5008,7 +5008,7 @@
         <v>46230.0</v>
       </c>
     </row>
-    <row r="65" hidden="false" outlineLevel="2">
+    <row r="65" hidden="true" outlineLevel="2">
       <c r="A65" t="s" s="63">
         <v>113</v>
       </c>
@@ -5049,7 +5049,7 @@
       </c>
       <c r="S65" s="17"/>
     </row>
-    <row r="66" hidden="false" outlineLevel="2">
+    <row r="66" hidden="true" outlineLevel="2">
       <c r="A66" t="s" s="63">
         <v>114</v>
       </c>
@@ -5094,7 +5094,7 @@
       </c>
       <c r="S66" s="5"/>
     </row>
-    <row r="67" hidden="false" outlineLevel="1">
+    <row r="67" hidden="true" outlineLevel="1">
       <c r="A67" t="s" s="27">
         <v>115</v>
       </c>
@@ -8946,7 +8946,7 @@
       <c r="R166" s="17"/>
       <c r="S166" s="19"/>
     </row>
-    <row r="167" hidden="false" outlineLevel="1">
+    <row r="167" hidden="true" outlineLevel="1">
       <c r="A167" s="25"/>
       <c r="B167" s="5"/>
       <c r="C167" s="5"/>
@@ -8967,7 +8967,7 @@
       <c r="R167" s="5"/>
       <c r="S167" s="5"/>
     </row>
-    <row r="168" hidden="false" outlineLevel="1">
+    <row r="168" hidden="true" outlineLevel="1">
       <c r="A168" t="s" s="27">
         <v>25</v>
       </c>
@@ -8994,7 +8994,7 @@
       <c r="R168" s="29"/>
       <c r="S168" s="53"/>
     </row>
-    <row r="169" hidden="false" outlineLevel="2">
+    <row r="169" hidden="true" outlineLevel="2">
       <c r="A169" t="s" s="63">
         <v>158</v>
       </c>
@@ -9043,7 +9043,7 @@
       </c>
       <c r="S169" s="5"/>
     </row>
-    <row r="170" hidden="false" outlineLevel="2">
+    <row r="170" hidden="true" outlineLevel="2">
       <c r="A170" t="s" s="37">
         <v>158</v>
       </c>
@@ -9094,7 +9094,7 @@
       </c>
       <c r="S170" s="5"/>
     </row>
-    <row r="171" hidden="false" outlineLevel="2">
+    <row r="171" hidden="true" outlineLevel="2">
       <c r="A171" t="s" s="37">
         <v>158</v>
       </c>
@@ -9145,7 +9145,7 @@
       </c>
       <c r="S171" s="5"/>
     </row>
-    <row r="172" hidden="false" outlineLevel="2">
+    <row r="172" hidden="true" outlineLevel="2">
       <c r="A172" t="s" s="37">
         <v>158</v>
       </c>
@@ -9196,7 +9196,7 @@
       </c>
       <c r="S172" s="5"/>
     </row>
-    <row r="173" hidden="false" outlineLevel="2">
+    <row r="173" hidden="true" outlineLevel="2">
       <c r="A173" t="s" s="95">
         <v>158</v>
       </c>
@@ -9243,7 +9243,7 @@
       </c>
       <c r="S173" s="5"/>
     </row>
-    <row r="174" hidden="false" outlineLevel="1">
+    <row r="174" hidden="true" outlineLevel="1">
       <c r="A174" t="s" s="27">
         <v>43</v>
       </c>
@@ -9272,7 +9272,7 @@
       </c>
       <c r="S174" s="53"/>
     </row>
-    <row r="175" hidden="false" outlineLevel="2">
+    <row r="175" hidden="true" outlineLevel="2">
       <c r="A175" t="s" s="37">
         <v>168</v>
       </c>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="S175" s="5"/>
     </row>
-    <row r="176" hidden="false" outlineLevel="2">
+    <row r="176" hidden="true" outlineLevel="2">
       <c r="A176" t="s" s="37">
         <v>168</v>
       </c>
@@ -9374,7 +9374,7 @@
       </c>
       <c r="S176" s="5"/>
     </row>
-    <row r="177" hidden="false" outlineLevel="1">
+    <row r="177" hidden="true" outlineLevel="1">
       <c r="A177" t="s" s="27">
         <v>50</v>
       </c>
@@ -9403,7 +9403,7 @@
       </c>
       <c r="S177" s="53"/>
     </row>
-    <row r="178" hidden="false" outlineLevel="2">
+    <row r="178" hidden="true" outlineLevel="2">
       <c r="A178" t="s" s="37">
         <v>171</v>
       </c>
@@ -9454,7 +9454,7 @@
       </c>
       <c r="S178" s="5"/>
     </row>
-    <row r="179" hidden="false" outlineLevel="2">
+    <row r="179" hidden="true" outlineLevel="2">
       <c r="A179" t="s" s="37">
         <v>171</v>
       </c>
@@ -9505,7 +9505,7 @@
       </c>
       <c r="S179" s="5"/>
     </row>
-    <row r="180" hidden="false" outlineLevel="1">
+    <row r="180" hidden="true" outlineLevel="1">
       <c r="A180" t="s" s="27">
         <v>58</v>
       </c>
@@ -9534,7 +9534,7 @@
       </c>
       <c r="S180" s="53"/>
     </row>
-    <row r="181" hidden="false" outlineLevel="2">
+    <row r="181" hidden="true" outlineLevel="2">
       <c r="A181" t="s" s="37">
         <v>174</v>
       </c>
@@ -9585,7 +9585,7 @@
       </c>
       <c r="S181" s="5"/>
     </row>
-    <row r="182" hidden="false" outlineLevel="2">
+    <row r="182" hidden="true" outlineLevel="2">
       <c r="A182" t="s" s="37">
         <v>174</v>
       </c>
@@ -9636,7 +9636,7 @@
       </c>
       <c r="S182" s="5"/>
     </row>
-    <row r="183" hidden="false" outlineLevel="1">
+    <row r="183" hidden="true" outlineLevel="1">
       <c r="A183" t="s" s="27">
         <v>66</v>
       </c>
@@ -9665,7 +9665,7 @@
       </c>
       <c r="S183" s="53"/>
     </row>
-    <row r="184" hidden="false" outlineLevel="2">
+    <row r="184" hidden="true" outlineLevel="2">
       <c r="A184" t="s" s="37">
         <v>177</v>
       </c>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="S184" s="5"/>
     </row>
-    <row r="185" hidden="false" outlineLevel="2">
+    <row r="185" hidden="true" outlineLevel="2">
       <c r="A185" t="s" s="37">
         <v>177</v>
       </c>
@@ -9767,7 +9767,7 @@
       </c>
       <c r="S185" s="5"/>
     </row>
-    <row r="186" hidden="false" outlineLevel="1">
+    <row r="186" hidden="true" outlineLevel="1">
       <c r="A186" t="s" s="27">
         <v>73</v>
       </c>
@@ -9796,7 +9796,7 @@
       </c>
       <c r="S186" s="53"/>
     </row>
-    <row r="187" hidden="false" outlineLevel="2">
+    <row r="187" hidden="true" outlineLevel="2">
       <c r="A187" t="s" s="37">
         <v>180</v>
       </c>
@@ -9847,7 +9847,7 @@
       </c>
       <c r="S187" s="5"/>
     </row>
-    <row r="188" hidden="false" outlineLevel="2">
+    <row r="188" hidden="true" outlineLevel="2">
       <c r="A188" t="s" s="37">
         <v>180</v>
       </c>
@@ -9898,7 +9898,7 @@
       </c>
       <c r="S188" s="5"/>
     </row>
-    <row r="189" hidden="false" outlineLevel="1">
+    <row r="189" hidden="true" outlineLevel="1">
       <c r="A189" t="s" s="27">
         <v>80</v>
       </c>
@@ -9927,7 +9927,7 @@
       </c>
       <c r="S189" s="53"/>
     </row>
-    <row r="190" hidden="false" outlineLevel="2">
+    <row r="190" hidden="true" outlineLevel="2">
       <c r="A190" t="s" s="63">
         <v>183</v>
       </c>
@@ -9978,7 +9978,7 @@
       </c>
       <c r="S190" s="5"/>
     </row>
-    <row r="191" hidden="false" outlineLevel="2">
+    <row r="191" hidden="true" outlineLevel="2">
       <c r="A191" t="s" s="63">
         <v>183</v>
       </c>
@@ -10029,7 +10029,7 @@
       </c>
       <c r="S191" s="5"/>
     </row>
-    <row r="192" hidden="false" outlineLevel="2">
+    <row r="192" hidden="true" outlineLevel="2">
       <c r="A192" t="s" s="37">
         <v>183</v>
       </c>
@@ -10078,7 +10078,7 @@
       </c>
       <c r="S192" s="5"/>
     </row>
-    <row r="193" hidden="false" outlineLevel="1">
+    <row r="193" hidden="true" outlineLevel="1">
       <c r="A193" t="s" s="27">
         <v>87</v>
       </c>
@@ -10107,7 +10107,7 @@
       </c>
       <c r="S193" s="53"/>
     </row>
-    <row r="194" hidden="false" outlineLevel="2">
+    <row r="194" hidden="true" outlineLevel="2">
       <c r="A194" t="s" s="63">
         <v>188</v>
       </c>
@@ -10158,7 +10158,7 @@
       </c>
       <c r="S194" s="5"/>
     </row>
-    <row r="195" hidden="false" outlineLevel="2">
+    <row r="195" hidden="true" outlineLevel="2">
       <c r="A195" t="s" s="63">
         <v>188</v>
       </c>
@@ -10209,7 +10209,7 @@
       </c>
       <c r="S195" s="5"/>
     </row>
-    <row r="196" hidden="false" outlineLevel="1">
+    <row r="196" hidden="true" outlineLevel="1">
       <c r="A196" t="s" s="27">
         <v>94</v>
       </c>
@@ -10238,7 +10238,7 @@
       </c>
       <c r="S196" s="53"/>
     </row>
-    <row r="197" hidden="false" outlineLevel="2">
+    <row r="197" hidden="true" outlineLevel="2">
       <c r="A197" t="s" s="63">
         <v>191</v>
       </c>
@@ -10289,7 +10289,7 @@
       </c>
       <c r="S197" s="5"/>
     </row>
-    <row r="198" hidden="false" outlineLevel="2">
+    <row r="198" hidden="true" outlineLevel="2">
       <c r="A198" t="s" s="63">
         <v>191</v>
       </c>
@@ -10340,7 +10340,7 @@
       </c>
       <c r="S198" s="5"/>
     </row>
-    <row r="199" hidden="false" outlineLevel="1">
+    <row r="199" hidden="true" outlineLevel="1">
       <c r="A199" t="s" s="27">
         <v>101</v>
       </c>
@@ -10369,7 +10369,7 @@
       </c>
       <c r="S199" s="53"/>
     </row>
-    <row r="200" hidden="false" outlineLevel="2">
+    <row r="200" hidden="true" outlineLevel="2">
       <c r="A200" t="s" s="63">
         <v>194</v>
       </c>
@@ -10420,7 +10420,7 @@
       </c>
       <c r="S200" s="5"/>
     </row>
-    <row r="201" hidden="false" outlineLevel="2">
+    <row r="201" hidden="true" outlineLevel="2">
       <c r="A201" t="s" s="63">
         <v>194</v>
       </c>
@@ -10471,7 +10471,7 @@
       </c>
       <c r="S201" s="5"/>
     </row>
-    <row r="202" hidden="false" outlineLevel="1">
+    <row r="202" hidden="true" outlineLevel="1">
       <c r="A202" t="s" s="27">
         <v>108</v>
       </c>
@@ -10500,7 +10500,7 @@
       </c>
       <c r="S202" s="53"/>
     </row>
-    <row r="203" hidden="false" outlineLevel="2">
+    <row r="203" hidden="true" outlineLevel="2">
       <c r="A203" t="s" s="63">
         <v>198</v>
       </c>
@@ -10551,7 +10551,7 @@
       </c>
       <c r="S203" s="5"/>
     </row>
-    <row r="204" hidden="false" outlineLevel="2">
+    <row r="204" hidden="true" outlineLevel="2">
       <c r="A204" t="s" s="63">
         <v>198</v>
       </c>
@@ -10602,7 +10602,7 @@
       </c>
       <c r="S204" s="5"/>
     </row>
-    <row r="205" hidden="false" outlineLevel="1">
+    <row r="205" hidden="true" outlineLevel="1">
       <c r="A205" t="s" s="27">
         <v>115</v>
       </c>
@@ -10631,7 +10631,7 @@
       </c>
       <c r="S205" s="53"/>
     </row>
-    <row r="206" hidden="false" outlineLevel="2">
+    <row r="206" hidden="true" outlineLevel="2">
       <c r="A206" t="s" s="63">
         <v>201</v>
       </c>
@@ -10682,7 +10682,7 @@
       </c>
       <c r="S206" s="5"/>
     </row>
-    <row r="207" hidden="false" outlineLevel="2">
+    <row r="207" hidden="true" outlineLevel="2">
       <c r="A207" t="s" s="63">
         <v>201</v>
       </c>
@@ -11529,40 +11529,42 @@
       <c r="S226" s="5"/>
     </row>
     <row r="227" hidden="true" outlineLevel="1">
-      <c r="A227" t="s" s="75">
+      <c r="A227" t="s" s="97">
         <v>236</v>
       </c>
-      <c r="B227" t="s" s="65">
+      <c r="B227" t="s" s="39">
         <v>45</v>
       </c>
-      <c r="C227" t="s" s="65">
+      <c r="C227" t="s" s="39">
         <v>231</v>
       </c>
-      <c r="D227" t="n" s="65">
+      <c r="D227" t="n" s="39">
         <v>1.1</v>
       </c>
-      <c r="E227" t="s" s="65">
+      <c r="E227" t="s" s="39">
         <v>233</v>
       </c>
-      <c r="F227" t="s" s="65">
+      <c r="F227" t="s" s="39">
         <v>234</v>
       </c>
-      <c r="G227" t="n" s="67">
+      <c r="G227" t="n" s="41">
         <v>46048.0</v>
       </c>
       <c r="H227" t="n" s="35">
         <v>46001.0</v>
       </c>
-      <c r="I227" t="n" s="69">
+      <c r="I227" t="n" s="45">
         <v>46001.0</v>
       </c>
-      <c r="J227" t="n" s="69">
+      <c r="J227" t="n" s="45">
         <v>46006.0</v>
       </c>
-      <c r="K227" t="n" s="65">
+      <c r="K227" t="n" s="39">
         <v>42.0</v>
       </c>
-      <c r="L227" s="71"/>
+      <c r="L227" t="n" s="49">
+        <v>46006.0</v>
+      </c>
       <c r="M227" s="33"/>
       <c r="N227" t="s" s="33">
         <v>237</v>
@@ -11580,40 +11582,42 @@
       <c r="S227" s="29"/>
     </row>
     <row r="228" hidden="true" outlineLevel="1">
-      <c r="A228" t="s" s="75">
+      <c r="A228" t="s" s="97">
         <v>239</v>
       </c>
-      <c r="B228" t="s" s="65">
+      <c r="B228" t="s" s="39">
         <v>52</v>
       </c>
-      <c r="C228" t="s" s="65">
+      <c r="C228" t="s" s="39">
         <v>231</v>
       </c>
-      <c r="D228" t="n" s="65">
+      <c r="D228" t="n" s="39">
         <v>2.2</v>
       </c>
-      <c r="E228" t="s" s="65">
+      <c r="E228" t="s" s="39">
         <v>233</v>
       </c>
-      <c r="F228" t="s" s="65">
+      <c r="F228" t="s" s="39">
         <v>234</v>
       </c>
-      <c r="G228" t="n" s="67">
+      <c r="G228" t="n" s="41">
         <v>46069.0</v>
       </c>
       <c r="H228" t="n" s="43">
         <v>46006.0</v>
       </c>
-      <c r="I228" t="n" s="69">
+      <c r="I228" t="n" s="45">
         <v>46006.0</v>
       </c>
-      <c r="J228" t="n" s="103">
+      <c r="J228" t="n" s="49">
         <v>46006.0</v>
       </c>
-      <c r="K228" t="n" s="65">
+      <c r="K228" t="n" s="39">
         <v>63.0</v>
       </c>
-      <c r="L228" s="71"/>
+      <c r="L228" t="n" s="49">
+        <v>46006.0</v>
+      </c>
       <c r="M228" s="11"/>
       <c r="N228" t="s" s="13">
         <v>240</v>
@@ -13221,40 +13225,42 @@
       <c r="S262" s="5"/>
     </row>
     <row r="263" hidden="false" outlineLevel="1">
-      <c r="A263" t="s" s="75">
+      <c r="A263" t="s" s="97">
         <v>284</v>
       </c>
-      <c r="B263" t="s" s="65">
+      <c r="B263" t="s" s="39">
         <v>89</v>
       </c>
-      <c r="C263" t="s" s="65">
+      <c r="C263" t="s" s="39">
         <v>272</v>
       </c>
-      <c r="D263" t="n" s="65">
+      <c r="D263" t="n" s="39">
         <v>1.4</v>
       </c>
-      <c r="E263" t="s" s="65">
+      <c r="E263" t="s" s="39">
         <v>273</v>
       </c>
-      <c r="F263" t="s" s="65">
+      <c r="F263" t="s" s="39">
         <v>274</v>
       </c>
-      <c r="G263" t="n" s="67">
+      <c r="G263" t="n" s="41">
         <v>46167.0</v>
       </c>
       <c r="H263" t="n" s="35">
         <v>46003.0</v>
       </c>
-      <c r="I263" t="n" s="69">
+      <c r="I263" t="n" s="45">
         <v>46003.0</v>
       </c>
-      <c r="J263" t="n" s="69">
+      <c r="J263" t="n" s="45">
         <v>46003.0</v>
       </c>
-      <c r="K263" t="n" s="65">
+      <c r="K263" t="n" s="39">
         <v>164.0</v>
       </c>
-      <c r="L263" s="71"/>
+      <c r="L263" t="n" s="49">
+        <v>46003.0</v>
+      </c>
       <c r="M263" s="33"/>
       <c r="N263" s="33"/>
       <c r="O263" t="s" s="33">
